--- a/output/NSE_200DMA_Recovery_Scanner.xlsx
+++ b/output/NSE_200DMA_Recovery_Scanner.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O87"/>
+  <dimension ref="A1:AF85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +492,91 @@
           <t>reasons</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>dividend_yield</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>roe</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>roce</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>net_profit_margin</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>debt_to_equity</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>current_ratio</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>quick_ratio</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>revenue_growth</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>profit_growth</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>fundamental_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -506,29 +587,33 @@
           <t>SUPREMEIND</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>46248</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>3558.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3587.1</v>
+        <v>3584.28</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.79</v>
+        <v>-0.71</v>
       </c>
       <c r="G2" t="n">
-        <v>3430.46</v>
+        <v>3426.33</v>
       </c>
       <c r="H2" t="n">
-        <v>58.64</v>
+        <v>58.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46100</v>
+        <v>1.36</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>3140</v>
@@ -548,6 +633,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>43.866634</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.3281016</v>
+      </c>
+      <c r="R2" t="n">
+        <v>81.13</v>
+      </c>
+      <c r="S2" t="n">
+        <v>103</v>
+      </c>
+      <c r="T2" t="n">
+        <v>452271374336</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>10.142</v>
+      </c>
+      <c r="X2" t="n">
+        <v>9.115</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -559,29 +685,33 @@
           <t>BLS</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>46248</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>278.12</v>
       </c>
       <c r="E3" t="n">
-        <v>279.17</v>
+        <v>279.51</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.38</v>
+        <v>-0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>250.71</v>
+        <v>251.14</v>
       </c>
       <c r="H3" t="n">
-        <v>75.52</v>
+        <v>74.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>45876</v>
+        <v>1.88</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
       </c>
       <c r="K3" t="n">
         <v>218.9</v>
@@ -601,6 +731,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P3" t="n">
+        <v>16.283373</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.646485</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="S3" t="n">
+        <v>111</v>
+      </c>
+      <c r="T3" t="n">
+        <v>114452561920</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>24.783</v>
+      </c>
+      <c r="X3" t="n">
+        <v>22.207001</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.468</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -612,8 +783,10 @@
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>46248</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>171.64</v>
@@ -633,8 +806,10 @@
       <c r="I4" t="n">
         <v>2.06</v>
       </c>
-      <c r="J4" s="1" t="n">
-        <v>46210</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>147.59</v>
@@ -654,6 +829,53 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>29.091524</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.079106</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>199</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1008188391424</v>
+      </c>
+      <c r="U4" t="n">
+        <v>21.639</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>19.485001</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.158</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>344.737</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -665,8 +887,10 @@
           <t>JUBLFOOD</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46248</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>504.1</v>
@@ -686,8 +910,10 @@
       <c r="I5" t="n">
         <v>3.43</v>
       </c>
-      <c r="J5" s="1" t="n">
-        <v>45860</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
       </c>
       <c r="K5" t="n">
         <v>408.55</v>
@@ -707,6 +933,43 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>86.91379000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14.464019</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24</v>
+      </c>
+      <c r="T5" t="n">
+        <v>331533746176</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>8.0299996</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -718,8 +981,10 @@
           <t>BDL</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>46248</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D6" t="n">
         <v>1398</v>
@@ -739,8 +1004,10 @@
       <c r="I6" t="n">
         <v>6.41</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <v>46210</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="K6" t="n">
         <v>1221</v>
@@ -760,6 +1027,53 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>122.41681</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12.074311</v>
+      </c>
+      <c r="R6" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="S6" t="n">
+        <v>37</v>
+      </c>
+      <c r="T6" t="n">
+        <v>512454361088</v>
+      </c>
+      <c r="U6" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>7.3709995</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17.214</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -771,8 +1085,10 @@
           <t>BHARTIHEXA</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>46248</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D7" t="n">
         <v>1621.1</v>
@@ -792,8 +1108,10 @@
       <c r="I7" t="n">
         <v>1.83</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>46238</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="K7" t="n">
         <v>1477.8</v>
@@ -813,6 +1131,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P7" t="n">
+        <v>44.43805</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.312315</v>
+      </c>
+      <c r="R7" t="n">
+        <v>36.48</v>
+      </c>
+      <c r="S7" t="n">
+        <v>115</v>
+      </c>
+      <c r="T7" t="n">
+        <v>810549968896</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>31.945</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>85.654</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -824,8 +1183,10 @@
           <t>CESC</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>46248</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>167.83</v>
@@ -845,8 +1206,10 @@
       <c r="I8" t="n">
         <v>4.49</v>
       </c>
-      <c r="J8" s="1" t="n">
-        <v>46210</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="K8" t="n">
         <v>158.93</v>
@@ -866,6 +1229,53 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>14.044352</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.7764677</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="S8" t="n">
+        <v>373</v>
+      </c>
+      <c r="T8" t="n">
+        <v>222470488064</v>
+      </c>
+      <c r="U8" t="n">
+        <v>12.547</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>12.3050004</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>164.311</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -874,41 +1284,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>46247</v>
+          <t>JYOTICNC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>951.7</v>
+        <v>826.9</v>
       </c>
       <c r="E9" t="n">
-        <v>944.37</v>
+        <v>818.76</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="G9" t="n">
-        <v>917.52</v>
+        <v>767.6</v>
       </c>
       <c r="H9" t="n">
-        <v>56.78</v>
+        <v>55.54</v>
       </c>
       <c r="I9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>46226</v>
+        <v>0.65</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="K9" t="n">
-        <v>903.25</v>
+        <v>738.9</v>
       </c>
       <c r="L9" t="n">
-        <v>5.36</v>
+        <v>11.91</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -917,8 +1331,47 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>58.438168</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9.402361000000001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>188056174592</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>18.441999</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.681</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>42.585</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -927,38 +1380,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TEGA</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>46248</v>
+          <t>PFIZER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>1703.8</v>
+        <v>4874.8</v>
       </c>
       <c r="E10" t="n">
-        <v>1754.54</v>
+        <v>4811.81</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.89</v>
+        <v>1.31</v>
       </c>
       <c r="G10" t="n">
-        <v>1661.3</v>
+        <v>4640.3</v>
       </c>
       <c r="H10" t="n">
-        <v>63.24</v>
+        <v>57.37</v>
       </c>
       <c r="I10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>46191</v>
+        <v>0.33</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
       </c>
       <c r="K10" t="n">
-        <v>1473</v>
+        <v>4360.1</v>
       </c>
       <c r="L10" t="n">
-        <v>15.67</v>
+        <v>11.8</v>
       </c>
       <c r="M10" t="n">
         <v>95</v>
@@ -970,8 +1427,49 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>31.055614</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.306124</v>
+      </c>
+      <c r="R10" t="n">
+        <v>156.97</v>
+      </c>
+      <c r="S10" t="n">
+        <v>150</v>
+      </c>
+      <c r="T10" t="n">
+        <v>223011028992</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>35.718</v>
+      </c>
+      <c r="X10" t="n">
+        <v>28.608</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.671</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -980,38 +1478,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>46248</v>
+          <t>CLEAN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>1298</v>
+        <v>821.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1310.76</v>
+        <v>810.67</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.97</v>
+        <v>1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>1208.71</v>
+        <v>771.58</v>
       </c>
       <c r="H11" t="n">
-        <v>67.19</v>
+        <v>63.16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>45924</v>
+        <v>0.58</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
       </c>
       <c r="K11" t="n">
-        <v>1123.6</v>
+        <v>652</v>
       </c>
       <c r="L11" t="n">
-        <v>15.52</v>
+        <v>26</v>
       </c>
       <c r="M11" t="n">
         <v>95</v>
@@ -1025,6 +1527,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P11" t="n">
+        <v>38.17379</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.515607</v>
+      </c>
+      <c r="R11" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="S11" t="n">
+        <v>72</v>
+      </c>
+      <c r="T11" t="n">
+        <v>87311089664</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>28.083</v>
+      </c>
+      <c r="X11" t="n">
+        <v>23.719</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -1033,38 +1576,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>46248</v>
+          <t>CEATLTD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>826.9</v>
+        <v>3688.8</v>
       </c>
       <c r="E12" t="n">
-        <v>818.42</v>
+        <v>3639.73</v>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G12" t="n">
-        <v>771.08</v>
+        <v>3549.95</v>
       </c>
       <c r="H12" t="n">
-        <v>55.32</v>
+        <v>55.54</v>
       </c>
       <c r="I12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>46241</v>
+        <v>0.19</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
       </c>
       <c r="K12" t="n">
-        <v>738.9</v>
+        <v>3309.1</v>
       </c>
       <c r="L12" t="n">
-        <v>11.91</v>
+        <v>11.47</v>
       </c>
       <c r="M12" t="n">
         <v>95</v>
@@ -1078,6 +1625,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P12" t="n">
+        <v>25.264025</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5360997</v>
+      </c>
+      <c r="R12" t="n">
+        <v>146.01</v>
+      </c>
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
+      <c r="T12" t="n">
+        <v>149212299264</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>4.145</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>64.742</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-96.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-96.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -1086,41 +1674,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CEATLTD</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>46248</v>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>3688.8</v>
+        <v>282.6</v>
       </c>
       <c r="E13" t="n">
-        <v>3643.27</v>
+        <v>279.26</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3547.64</v>
+        <v>278.79</v>
       </c>
       <c r="H13" t="n">
-        <v>54.95</v>
+        <v>55.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>46220</v>
+        <v>2.54</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="K13" t="n">
-        <v>3309.1</v>
+        <v>273</v>
       </c>
       <c r="L13" t="n">
-        <v>11.47</v>
+        <v>3.52</v>
       </c>
       <c r="M13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1129,8 +1721,49 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>10.078459</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.9018266</v>
+      </c>
+      <c r="R13" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="S13" t="n">
+        <v>358</v>
+      </c>
+      <c r="T13" t="n">
+        <v>423900053504</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>24.001</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11.3199994</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.507</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1139,41 +1772,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PFIZER</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>46248</v>
+          <t>MRPL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>4874.8</v>
+        <v>170.54</v>
       </c>
       <c r="E14" t="n">
-        <v>4809.38</v>
+        <v>166.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>4647.65</v>
+        <v>162.15</v>
       </c>
       <c r="H14" t="n">
-        <v>57.07</v>
+        <v>52.59</v>
       </c>
       <c r="I14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>46065</v>
+        <v>0.28</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="K14" t="n">
-        <v>4360.1</v>
+        <v>161.2</v>
       </c>
       <c r="L14" t="n">
-        <v>11.8</v>
+        <v>5.79</v>
       </c>
       <c r="M14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1182,8 +1819,45 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>9.728465</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.097534</v>
+      </c>
+      <c r="R14" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="S14" t="n">
+        <v>229</v>
+      </c>
+      <c r="T14" t="n">
+        <v>298888200192</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.8670002</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>108.059</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1192,41 +1866,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLEAN</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>46248</v>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>821.5</v>
+        <v>444.1</v>
       </c>
       <c r="E15" t="n">
-        <v>809.1</v>
+        <v>456.75</v>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>-2.77</v>
       </c>
       <c r="G15" t="n">
-        <v>770.4299999999999</v>
+        <v>428.23</v>
       </c>
       <c r="H15" t="n">
-        <v>63.78</v>
+        <v>58.97</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>45856</v>
+        <v>0.44</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
       </c>
       <c r="K15" t="n">
-        <v>652</v>
+        <v>365.3</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>21.57</v>
       </c>
       <c r="M15" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1235,8 +1913,49 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>16.460342</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.6806881</v>
+      </c>
+      <c r="R15" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="S15" t="n">
+        <v>248</v>
+      </c>
+      <c r="T15" t="n">
+        <v>280929370112</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>6.451</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5.829</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>21.987</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2660</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2660</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1245,41 +1964,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>46248</v>
+          <t>SBFC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>282.6</v>
+        <v>94.05</v>
       </c>
       <c r="E16" t="n">
-        <v>279.26</v>
+        <v>96.66</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>278.79</v>
+        <v>92.22</v>
       </c>
       <c r="H16" t="n">
-        <v>55.2</v>
+        <v>55.99</v>
       </c>
       <c r="I16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>46245</v>
+        <v>0.42</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
       </c>
       <c r="K16" t="n">
-        <v>273</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>3.52</v>
+        <v>18.15</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1288,8 +2011,47 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>21.5711</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.7916298</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>104160116736</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>58.55099999999999</v>
+      </c>
+      <c r="X16" t="n">
+        <v>44.877997</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>195.685</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -1298,41 +2060,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MRPL</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>46248</v>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>170.54</v>
+        <v>940</v>
       </c>
       <c r="E17" t="n">
-        <v>166.6</v>
+        <v>963.5599999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>-2.45</v>
       </c>
       <c r="G17" t="n">
-        <v>162.15</v>
+        <v>892.75</v>
       </c>
       <c r="H17" t="n">
-        <v>52.59</v>
+        <v>56.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>46244</v>
+        <v>0.65</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
       </c>
       <c r="K17" t="n">
-        <v>161.2</v>
+        <v>784.95</v>
       </c>
       <c r="L17" t="n">
-        <v>5.79</v>
+        <v>19.75</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1341,8 +2107,49 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>47.739967</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9.69312</v>
+      </c>
+      <c r="R17" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="S17" t="n">
+        <v>129</v>
+      </c>
+      <c r="T17" t="n">
+        <v>162499756032</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>26.553</v>
+      </c>
+      <c r="X17" t="n">
+        <v>24.400999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -1351,38 +2158,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>46248</v>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>444.1</v>
+        <v>1496.5</v>
       </c>
       <c r="E18" t="n">
-        <v>456.36</v>
+        <v>1530.94</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.69</v>
+        <v>-2.25</v>
       </c>
       <c r="G18" t="n">
-        <v>428.86</v>
+        <v>1443.66</v>
       </c>
       <c r="H18" t="n">
-        <v>59.27</v>
+        <v>59.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>46069</v>
+        <v>1.03</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
       </c>
       <c r="K18" t="n">
-        <v>365.3</v>
+        <v>1356.6</v>
       </c>
       <c r="L18" t="n">
-        <v>21.57</v>
+        <v>10.31</v>
       </c>
       <c r="M18" t="n">
         <v>85</v>
@@ -1396,6 +2207,53 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P18" t="n">
+        <v>55.241787</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.703518</v>
+      </c>
+      <c r="R18" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="S18" t="n">
+        <v>88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>393700409344</v>
+      </c>
+      <c r="U18" t="n">
+        <v>12.517</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>18.714</v>
+      </c>
+      <c r="X18" t="n">
+        <v>14.272</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28.466</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -1404,38 +2262,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBFC</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>46248</v>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>94.05</v>
+        <v>5558</v>
       </c>
       <c r="E19" t="n">
-        <v>96.54000000000001</v>
+        <v>5682.22</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.58</v>
+        <v>-2.19</v>
       </c>
       <c r="G19" t="n">
-        <v>92.16</v>
+        <v>5348.37</v>
       </c>
       <c r="H19" t="n">
-        <v>56.47</v>
+        <v>57.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>46042</v>
+        <v>0.77</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
       </c>
       <c r="K19" t="n">
-        <v>79.59999999999999</v>
+        <v>5035</v>
       </c>
       <c r="L19" t="n">
-        <v>18.15</v>
+        <v>10.39</v>
       </c>
       <c r="M19" t="n">
         <v>85</v>
@@ -1449,6 +2311,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P19" t="n">
+        <v>51.287254</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>26.21624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>108.37</v>
+      </c>
+      <c r="S19" t="n">
+        <v>161</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1338745946112</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>15.212</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13.376</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26.875</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -1457,38 +2360,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>46248</v>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>1496.5</v>
+        <v>737.85</v>
       </c>
       <c r="E20" t="n">
-        <v>1535.22</v>
+        <v>751.37</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.52</v>
+        <v>-1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1446.39</v>
+        <v>711.95</v>
       </c>
       <c r="H20" t="n">
-        <v>58.89</v>
+        <v>55.85</v>
       </c>
       <c r="I20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>46157</v>
+        <v>0.67</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
       </c>
       <c r="K20" t="n">
-        <v>1356.6</v>
+        <v>652.25</v>
       </c>
       <c r="L20" t="n">
-        <v>10.31</v>
+        <v>13.12</v>
       </c>
       <c r="M20" t="n">
         <v>85</v>
@@ -1502,6 +2409,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P20" t="n">
+        <v>18.755718</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13.507057</v>
+      </c>
+      <c r="R20" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>54</v>
+      </c>
+      <c r="T20" t="n">
+        <v>607951388672</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>9.103999999999999</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.379</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>37.523</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1510,38 +2458,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>46248</v>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>940</v>
+        <v>1298</v>
       </c>
       <c r="E21" t="n">
-        <v>962.38</v>
+        <v>1311.85</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.33</v>
+        <v>-1.06</v>
       </c>
       <c r="G21" t="n">
-        <v>894.14</v>
+        <v>1206.51</v>
       </c>
       <c r="H21" t="n">
-        <v>56.43</v>
+        <v>67.27</v>
       </c>
       <c r="I21" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>45971</v>
+        <v>0.71</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="K21" t="n">
-        <v>784.95</v>
+        <v>1123.6</v>
       </c>
       <c r="L21" t="n">
-        <v>19.75</v>
+        <v>15.52</v>
       </c>
       <c r="M21" t="n">
         <v>85</v>
@@ -1555,6 +2507,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P21" t="n">
+        <v>48.778652</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8.610682000000001</v>
+      </c>
+      <c r="R21" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="S21" t="n">
+        <v>94</v>
+      </c>
+      <c r="T21" t="n">
+        <v>814575058944</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>5.302</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.923</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.801</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -1563,41 +2556,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>46248</v>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>5558</v>
+        <v>144.1</v>
       </c>
       <c r="E22" t="n">
-        <v>5680</v>
+        <v>147.76</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.15</v>
+        <v>-2.47</v>
       </c>
       <c r="G22" t="n">
-        <v>5354.29</v>
+        <v>142.97</v>
       </c>
       <c r="H22" t="n">
-        <v>56.21</v>
+        <v>53.56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>46100</v>
+        <v>0.46</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="K22" t="n">
-        <v>5035</v>
+        <v>135.62</v>
       </c>
       <c r="L22" t="n">
-        <v>10.39</v>
+        <v>6.25</v>
       </c>
       <c r="M22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1606,8 +2603,49 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>5.337037</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.7214199</v>
+      </c>
+      <c r="R22" t="n">
+        <v>27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>323</v>
+      </c>
+      <c r="T22" t="n">
+        <v>656039411712</v>
+      </c>
+      <c r="U22" t="n">
+        <v>13.697</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>48.535</v>
+      </c>
+      <c r="X22" t="n">
+        <v>34.992</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="23">
@@ -1616,41 +2654,45 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JSL</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>46248</v>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>737.85</v>
+        <v>410.8</v>
       </c>
       <c r="E23" t="n">
-        <v>751.03</v>
+        <v>419.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.75</v>
+        <v>-2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>712.84</v>
+        <v>408.23</v>
       </c>
       <c r="H23" t="n">
-        <v>55.79</v>
+        <v>58.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>46150</v>
+        <v>0.58</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="K23" t="n">
-        <v>652.25</v>
+        <v>382.2</v>
       </c>
       <c r="L23" t="n">
-        <v>13.12</v>
+        <v>7.48</v>
       </c>
       <c r="M23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1659,8 +2701,49 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>48.788597</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12.517901</v>
+      </c>
+      <c r="R23" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3002857160704</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>22.135</v>
+      </c>
+      <c r="X23" t="n">
+        <v>21.403</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="24">
@@ -1669,38 +2752,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>46248</v>
+          <t>COHANCE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>144.1</v>
+        <v>440.65</v>
       </c>
       <c r="E24" t="n">
-        <v>147.76</v>
+        <v>444.74</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.47</v>
+        <v>-0.92</v>
       </c>
       <c r="G24" t="n">
-        <v>142.97</v>
+        <v>437.84</v>
       </c>
       <c r="H24" t="n">
-        <v>53.56</v>
+        <v>50.99</v>
       </c>
       <c r="I24" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>46225</v>
+        <v>0.36</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="K24" t="n">
-        <v>135.62</v>
+        <v>438.5</v>
       </c>
       <c r="L24" t="n">
-        <v>6.25</v>
+        <v>0.49</v>
       </c>
       <c r="M24" t="n">
         <v>80</v>
@@ -1712,8 +2799,47 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>160.23636</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.3186584</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>168591523840</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-11.457</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.961</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.928000000000001</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-96.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-96.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1722,38 +2848,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>46248</v>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>410.8</v>
+        <v>221.06</v>
       </c>
       <c r="E25" t="n">
-        <v>419.76</v>
+        <v>220.31</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.14</v>
+        <v>0.34</v>
       </c>
       <c r="G25" t="n">
-        <v>408.23</v>
+        <v>217.22</v>
       </c>
       <c r="H25" t="n">
-        <v>58.27</v>
+        <v>49.38</v>
       </c>
       <c r="I25" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>46210</v>
+        <v>0.26</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
       </c>
       <c r="K25" t="n">
-        <v>382.2</v>
+        <v>210.24</v>
       </c>
       <c r="L25" t="n">
-        <v>7.48</v>
+        <v>5.15</v>
       </c>
       <c r="M25" t="n">
         <v>80</v>
@@ -1765,8 +2895,49 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>25.438437</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.9687612</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="S25" t="n">
+        <v>249</v>
+      </c>
+      <c r="T25" t="n">
+        <v>106242269184</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>18.431</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16.983</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1775,38 +2946,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COHANCE</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>46248</v>
+          <t>ASAHIINDIA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>440.65</v>
+        <v>939.2</v>
       </c>
       <c r="E26" t="n">
-        <v>442.57</v>
+        <v>912.46</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.43</v>
+        <v>2.93</v>
       </c>
       <c r="G26" t="n">
-        <v>437.72</v>
+        <v>886.15</v>
       </c>
       <c r="H26" t="n">
-        <v>51.24</v>
+        <v>62.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>46246</v>
+        <v>3.49</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="K26" t="n">
-        <v>438.5</v>
+        <v>879.1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>6.84</v>
       </c>
       <c r="M26" t="n">
         <v>80</v>
@@ -1818,8 +2993,49 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>54.039127</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.0853057</v>
+      </c>
+      <c r="R26" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21</v>
+      </c>
+      <c r="T26" t="n">
+        <v>239427633152</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>17.254</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8.457000000000001</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>55.868</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1828,41 +3044,45 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RITES</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>46248</v>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>221.06</v>
+        <v>1402.9</v>
       </c>
       <c r="E27" t="n">
-        <v>220.44</v>
+        <v>1436.48</v>
       </c>
       <c r="F27" t="n">
-        <v>0.28</v>
+        <v>-2.34</v>
       </c>
       <c r="G27" t="n">
-        <v>216.83</v>
+        <v>1361.18</v>
       </c>
       <c r="H27" t="n">
-        <v>49.44</v>
+        <v>51.87</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>46217</v>
+        <v>1.55</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
       </c>
       <c r="K27" t="n">
-        <v>210.24</v>
+        <v>1080.1</v>
       </c>
       <c r="L27" t="n">
-        <v>5.15</v>
+        <v>29.89</v>
       </c>
       <c r="M27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1871,8 +3091,47 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
-        </is>
+          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>4.1930685</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-31.78</v>
+      </c>
+      <c r="S27" t="n">
+        <v>18</v>
+      </c>
+      <c r="T27" t="n">
+        <v>155129659392</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-8.911</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-186.002</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-24.914</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>152.371</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -1881,41 +3140,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>46248</v>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>939.2</v>
+        <v>4060</v>
       </c>
       <c r="E28" t="n">
-        <v>912.1799999999999</v>
+        <v>4038.19</v>
       </c>
       <c r="F28" t="n">
-        <v>2.96</v>
+        <v>0.54</v>
       </c>
       <c r="G28" t="n">
-        <v>885.64</v>
+        <v>4083.48</v>
       </c>
       <c r="H28" t="n">
-        <v>62.96</v>
+        <v>53.37</v>
       </c>
       <c r="I28" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>46241</v>
+        <v>0.66</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="K28" t="n">
-        <v>879.1</v>
+        <v>3755.1</v>
       </c>
       <c r="L28" t="n">
-        <v>6.84</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1924,8 +3187,47 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>86.733604</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10.799423</v>
+      </c>
+      <c r="R28" t="n">
+        <v>46.81</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>2648118657024</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>6.447</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.2919997</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.913</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1934,38 +3236,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABREL</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>46248</v>
+          <t>SCHAEFFLER</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>1402.9</v>
+        <v>4043.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1435.1</v>
+        <v>4004.06</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.24</v>
+        <v>0.98</v>
       </c>
       <c r="G29" t="n">
-        <v>1364.79</v>
+        <v>4119.02</v>
       </c>
       <c r="H29" t="n">
-        <v>51.74</v>
+        <v>44.24</v>
       </c>
       <c r="I29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>45842</v>
+        <v>2.78</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
       </c>
       <c r="K29" t="n">
-        <v>1080.1</v>
+        <v>3811.1</v>
       </c>
       <c r="L29" t="n">
-        <v>29.89</v>
+        <v>6.09</v>
       </c>
       <c r="M29" t="n">
         <v>75</v>
@@ -1977,8 +3283,55 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>50.43283</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10.30154</v>
+      </c>
+      <c r="R29" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="S29" t="n">
+        <v>85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>631966990336</v>
+      </c>
+      <c r="U29" t="n">
+        <v>21.645</v>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>14.774999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.9320005</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -1987,38 +3340,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>46248</v>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>4060</v>
+        <v>591.55</v>
       </c>
       <c r="E30" t="n">
-        <v>4036.69</v>
+        <v>581.48</v>
       </c>
       <c r="F30" t="n">
-        <v>0.58</v>
+        <v>1.73</v>
       </c>
       <c r="G30" t="n">
-        <v>4079.02</v>
+        <v>542.85</v>
       </c>
       <c r="H30" t="n">
-        <v>53.84</v>
+        <v>59.64</v>
       </c>
       <c r="I30" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>46206</v>
+        <v>1.12</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
       </c>
       <c r="K30" t="n">
-        <v>3755.1</v>
+        <v>450.75</v>
       </c>
       <c r="L30" t="n">
-        <v>8.119999999999999</v>
+        <v>31.24</v>
       </c>
       <c r="M30" t="n">
         <v>75</v>
@@ -2030,8 +3387,55 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>29.951899</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>28.286232</v>
+      </c>
+      <c r="R30" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>34</v>
+      </c>
+      <c r="T30" t="n">
+        <v>192941342720</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10.786</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>20.204</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11.311</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>84.316</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="31">
@@ -2040,38 +3444,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>46248</v>
+          <t>M%26M</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>4043.2</v>
+        <v>3428.3</v>
       </c>
       <c r="E31" t="n">
-        <v>4005.09</v>
+        <v>3354.41</v>
       </c>
       <c r="F31" t="n">
-        <v>0.95</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>4119.89</v>
+        <v>3197.21</v>
       </c>
       <c r="H31" t="n">
-        <v>44.28</v>
+        <v>59.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>46184</v>
+        <v>0.41</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
       </c>
       <c r="K31" t="n">
-        <v>3811.1</v>
+        <v>2896</v>
       </c>
       <c r="L31" t="n">
-        <v>6.09</v>
+        <v>18.38</v>
       </c>
       <c r="M31" t="n">
         <v>75</v>
@@ -2083,8 +3491,49 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>20.877535</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.115483</v>
+      </c>
+      <c r="R31" t="n">
+        <v>164.21</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.9599999499999999</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4116573323264</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>17.031</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.609</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>125.278</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="32">
@@ -2093,38 +3542,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>46248</v>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>591.55</v>
+        <v>118</v>
       </c>
       <c r="E32" t="n">
-        <v>580.59</v>
+        <v>115.23</v>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="n">
-        <v>544.6900000000001</v>
+        <v>109.29</v>
       </c>
       <c r="H32" t="n">
-        <v>59.55</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>45965</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
       </c>
       <c r="K32" t="n">
-        <v>450.75</v>
+        <v>98.5</v>
       </c>
       <c r="L32" t="n">
-        <v>31.24</v>
+        <v>19.8</v>
       </c>
       <c r="M32" t="n">
         <v>75</v>
@@ -2138,6 +3591,47 @@
         <is>
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P32" t="n">
+        <v>6.1426344</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.86730266</v>
+      </c>
+      <c r="R32" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="S32" t="n">
+        <v>255</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1356167249920</v>
+      </c>
+      <c r="U32" t="n">
+        <v>14.965999</v>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>29.405</v>
+      </c>
+      <c r="X32" t="n">
+        <v>38.147</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="33">
@@ -2146,38 +3640,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M%26M</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>46248</v>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>3428.3</v>
+        <v>3167.4</v>
       </c>
       <c r="E33" t="n">
-        <v>3354.41</v>
+        <v>3085.47</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="G33" t="n">
-        <v>3197.21</v>
+        <v>3099.91</v>
       </c>
       <c r="H33" t="n">
-        <v>59.7</v>
+        <v>58.91</v>
       </c>
       <c r="I33" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>46080</v>
+        <v>0.68</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
       </c>
       <c r="K33" t="n">
-        <v>2896</v>
+        <v>2862</v>
       </c>
       <c r="L33" t="n">
-        <v>18.38</v>
+        <v>10.67</v>
       </c>
       <c r="M33" t="n">
         <v>75</v>
@@ -2191,6 +3689,31 @@
         <is>
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P33" t="n">
+        <v>7.347592</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.883686</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>144244375552</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -2199,38 +3722,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>46248</v>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>118</v>
+        <v>2545</v>
       </c>
       <c r="E34" t="n">
-        <v>115.23</v>
+        <v>2478.76</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="G34" t="n">
-        <v>109.29</v>
+        <v>2340.14</v>
       </c>
       <c r="H34" t="n">
-        <v>68.73999999999999</v>
+        <v>63.59</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J34" s="1" t="n">
-        <v>46094</v>
+        <v>0.57</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="K34" t="n">
-        <v>98.5</v>
+        <v>2013</v>
       </c>
       <c r="L34" t="n">
-        <v>19.8</v>
+        <v>26.43</v>
       </c>
       <c r="M34" t="n">
         <v>75</v>
@@ -2244,6 +3771,53 @@
         <is>
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P34" t="n">
+        <v>25.444912</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.2841005</v>
+      </c>
+      <c r="R34" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="S34" t="n">
+        <v>244</v>
+      </c>
+      <c r="T34" t="n">
+        <v>485629394944</v>
+      </c>
+      <c r="U34" t="n">
+        <v>17.743999</v>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="n">
+        <v>14.783</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.5559995</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>24.675</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -2252,51 +3826,102 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>46248</v>
+          <t>HEXT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>3167.4</v>
+        <v>569.85</v>
       </c>
       <c r="E35" t="n">
-        <v>3083.74</v>
+        <v>582.21</v>
       </c>
       <c r="F35" t="n">
-        <v>2.71</v>
+        <v>-2.12</v>
       </c>
       <c r="G35" t="n">
-        <v>3096.47</v>
+        <v>540.83</v>
       </c>
       <c r="H35" t="n">
-        <v>59.25</v>
+        <v>53.78</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>46210</v>
+        <v>0.12</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="K35" t="n">
-        <v>2862</v>
+        <v>548.8</v>
       </c>
       <c r="L35" t="n">
-        <v>10.67</v>
+        <v>3.84</v>
       </c>
       <c r="M35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>26.16391</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.177395</v>
+      </c>
+      <c r="R35" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="S35" t="n">
+        <v>248</v>
+      </c>
+      <c r="T35" t="n">
+        <v>347489959936</v>
+      </c>
+      <c r="U35" t="n">
+        <v>21.473</v>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>13.739</v>
+      </c>
+      <c r="X35" t="n">
+        <v>9.318</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -2305,51 +3930,96 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>46248</v>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>2545</v>
+        <v>561.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2476.31</v>
+        <v>571.86</v>
       </c>
       <c r="F36" t="n">
-        <v>2.77</v>
+        <v>-1.74</v>
       </c>
       <c r="G36" t="n">
-        <v>2340.39</v>
+        <v>547.61</v>
       </c>
       <c r="H36" t="n">
-        <v>63.96</v>
+        <v>50.66</v>
       </c>
       <c r="I36" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>46057</v>
+        <v>1.01</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K36" t="n">
-        <v>2013</v>
+        <v>557.8</v>
       </c>
       <c r="L36" t="n">
-        <v>26.43</v>
+        <v>0.74</v>
       </c>
       <c r="M36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>14.326874</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>10.491822</v>
+      </c>
+      <c r="R36" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>374</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2374206750720</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>54.70699999999999</v>
+      </c>
+      <c r="X36" t="n">
+        <v>38.068</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.034</v>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="37">
@@ -2358,38 +4028,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HEXT</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>46248</v>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>569.85</v>
+        <v>1344.4</v>
       </c>
       <c r="E37" t="n">
-        <v>582.21</v>
+        <v>1359.51</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.12</v>
+        <v>-1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>540.83</v>
+        <v>1332.85</v>
       </c>
       <c r="H37" t="n">
-        <v>53.78</v>
+        <v>50.88</v>
       </c>
       <c r="I37" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J37" s="1" t="n">
-        <v>46233</v>
+        <v>0.44</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
       <c r="K37" t="n">
-        <v>548.8</v>
+        <v>1305</v>
       </c>
       <c r="L37" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="M37" t="n">
         <v>70</v>
@@ -2403,6 +4077,53 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P37" t="n">
+        <v>59.513058</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>14.337361</v>
+      </c>
+      <c r="R37" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="S37" t="n">
+        <v>95</v>
+      </c>
+      <c r="T37" t="n">
+        <v>280979603456</v>
+      </c>
+      <c r="U37" t="n">
+        <v>23.913</v>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="X37" t="n">
+        <v>36.923</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.464</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="38">
@@ -2411,38 +4132,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>46248</v>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D38" t="n">
-        <v>561.9</v>
+        <v>27060</v>
       </c>
       <c r="E38" t="n">
-        <v>571.86</v>
+        <v>27350.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.74</v>
+        <v>-1.06</v>
       </c>
       <c r="G38" t="n">
-        <v>547.61</v>
+        <v>26943.3</v>
       </c>
       <c r="H38" t="n">
-        <v>50.66</v>
+        <v>42.71</v>
       </c>
       <c r="I38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J38" s="1" t="n">
-        <v>46248</v>
+        <v>1.67</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K38" t="n">
-        <v>557.8</v>
+        <v>27000</v>
       </c>
       <c r="L38" t="n">
-        <v>0.74</v>
+        <v>0.22</v>
       </c>
       <c r="M38" t="n">
         <v>70</v>
@@ -2454,8 +4179,55 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>35.626358</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>12.044059</v>
+      </c>
+      <c r="R38" t="n">
+        <v>759.55</v>
+      </c>
+      <c r="S38" t="n">
+        <v>190</v>
+      </c>
+      <c r="T38" t="n">
+        <v>575006113792</v>
+      </c>
+      <c r="U38" t="n">
+        <v>34.460998</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>27.021</v>
+      </c>
+      <c r="X38" t="n">
+        <v>22.399001</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.878</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="39">
@@ -2464,38 +4236,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CDSL</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>46248</v>
+          <t>NUVOCO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>1344.4</v>
+        <v>331.55</v>
       </c>
       <c r="E39" t="n">
-        <v>1359.51</v>
+        <v>333.74</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.11</v>
+        <v>-0.66</v>
       </c>
       <c r="G39" t="n">
-        <v>1332.85</v>
+        <v>329.74</v>
       </c>
       <c r="H39" t="n">
-        <v>50.88</v>
+        <v>44.42</v>
       </c>
       <c r="I39" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J39" s="1" t="n">
-        <v>46224</v>
+        <v>0.32</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K39" t="n">
-        <v>1305</v>
+        <v>330.25</v>
       </c>
       <c r="L39" t="n">
-        <v>3.02</v>
+        <v>0.39</v>
       </c>
       <c r="M39" t="n">
         <v>70</v>
@@ -2507,8 +4283,47 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>31.160711</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.157679</v>
+      </c>
+      <c r="R39" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>118415122432</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>10.953</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.329</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>48.061</v>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -2517,38 +4332,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>46248</v>
+          <t>CHALET</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D40" t="n">
-        <v>27060</v>
+        <v>825.1</v>
       </c>
       <c r="E40" t="n">
-        <v>27340.9</v>
+        <v>826.87</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.03</v>
+        <v>-0.21</v>
       </c>
       <c r="G40" t="n">
-        <v>26978.6</v>
+        <v>815.9299999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>42.24</v>
+        <v>48.36</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>46248</v>
+        <v>0.71</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="K40" t="n">
-        <v>27000</v>
+        <v>811.8</v>
       </c>
       <c r="L40" t="n">
-        <v>0.22</v>
+        <v>1.64</v>
       </c>
       <c r="M40" t="n">
         <v>70</v>
@@ -2560,8 +4379,49 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>34.12324</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.882711</v>
+      </c>
+      <c r="R40" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="S40" t="n">
+        <v>24</v>
+      </c>
+      <c r="T40" t="n">
+        <v>180692041728</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>33.731</v>
+      </c>
+      <c r="X40" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>64.041</v>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="41">
@@ -2570,38 +4430,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>46248</v>
+          <t>LINDEINDIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D41" t="n">
-        <v>331.55</v>
+        <v>6696</v>
       </c>
       <c r="E41" t="n">
-        <v>333.74</v>
+        <v>6659.96</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.66</v>
+        <v>0.54</v>
       </c>
       <c r="G41" t="n">
-        <v>329.74</v>
+        <v>7006.07</v>
       </c>
       <c r="H41" t="n">
-        <v>44.42</v>
+        <v>39.57</v>
       </c>
       <c r="I41" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>46248</v>
+        <v>0.66</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
       </c>
       <c r="K41" t="n">
-        <v>330.25</v>
+        <v>5673</v>
       </c>
       <c r="L41" t="n">
-        <v>0.39</v>
+        <v>18.03</v>
       </c>
       <c r="M41" t="n">
         <v>70</v>
@@ -2613,8 +4477,47 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>104.28282</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>13.3846655</v>
+      </c>
+      <c r="R41" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="n">
+        <v>571063140352</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>20.444</v>
+      </c>
+      <c r="X41" t="n">
+        <v>20.587</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="42">
@@ -2623,38 +4526,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHALET</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>46248</v>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>825.1</v>
+        <v>287.3</v>
       </c>
       <c r="E42" t="n">
-        <v>826.27</v>
+        <v>283.54</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.14</v>
+        <v>1.32</v>
       </c>
       <c r="G42" t="n">
-        <v>816.61</v>
+        <v>324.36</v>
       </c>
       <c r="H42" t="n">
-        <v>48.48</v>
+        <v>31.65</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J42" s="1" t="n">
-        <v>46245</v>
+        <v>0.76</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
       </c>
       <c r="K42" t="n">
-        <v>811.8</v>
+        <v>208.63</v>
       </c>
       <c r="L42" t="n">
-        <v>1.64</v>
+        <v>37.71</v>
       </c>
       <c r="M42" t="n">
         <v>70</v>
@@ -2666,8 +4573,49 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>26.382</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.2775254</v>
+      </c>
+      <c r="R42" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="S42" t="n">
+        <v>173</v>
+      </c>
+      <c r="T42" t="n">
+        <v>262502383616</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>24.655001</v>
+      </c>
+      <c r="X42" t="n">
+        <v>20.698</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>129.314</v>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="43">
@@ -2676,38 +4624,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>46248</v>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D43" t="n">
-        <v>6696</v>
+        <v>531.15</v>
       </c>
       <c r="E43" t="n">
-        <v>6663.26</v>
+        <v>521.38</v>
       </c>
       <c r="F43" t="n">
-        <v>0.49</v>
+        <v>1.87</v>
       </c>
       <c r="G43" t="n">
-        <v>7000.76</v>
+        <v>510.3</v>
       </c>
       <c r="H43" t="n">
-        <v>39.53</v>
+        <v>61.67</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J43" s="1" t="n">
-        <v>45924</v>
+        <v>1.04</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="K43" t="n">
-        <v>5673</v>
+        <v>487.9</v>
       </c>
       <c r="L43" t="n">
-        <v>18.03</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>70</v>
@@ -2719,8 +4671,49 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>16.582893</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.5415702</v>
+      </c>
+      <c r="R43" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="S43" t="n">
+        <v>38</v>
+      </c>
+      <c r="T43" t="n">
+        <v>187167326208</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>35.115</v>
+      </c>
+      <c r="X43" t="n">
+        <v>19.941</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>35.204</v>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -2729,38 +4722,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>46248</v>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D44" t="n">
-        <v>287.3</v>
+        <v>4057</v>
       </c>
       <c r="E44" t="n">
-        <v>283.54</v>
+        <v>3978.76</v>
       </c>
       <c r="F44" t="n">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="G44" t="n">
-        <v>324.36</v>
+        <v>3998.81</v>
       </c>
       <c r="H44" t="n">
-        <v>31.65</v>
+        <v>58.6</v>
       </c>
       <c r="I44" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J44" s="1" t="n">
-        <v>46069</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
       </c>
       <c r="K44" t="n">
-        <v>208.63</v>
+        <v>3720</v>
       </c>
       <c r="L44" t="n">
-        <v>37.71</v>
+        <v>9.06</v>
       </c>
       <c r="M44" t="n">
         <v>70</v>
@@ -2772,8 +4769,49 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>33.782997</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>5.1065493</v>
+      </c>
+      <c r="R44" t="n">
+        <v>120.09</v>
+      </c>
+      <c r="S44" t="n">
+        <v>93</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5581888815104</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>10.609999</v>
+      </c>
+      <c r="X44" t="n">
+        <v>5.588</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -2782,38 +4820,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>46248</v>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D45" t="n">
-        <v>531.15</v>
+        <v>1992.1</v>
       </c>
       <c r="E45" t="n">
-        <v>521.24</v>
+        <v>1947.98</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="G45" t="n">
-        <v>509.7</v>
+        <v>1903.73</v>
       </c>
       <c r="H45" t="n">
-        <v>61.84</v>
+        <v>61.25</v>
       </c>
       <c r="I45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>46233</v>
+        <v>1.8</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="K45" t="n">
-        <v>487.9</v>
+        <v>1901.3</v>
       </c>
       <c r="L45" t="n">
-        <v>8.859999999999999</v>
+        <v>4.78</v>
       </c>
       <c r="M45" t="n">
         <v>70</v>
@@ -2825,8 +4867,55 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>40.489838</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7.677307</v>
+      </c>
+      <c r="R45" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>124</v>
+      </c>
+      <c r="T45" t="n">
+        <v>12428031033344</v>
+      </c>
+      <c r="U45" t="n">
+        <v>20.151</v>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>32.573003</v>
+      </c>
+      <c r="X45" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>100.415</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="46">
@@ -2835,41 +4924,45 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>46248</v>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D46" t="n">
-        <v>4057</v>
+        <v>382.05</v>
       </c>
       <c r="E46" t="n">
-        <v>3978.76</v>
+        <v>390.64</v>
       </c>
       <c r="F46" t="n">
-        <v>1.97</v>
+        <v>-2.2</v>
       </c>
       <c r="G46" t="n">
-        <v>3998.81</v>
+        <v>384.62</v>
       </c>
       <c r="H46" t="n">
-        <v>58.6</v>
+        <v>50.89</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>46211</v>
+        <v>2.33</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
       </c>
       <c r="K46" t="n">
-        <v>3720</v>
+        <v>367.85</v>
       </c>
       <c r="L46" t="n">
-        <v>9.06</v>
+        <v>3.86</v>
       </c>
       <c r="M46" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2878,8 +4971,49 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>31.679102</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.0924454</v>
+      </c>
+      <c r="R46" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="S46" t="n">
+        <v>65</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1220779442176</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>14.453</v>
+      </c>
+      <c r="X46" t="n">
+        <v>6.0890004</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>168.051</v>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -2888,41 +5022,45 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>46248</v>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D47" t="n">
-        <v>1992.1</v>
+        <v>36750</v>
       </c>
       <c r="E47" t="n">
-        <v>1947.98</v>
+        <v>36917.68</v>
       </c>
       <c r="F47" t="n">
-        <v>2.26</v>
+        <v>-0.45</v>
       </c>
       <c r="G47" t="n">
-        <v>1903.73</v>
+        <v>39986.8</v>
       </c>
       <c r="H47" t="n">
-        <v>61.25</v>
+        <v>30.7</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J47" s="1" t="n">
-        <v>46244</v>
+        <v>3.94</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="K47" t="n">
-        <v>1901.3</v>
+        <v>36410</v>
       </c>
       <c r="L47" t="n">
-        <v>4.78</v>
+        <v>0.93</v>
       </c>
       <c r="M47" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -2931,8 +5069,55 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>54.102196</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>27.279732</v>
+      </c>
+      <c r="R47" t="n">
+        <v>679.27</v>
+      </c>
+      <c r="S47" t="n">
+        <v>157</v>
+      </c>
+      <c r="T47" t="n">
+        <v>409904873472</v>
+      </c>
+      <c r="U47" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>18.868999</v>
+      </c>
+      <c r="X47" t="n">
+        <v>14.558</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>18.422</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="48">
@@ -2941,38 +5126,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>46248</v>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D48" t="n">
-        <v>382.05</v>
+        <v>7222</v>
       </c>
       <c r="E48" t="n">
-        <v>390.64</v>
+        <v>7252.02</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.2</v>
+        <v>-0.41</v>
       </c>
       <c r="G48" t="n">
-        <v>384.62</v>
+        <v>7557.64</v>
       </c>
       <c r="H48" t="n">
-        <v>50.89</v>
+        <v>43.57</v>
       </c>
       <c r="I48" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>46198</v>
+        <v>2.54</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="K48" t="n">
-        <v>367.85</v>
+        <v>6951</v>
       </c>
       <c r="L48" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="M48" t="n">
         <v>65</v>
@@ -2984,8 +5173,53 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>143.77863</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.813523</v>
+      </c>
+      <c r="R48" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>254703812608</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5.583</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>6.243</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.4579999</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>46.566</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -2994,38 +5228,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>46248</v>
+          <t>TIMKEN</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D49" t="n">
-        <v>36750</v>
+        <v>3275.8</v>
       </c>
       <c r="E49" t="n">
-        <v>36914.43</v>
+        <v>3274.08</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.45</v>
+        <v>0.05</v>
       </c>
       <c r="G49" t="n">
-        <v>40027.4</v>
+        <v>3359.19</v>
       </c>
       <c r="H49" t="n">
-        <v>30.04</v>
+        <v>52.08</v>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>46247</v>
+        <v>0.66</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="K49" t="n">
-        <v>36410</v>
+        <v>3164.7</v>
       </c>
       <c r="L49" t="n">
-        <v>0.93</v>
+        <v>3.51</v>
       </c>
       <c r="M49" t="n">
         <v>65</v>
@@ -3037,8 +5275,49 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>57.470177</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>8.454114000000001</v>
+      </c>
+      <c r="R49" t="n">
+        <v>57</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>246401531904</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>15.506</v>
+      </c>
+      <c r="X49" t="n">
+        <v>11.8389994</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -3047,38 +5326,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>46248</v>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D50" t="n">
-        <v>7222</v>
+        <v>929</v>
       </c>
       <c r="E50" t="n">
-        <v>7246.59</v>
+        <v>919.79</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.34</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>7550.01</v>
+        <v>957.1</v>
       </c>
       <c r="H50" t="n">
-        <v>43.66</v>
+        <v>46.17</v>
       </c>
       <c r="I50" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>46244</v>
+        <v>1.11</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="K50" t="n">
-        <v>6951</v>
+        <v>879.1</v>
       </c>
       <c r="L50" t="n">
-        <v>3.9</v>
+        <v>5.68</v>
       </c>
       <c r="M50" t="n">
         <v>65</v>
@@ -3090,8 +5373,49 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>67.02742000000001</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>7.0875993</v>
+      </c>
+      <c r="R50" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="S50" t="n">
+        <v>11</v>
+      </c>
+      <c r="T50" t="n">
+        <v>701356113920</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>16.316</v>
+      </c>
+      <c r="X50" t="n">
+        <v>11.023</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -3100,38 +5424,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>46248</v>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D51" t="n">
-        <v>3275.8</v>
+        <v>101.51</v>
       </c>
       <c r="E51" t="n">
-        <v>3274.7</v>
+        <v>100.34</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03</v>
+        <v>1.17</v>
       </c>
       <c r="G51" t="n">
-        <v>3349.23</v>
+        <v>108.13</v>
       </c>
       <c r="H51" t="n">
-        <v>52.49</v>
+        <v>32.22</v>
       </c>
       <c r="I51" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>46245</v>
+        <v>0.68</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
       </c>
       <c r="K51" t="n">
-        <v>3164.7</v>
+        <v>92.3</v>
       </c>
       <c r="L51" t="n">
-        <v>3.51</v>
+        <v>9.98</v>
       </c>
       <c r="M51" t="n">
         <v>65</v>
@@ -3143,8 +5471,45 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>253.77501</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-42.687134</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>1071841673216</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>26.193002</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.1849999</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="52">
@@ -3153,38 +5518,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>46248</v>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D52" t="n">
-        <v>101.51</v>
+        <v>762.25</v>
       </c>
       <c r="E52" t="n">
-        <v>100.4</v>
+        <v>748.01</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="G52" t="n">
-        <v>108.19</v>
+        <v>782.6</v>
       </c>
       <c r="H52" t="n">
-        <v>31.86</v>
+        <v>40.86</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>46160</v>
+        <v>0.71</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
       </c>
       <c r="K52" t="n">
-        <v>92.3</v>
+        <v>720</v>
       </c>
       <c r="L52" t="n">
-        <v>9.98</v>
+        <v>5.87</v>
       </c>
       <c r="M52" t="n">
         <v>65</v>
@@ -3198,6 +5567,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
+      </c>
+      <c r="P52" t="n">
+        <v>38.910156</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>14.310254</v>
+      </c>
+      <c r="R52" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="S52" t="n">
+        <v>166</v>
+      </c>
+      <c r="T52" t="n">
+        <v>189264805888</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>40.046</v>
+      </c>
+      <c r="X52" t="n">
+        <v>31.785</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>4.863</v>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="53">
@@ -3206,38 +5616,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>46248</v>
+          <t>IGIL</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D53" t="n">
-        <v>762.25</v>
+        <v>345.9</v>
       </c>
       <c r="E53" t="n">
-        <v>748.01</v>
+        <v>338.21</v>
       </c>
       <c r="F53" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="G53" t="n">
-        <v>782.6</v>
+        <v>352.93</v>
       </c>
       <c r="H53" t="n">
-        <v>40.86</v>
+        <v>46.73</v>
       </c>
       <c r="I53" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>46183</v>
+        <v>0.26</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
       </c>
       <c r="K53" t="n">
-        <v>720</v>
+        <v>326</v>
       </c>
       <c r="L53" t="n">
-        <v>5.87</v>
+        <v>6.1</v>
       </c>
       <c r="M53" t="n">
         <v>65</v>
@@ -3251,6 +5665,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
+      </c>
+      <c r="P53" t="n">
+        <v>29.214525</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10.045888</v>
+      </c>
+      <c r="R53" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="S53" t="n">
+        <v>145</v>
+      </c>
+      <c r="T53" t="n">
+        <v>149484027904</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="n">
+        <v>56.596</v>
+      </c>
+      <c r="X53" t="n">
+        <v>44.739</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>9.593999999999999</v>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="54">
@@ -3259,41 +5714,45 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IGIL</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>46248</v>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D54" t="n">
-        <v>345.9</v>
+        <v>391.15</v>
       </c>
       <c r="E54" t="n">
-        <v>338.29</v>
+        <v>401.48</v>
       </c>
       <c r="F54" t="n">
-        <v>2.25</v>
+        <v>-2.57</v>
       </c>
       <c r="G54" t="n">
-        <v>352.63</v>
+        <v>391.15</v>
       </c>
       <c r="H54" t="n">
-        <v>46.4</v>
+        <v>51.08</v>
       </c>
       <c r="I54" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>46230</v>
+        <v>0.75</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
       </c>
       <c r="K54" t="n">
-        <v>326</v>
+        <v>368.4</v>
       </c>
       <c r="L54" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="M54" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3302,8 +5761,47 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
+          <t>within 3% of 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>19.174019</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.1468048</v>
+      </c>
+      <c r="R54" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S54" t="n">
+        <v>17</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3890559844352</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="n">
+        <v>34.761003</v>
+      </c>
+      <c r="X54" t="n">
+        <v>28.467</v>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -3312,38 +5810,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>46248</v>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D55" t="n">
-        <v>2095.3</v>
+        <v>11619</v>
       </c>
       <c r="E55" t="n">
-        <v>2111.11</v>
+        <v>11791.94</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.75</v>
+        <v>-1.47</v>
       </c>
       <c r="G55" t="n">
-        <v>2015.39</v>
+        <v>11599.76</v>
       </c>
       <c r="H55" t="n">
-        <v>57.71</v>
+        <v>43.34</v>
       </c>
       <c r="I55" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
-        <v>46239</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="K55" t="n">
-        <v>2043</v>
+        <v>11570</v>
       </c>
       <c r="L55" t="n">
-        <v>2.56</v>
+        <v>0.42</v>
       </c>
       <c r="M55" t="n">
         <v>60</v>
@@ -3355,8 +5857,49 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>40.022736</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.460094</v>
+      </c>
+      <c r="R55" t="n">
+        <v>290.31</v>
+      </c>
+      <c r="S55" t="n">
+        <v>205</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3417956941824</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>15.478</v>
+      </c>
+      <c r="X55" t="n">
+        <v>9.2930004</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>29.432</v>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="56">
@@ -3365,38 +5908,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>46248</v>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D56" t="n">
-        <v>186.82</v>
+        <v>2095.3</v>
       </c>
       <c r="E56" t="n">
-        <v>185.9</v>
+        <v>2110.01</v>
       </c>
       <c r="F56" t="n">
-        <v>0.49</v>
+        <v>-0.7</v>
       </c>
       <c r="G56" t="n">
-        <v>185.46</v>
+        <v>2019.87</v>
       </c>
       <c r="H56" t="n">
-        <v>49.53</v>
+        <v>57.65</v>
       </c>
       <c r="I56" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>45891</v>
+        <v>0.72</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="K56" t="n">
-        <v>170.1</v>
+        <v>2043</v>
       </c>
       <c r="L56" t="n">
-        <v>9.83</v>
+        <v>2.56</v>
       </c>
       <c r="M56" t="n">
         <v>60</v>
@@ -3408,8 +5955,49 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA</t>
-        </is>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>33.773373</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.9136887</v>
+      </c>
+      <c r="R56" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="S56" t="n">
+        <v>53</v>
+      </c>
+      <c r="T56" t="n">
+        <v>617058795520</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>6.771999600000001</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5.619</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>11.469</v>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -3418,38 +6006,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MGL</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>46248</v>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D57" t="n">
-        <v>1138.7</v>
+        <v>186.82</v>
       </c>
       <c r="E57" t="n">
-        <v>1117.67</v>
+        <v>185.97</v>
       </c>
       <c r="F57" t="n">
-        <v>1.88</v>
+        <v>0.46</v>
       </c>
       <c r="G57" t="n">
-        <v>1128.11</v>
+        <v>185.43</v>
       </c>
       <c r="H57" t="n">
-        <v>56.14</v>
+        <v>49.61</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>46246</v>
+        <v>0.45</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
       </c>
       <c r="K57" t="n">
-        <v>1114</v>
+        <v>170.1</v>
       </c>
       <c r="L57" t="n">
-        <v>2.22</v>
+        <v>9.83</v>
       </c>
       <c r="M57" t="n">
         <v>60</v>
@@ -3461,8 +6053,55 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>17.394787</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>9.694862000000001</v>
+      </c>
+      <c r="R57" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="S57" t="n">
+        <v>667</v>
+      </c>
+      <c r="T57" t="n">
+        <v>184787845120</v>
+      </c>
+      <c r="U57" t="n">
+        <v>56.996</v>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>24.779</v>
+      </c>
+      <c r="X57" t="n">
+        <v>17.066</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="58">
@@ -3471,38 +6110,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>46248</v>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D58" t="n">
-        <v>5580</v>
+        <v>1138.7</v>
       </c>
       <c r="E58" t="n">
-        <v>5468.01</v>
+        <v>1118.47</v>
       </c>
       <c r="F58" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="G58" t="n">
-        <v>5078.14</v>
+        <v>1127.48</v>
       </c>
       <c r="H58" t="n">
-        <v>64.52</v>
+        <v>56.06</v>
       </c>
       <c r="I58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>46240</v>
+        <v>0.78</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="K58" t="n">
-        <v>5390</v>
+        <v>1114</v>
       </c>
       <c r="L58" t="n">
-        <v>3.53</v>
+        <v>2.22</v>
       </c>
       <c r="M58" t="n">
         <v>60</v>
@@ -3516,6 +6159,47 @@
         <is>
           <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P58" t="n">
+        <v>15.7235565</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.7499615</v>
+      </c>
+      <c r="R58" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="S58" t="n">
+        <v>322</v>
+      </c>
+      <c r="T58" t="n">
+        <v>112478248960</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>9.854999000000001</v>
+      </c>
+      <c r="X58" t="n">
+        <v>8.382000000000001</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>3.461</v>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -3524,41 +6208,45 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>46248</v>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D59" t="n">
-        <v>152.39</v>
+        <v>5580</v>
       </c>
       <c r="E59" t="n">
-        <v>155.77</v>
+        <v>5469.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.17</v>
+        <v>2.02</v>
       </c>
       <c r="G59" t="n">
-        <v>167.55</v>
+        <v>5067.93</v>
       </c>
       <c r="H59" t="n">
-        <v>35.7</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>46248</v>
+        <v>1.13</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="K59" t="n">
-        <v>152</v>
+        <v>5390</v>
       </c>
       <c r="L59" t="n">
-        <v>0.26</v>
+        <v>3.53</v>
       </c>
       <c r="M59" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3567,8 +6255,49 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>45.71522</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>11.137925</v>
+      </c>
+      <c r="R59" t="n">
+        <v>122.06</v>
+      </c>
+      <c r="S59" t="n">
+        <v>65</v>
+      </c>
+      <c r="T59" t="n">
+        <v>871769178112</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="n">
+        <v>13.516</v>
+      </c>
+      <c r="X59" t="n">
+        <v>12.236</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>6.092</v>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="60">
@@ -3577,38 +6306,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TARIL</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>46248</v>
+          <t>SAMMAANCAP</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D60" t="n">
-        <v>298.05</v>
+        <v>152.39</v>
       </c>
       <c r="E60" t="n">
-        <v>302.2</v>
+        <v>155.77</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.37</v>
+        <v>-2.17</v>
       </c>
       <c r="G60" t="n">
-        <v>320.01</v>
+        <v>167.55</v>
       </c>
       <c r="H60" t="n">
-        <v>42.97</v>
+        <v>35.7</v>
       </c>
       <c r="I60" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J60" s="1" t="n">
-        <v>46224</v>
+        <v>3.25</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K60" t="n">
-        <v>288.1</v>
+        <v>152</v>
       </c>
       <c r="L60" t="n">
-        <v>3.45</v>
+        <v>0.26</v>
       </c>
       <c r="M60" t="n">
         <v>55</v>
@@ -3622,6 +6355,43 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="n">
+        <v>0.6559713</v>
+      </c>
+      <c r="R60" t="n">
+        <v>-89.77</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>175048392704</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="n">
+        <v>93.80199999999999</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>273.033</v>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>-52.90000000000001</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3630,38 +6400,42 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>46248</v>
+          <t>TARIL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D61" t="n">
-        <v>413.5</v>
+        <v>298.05</v>
       </c>
       <c r="E61" t="n">
-        <v>419.17</v>
+        <v>302.2</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
       <c r="G61" t="n">
-        <v>421.36</v>
+        <v>320.01</v>
       </c>
       <c r="H61" t="n">
-        <v>48.92</v>
+        <v>42.97</v>
       </c>
       <c r="I61" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J61" s="1" t="n">
-        <v>46238</v>
+        <v>2.28</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
       <c r="K61" t="n">
-        <v>385.9</v>
+        <v>288.1</v>
       </c>
       <c r="L61" t="n">
-        <v>7.15</v>
+        <v>3.45</v>
       </c>
       <c r="M61" t="n">
         <v>55</v>
@@ -3673,8 +6447,49 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>34.616726</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5.778402</v>
+      </c>
+      <c r="R61" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="S61" t="n">
+        <v>6</v>
+      </c>
+      <c r="T61" t="n">
+        <v>89464422400</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>15.117</v>
+      </c>
+      <c r="X61" t="n">
+        <v>10.132</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>29.595</v>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -3683,38 +6498,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>46248</v>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D62" t="n">
-        <v>1718.1</v>
+        <v>413.5</v>
       </c>
       <c r="E62" t="n">
-        <v>1730.7</v>
+        <v>419.17</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.73</v>
+        <v>-1.35</v>
       </c>
       <c r="G62" t="n">
-        <v>1863.63</v>
+        <v>421.36</v>
       </c>
       <c r="H62" t="n">
-        <v>37.48</v>
+        <v>48.92</v>
       </c>
       <c r="I62" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J62" s="1" t="n">
-        <v>46248</v>
+        <v>0.91</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="K62" t="n">
-        <v>1714.4</v>
+        <v>385.9</v>
       </c>
       <c r="L62" t="n">
-        <v>0.22</v>
+        <v>7.15</v>
       </c>
       <c r="M62" t="n">
         <v>55</v>
@@ -3726,8 +6545,49 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>8.708930000000001</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.9618435</v>
+      </c>
+      <c r="R62" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="S62" t="n">
+        <v>243</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2615386570752</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="X62" t="n">
+        <v>6.515</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="63">
@@ -3739,29 +6599,33 @@
           <t>AAVAS</t>
         </is>
       </c>
-      <c r="C63" s="1" t="n">
-        <v>46248</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D63" t="n">
         <v>1397.4</v>
       </c>
       <c r="E63" t="n">
-        <v>1406.72</v>
+        <v>1408.24</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.66</v>
+        <v>-0.77</v>
       </c>
       <c r="G63" t="n">
-        <v>1434.81</v>
+        <v>1433.57</v>
       </c>
       <c r="H63" t="n">
-        <v>46.82</v>
+        <v>46.45</v>
       </c>
       <c r="I63" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J63" s="1" t="n">
-        <v>46248</v>
+        <v>0.6</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K63" t="n">
         <v>1385.2</v>
@@ -3781,6 +6645,45 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P63" t="n">
+        <v>16.611982</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.1909964</v>
+      </c>
+      <c r="R63" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>110799880192</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="n">
+        <v>54.527</v>
+      </c>
+      <c r="X63" t="n">
+        <v>42.543998</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>310.553</v>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="64">
@@ -3789,35 +6692,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>46248</v>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D64" t="n">
-        <v>2235</v>
+        <v>1718.1</v>
       </c>
       <c r="E64" t="n">
-        <v>2245.45</v>
+        <v>1730.7</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.47</v>
+        <v>-0.73</v>
       </c>
       <c r="G64" t="n">
-        <v>2381.35</v>
+        <v>1863.63</v>
       </c>
       <c r="H64" t="n">
-        <v>29.9</v>
+        <v>37.48</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>46248</v>
+        <v>0.75</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K64" t="n">
-        <v>2230.1</v>
+        <v>1714.4</v>
       </c>
       <c r="L64" t="n">
         <v>0.22</v>
@@ -3834,6 +6741,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P64" t="n">
+        <v>53.19195</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>14.205161</v>
+      </c>
+      <c r="R64" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="S64" t="n">
+        <v>100</v>
+      </c>
+      <c r="T64" t="n">
+        <v>489687252992</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="n">
+        <v>7.454</v>
+      </c>
+      <c r="X64" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>335.854</v>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -3842,38 +6790,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>46248</v>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D65" t="n">
-        <v>17.39</v>
+        <v>2235</v>
       </c>
       <c r="E65" t="n">
-        <v>17.35</v>
+        <v>2242.97</v>
       </c>
       <c r="F65" t="n">
-        <v>0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="G65" t="n">
-        <v>17.68</v>
+        <v>2378.4</v>
       </c>
       <c r="H65" t="n">
-        <v>44.93</v>
+        <v>30.68</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J65" s="1" t="n">
-        <v>46225</v>
+        <v>0.5</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K65" t="n">
-        <v>16.75</v>
+        <v>2230.1</v>
       </c>
       <c r="L65" t="n">
-        <v>3.82</v>
+        <v>0.22</v>
       </c>
       <c r="M65" t="n">
         <v>55</v>
@@ -3887,6 +6839,47 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P65" t="n">
+        <v>18.656094</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>4.5517774</v>
+      </c>
+      <c r="R65" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="S65" t="n">
+        <v>80</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1021919952896</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="n">
+        <v>25.354</v>
+      </c>
+      <c r="X65" t="n">
+        <v>18.450001</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>29.388</v>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -3895,38 +6888,42 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JBMA</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>46248</v>
+          <t>JPPOWER</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D66" t="n">
-        <v>622.95</v>
+        <v>17.39</v>
       </c>
       <c r="E66" t="n">
-        <v>618.67</v>
+        <v>17.35</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="G66" t="n">
-        <v>675.37</v>
+        <v>17.68</v>
       </c>
       <c r="H66" t="n">
-        <v>34.35</v>
+        <v>44.93</v>
       </c>
       <c r="I66" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
-        <v>46136</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="K66" t="n">
-        <v>606.65</v>
+        <v>16.75</v>
       </c>
       <c r="L66" t="n">
-        <v>2.69</v>
+        <v>3.82</v>
       </c>
       <c r="M66" t="n">
         <v>55</v>
@@ -3940,6 +6937,45 @@
         <is>
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P66" t="n">
+        <v>25.202898</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.3351247</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="n">
+        <v>119181647872</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="n">
+        <v>36.141</v>
+      </c>
+      <c r="X66" t="n">
+        <v>11.1420006</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>26.634</v>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="67">
@@ -3948,38 +6984,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MMTC</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>46248</v>
+          <t>JBMA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>64.34999999999999</v>
+        <v>622.95</v>
       </c>
       <c r="E67" t="n">
-        <v>63.43</v>
+        <v>618.66</v>
       </c>
       <c r="F67" t="n">
-        <v>1.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>66</v>
+        <v>675.8</v>
       </c>
       <c r="H67" t="n">
-        <v>51.7</v>
+        <v>34.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J67" s="1" t="n">
-        <v>46220</v>
+        <v>0.6</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
       </c>
       <c r="K67" t="n">
-        <v>59.9</v>
+        <v>606.65</v>
       </c>
       <c r="L67" t="n">
-        <v>7.43</v>
+        <v>2.69</v>
       </c>
       <c r="M67" t="n">
         <v>55</v>
@@ -3991,8 +7031,49 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>66.697</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>12.903393</v>
+      </c>
+      <c r="R67" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="S67" t="n">
+        <v>13</v>
+      </c>
+      <c r="T67" t="n">
+        <v>147324108800</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="n">
+        <v>8.273999999999999</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3.571</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>190.282</v>
+      </c>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="68">
@@ -4001,38 +7082,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GRSE</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>46248</v>
+          <t>MMTC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D68" t="n">
-        <v>2618.6</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>2574.51</v>
+        <v>63.45</v>
       </c>
       <c r="F68" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="G68" t="n">
-        <v>2652.61</v>
+        <v>66.11</v>
       </c>
       <c r="H68" t="n">
-        <v>51.05</v>
+        <v>51.35</v>
       </c>
       <c r="I68" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J68" s="1" t="n">
-        <v>46238</v>
+        <v>0.97</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
       </c>
       <c r="K68" t="n">
-        <v>2471.7</v>
+        <v>59.9</v>
       </c>
       <c r="L68" t="n">
-        <v>5.94</v>
+        <v>7.43</v>
       </c>
       <c r="M68" t="n">
         <v>55</v>
@@ -4046,6 +7131,45 @@
         <is>
           <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
+      </c>
+      <c r="P68" t="n">
+        <v>21.521738</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4.552851</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="n">
+        <v>96525000704</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="n">
+        <v>85.238</v>
+      </c>
+      <c r="X68" t="n">
+        <v>573.759</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>10644.1</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="69">
@@ -4054,38 +7178,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>46248</v>
+          <t>GRSE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D69" t="n">
-        <v>498.2</v>
+        <v>2618.6</v>
       </c>
       <c r="E69" t="n">
-        <v>486.35</v>
+        <v>2574.51</v>
       </c>
       <c r="F69" t="n">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="G69" t="n">
-        <v>506.04</v>
+        <v>2652.61</v>
       </c>
       <c r="H69" t="n">
-        <v>45.65</v>
+        <v>51.05</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J69" s="1" t="n">
-        <v>46191</v>
+        <v>0.93</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="K69" t="n">
-        <v>481.75</v>
+        <v>2471.7</v>
       </c>
       <c r="L69" t="n">
-        <v>3.41</v>
+        <v>5.94</v>
       </c>
       <c r="M69" t="n">
         <v>55</v>
@@ -4097,8 +7225,49 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>37.451374</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>11.421667</v>
+      </c>
+      <c r="R69" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="S69" t="n">
+        <v>102</v>
+      </c>
+      <c r="T69" t="n">
+        <v>299965874176</v>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="X69" t="n">
+        <v>10.665</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="70">
@@ -4107,51 +7276,94 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>46248</v>
+          <t>AADHARHFC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D70" t="n">
-        <v>1091.5</v>
+        <v>498.2</v>
       </c>
       <c r="E70" t="n">
-        <v>1122.84</v>
+        <v>486.42</v>
       </c>
       <c r="F70" t="n">
-        <v>-2.79</v>
+        <v>2.42</v>
       </c>
       <c r="G70" t="n">
-        <v>1082.14</v>
+        <v>505.47</v>
       </c>
       <c r="H70" t="n">
-        <v>50.85</v>
+        <v>45.58</v>
       </c>
       <c r="I70" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J70" s="1" t="n">
-        <v>46245</v>
+        <v>0.51</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
       </c>
       <c r="K70" t="n">
-        <v>1086</v>
+        <v>481.75</v>
       </c>
       <c r="L70" t="n">
-        <v>0.51</v>
+        <v>3.41</v>
       </c>
       <c r="M70" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>NEAR 200DMA</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>19.340063</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.8785374</v>
+      </c>
+      <c r="R70" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="n">
+        <v>218080821248</v>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="n">
+        <v>61.72299999999999</v>
+      </c>
+      <c r="X70" t="n">
+        <v>48.151</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>255.574</v>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="71">
@@ -4160,38 +7372,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>46248</v>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D71" t="n">
-        <v>84.40000000000001</v>
+        <v>1091.5</v>
       </c>
       <c r="E71" t="n">
-        <v>82.89</v>
+        <v>1122.7</v>
       </c>
       <c r="F71" t="n">
-        <v>1.82</v>
+        <v>-2.78</v>
       </c>
       <c r="G71" t="n">
-        <v>85.59</v>
+        <v>1083.72</v>
       </c>
       <c r="H71" t="n">
-        <v>46.45</v>
+        <v>51.16</v>
       </c>
       <c r="I71" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J71" s="1" t="n">
-        <v>46104</v>
+        <v>0.53</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="K71" t="n">
-        <v>74.55</v>
+        <v>1086</v>
       </c>
       <c r="L71" t="n">
-        <v>13.21</v>
+        <v>0.51</v>
       </c>
       <c r="M71" t="n">
         <v>50</v>
@@ -4203,8 +7419,49 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%</t>
-        </is>
+          <t>within 3% of 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>40.83427</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.1815078</v>
+      </c>
+      <c r="R71" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="S71" t="n">
+        <v>18</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1110588260352</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="n">
+        <v>11.1999996</v>
+      </c>
+      <c r="X71" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>43.613</v>
+      </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="72">
@@ -4213,41 +7470,45 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>46248</v>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D72" t="n">
-        <v>1559.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>1605.01</v>
+        <v>82.89</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.85</v>
+        <v>1.82</v>
       </c>
       <c r="G72" t="n">
-        <v>1629.43</v>
+        <v>85.59</v>
       </c>
       <c r="H72" t="n">
-        <v>42.42</v>
+        <v>46.45</v>
       </c>
       <c r="I72" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J72" s="1" t="n">
-        <v>46237</v>
+        <v>1.12</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
       </c>
       <c r="K72" t="n">
-        <v>1506.7</v>
+        <v>74.55</v>
       </c>
       <c r="L72" t="n">
-        <v>3.48</v>
+        <v>13.21</v>
       </c>
       <c r="M72" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -4256,8 +7517,55 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>at/above 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10.035672</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.1744733</v>
+      </c>
+      <c r="R72" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="S72" t="n">
+        <v>412</v>
+      </c>
+      <c r="T72" t="n">
+        <v>742029393920</v>
+      </c>
+      <c r="U72" t="n">
+        <v>23.363</v>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>21.968001</v>
+      </c>
+      <c r="X72" t="n">
+        <v>23.231001</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>18.802</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="73">
@@ -4266,38 +7574,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>46248</v>
+          <t>ONESOURCE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D73" t="n">
-        <v>391.15</v>
+        <v>1559.2</v>
       </c>
       <c r="E73" t="n">
-        <v>401.27</v>
+        <v>1606.09</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.52</v>
+        <v>-2.92</v>
       </c>
       <c r="G73" t="n">
-        <v>391.41</v>
+        <v>1632.83</v>
       </c>
       <c r="H73" t="n">
-        <v>50.97</v>
+        <v>42.46</v>
       </c>
       <c r="I73" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J73" s="1" t="n">
-        <v>46202</v>
+        <v>0.97</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
       </c>
       <c r="K73" t="n">
-        <v>368.4</v>
+        <v>1506.7</v>
       </c>
       <c r="L73" t="n">
-        <v>6.18</v>
+        <v>3.48</v>
       </c>
       <c r="M73" t="n">
         <v>45</v>
@@ -4309,8 +7621,41 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>3.0729208</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="n">
+        <v>178797969408</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="n">
+        <v>11.492</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>25.791</v>
+      </c>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="74">
@@ -4319,35 +7664,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="n">
-        <v>46248</v>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D74" t="n">
-        <v>275.4</v>
+        <v>1284.5</v>
       </c>
       <c r="E74" t="n">
-        <v>281.91</v>
+        <v>1318.87</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.31</v>
+        <v>-2.61</v>
       </c>
       <c r="G74" t="n">
-        <v>305.75</v>
+        <v>1405.23</v>
       </c>
       <c r="H74" t="n">
-        <v>31.51</v>
+        <v>34.87</v>
       </c>
       <c r="I74" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J74" s="1" t="n">
-        <v>46246</v>
+        <v>0.51</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
       </c>
       <c r="K74" t="n">
-        <v>271.65</v>
+        <v>1267</v>
       </c>
       <c r="L74" t="n">
         <v>1.38</v>
@@ -4364,6 +7713,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P74" t="n">
+        <v>4.903233</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.081117</v>
+      </c>
+      <c r="R74" t="n">
+        <v>261.97</v>
+      </c>
+      <c r="S74" t="n">
+        <v>443</v>
+      </c>
+      <c r="T74" t="n">
+        <v>183387652096</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="n">
+        <v>54.431</v>
+      </c>
+      <c r="X74" t="n">
+        <v>60.307</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>6.409</v>
+      </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="75">
@@ -4372,38 +7762,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HDBFS</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>46248</v>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D75" t="n">
-        <v>686.95</v>
+        <v>275.4</v>
       </c>
       <c r="E75" t="n">
-        <v>702.47</v>
+        <v>281.72</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.21</v>
+        <v>-2.24</v>
       </c>
       <c r="G75" t="n">
-        <v>705.49</v>
+        <v>306.53</v>
       </c>
       <c r="H75" t="n">
-        <v>45.48</v>
+        <v>32.01</v>
       </c>
       <c r="I75" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J75" s="1" t="n">
-        <v>46225</v>
+        <v>0.58</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="K75" t="n">
-        <v>657</v>
+        <v>271.65</v>
       </c>
       <c r="L75" t="n">
-        <v>4.56</v>
+        <v>1.38</v>
       </c>
       <c r="M75" t="n">
         <v>45</v>
@@ -4417,6 +7811,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P75" t="n">
+        <v>11.590909</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1.7740043</v>
+      </c>
+      <c r="R75" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="S75" t="n">
+        <v>262</v>
+      </c>
+      <c r="T75" t="n">
+        <v>381879746560</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="n">
+        <v>28.304002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>17.458001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="76">
@@ -4425,38 +7860,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>46248</v>
+          <t>HDBFS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D76" t="n">
-        <v>667.3</v>
+        <v>686.95</v>
       </c>
       <c r="E76" t="n">
-        <v>681.6799999999999</v>
+        <v>702.47</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.11</v>
+        <v>-2.21</v>
       </c>
       <c r="G76" t="n">
-        <v>670.1799999999999</v>
+        <v>705.49</v>
       </c>
       <c r="H76" t="n">
-        <v>47.2</v>
+        <v>45.48</v>
       </c>
       <c r="I76" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J76" s="1" t="n">
-        <v>46246</v>
+        <v>0.52</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="K76" t="n">
-        <v>664.2</v>
+        <v>657</v>
       </c>
       <c r="L76" t="n">
-        <v>0.47</v>
+        <v>4.56</v>
       </c>
       <c r="M76" t="n">
         <v>45</v>
@@ -4470,6 +7909,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P76" t="n">
+        <v>20.555058</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.760321</v>
+      </c>
+      <c r="R76" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="S76" t="n">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="T76" t="n">
+        <v>569106890752</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="n">
+        <v>42.416</v>
+      </c>
+      <c r="X76" t="n">
+        <v>29.786</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>484.313</v>
+      </c>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="77">
@@ -4481,8 +7961,10 @@
           <t>GMDCLTD</t>
         </is>
       </c>
-      <c r="C77" s="1" t="n">
-        <v>46248</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D77" t="n">
         <v>580.8</v>
@@ -4502,8 +7984,10 @@
       <c r="I77" t="n">
         <v>0.66</v>
       </c>
-      <c r="J77" s="1" t="n">
-        <v>46248</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="K77" t="n">
         <v>578.5</v>
@@ -4523,6 +8007,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P77" t="n">
+        <v>19.721561</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.6128383</v>
+      </c>
+      <c r="R77" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="S77" t="n">
+        <v>170</v>
+      </c>
+      <c r="T77" t="n">
+        <v>184694390784</v>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="n">
+        <v>17.395</v>
+      </c>
+      <c r="X77" t="n">
+        <v>33.823</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>4.475</v>
+      </c>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -4531,38 +8056,42 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>46247</v>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D78" t="n">
-        <v>906.15</v>
+        <v>1832.6</v>
       </c>
       <c r="E78" t="n">
-        <v>921.34</v>
+        <v>1856.59</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.65</v>
+        <v>-1.29</v>
       </c>
       <c r="G78" t="n">
-        <v>956.5</v>
+        <v>1947.77</v>
       </c>
       <c r="H78" t="n">
-        <v>38.14</v>
+        <v>34.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J78" s="1" t="n">
-        <v>46246</v>
+        <v>0.6</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="K78" t="n">
-        <v>879.1</v>
+        <v>1815</v>
       </c>
       <c r="L78" t="n">
-        <v>3.08</v>
+        <v>0.97</v>
       </c>
       <c r="M78" t="n">
         <v>45</v>
@@ -4576,6 +8105,47 @@
         <is>
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
+      </c>
+      <c r="P78" t="n">
+        <v>45.249382</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>8.203222999999999</v>
+      </c>
+      <c r="R78" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="n">
+        <v>372200767488</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="n">
+        <v>12.839</v>
+      </c>
+      <c r="X78" t="n">
+        <v>8.984</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>129.033</v>
+      </c>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="79">
@@ -4584,41 +8154,45 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>46248</v>
+          <t>NAVA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D79" t="n">
-        <v>11619</v>
+        <v>572.65</v>
       </c>
       <c r="E79" t="n">
-        <v>11791.8</v>
+        <v>586.21</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.47</v>
+        <v>-2.31</v>
       </c>
       <c r="G79" t="n">
-        <v>11619.58</v>
+        <v>590.52</v>
       </c>
       <c r="H79" t="n">
-        <v>42.89</v>
+        <v>46.52</v>
       </c>
       <c r="I79" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J79" s="1" t="n">
-        <v>46247</v>
+        <v>3.63</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="K79" t="n">
-        <v>11570</v>
+        <v>560.5</v>
       </c>
       <c r="L79" t="n">
-        <v>0.42</v>
+        <v>2.17</v>
       </c>
       <c r="M79" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -4627,8 +8201,55 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>20.569326</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.8531164</v>
+      </c>
+      <c r="R79" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="S79" t="n">
+        <v>144</v>
+      </c>
+      <c r="T79" t="n">
+        <v>162278129664</v>
+      </c>
+      <c r="U79" t="n">
+        <v>10.309</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="n">
+        <v>25.088</v>
+      </c>
+      <c r="X79" t="n">
+        <v>18.333</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>20.684</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>6.018</v>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="80">
@@ -4637,41 +8258,45 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>46248</v>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D80" t="n">
-        <v>1832.6</v>
+        <v>2733.5</v>
       </c>
       <c r="E80" t="n">
-        <v>1857.86</v>
+        <v>2779.47</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.36</v>
+        <v>-1.65</v>
       </c>
       <c r="G80" t="n">
-        <v>1948.97</v>
+        <v>2960.46</v>
       </c>
       <c r="H80" t="n">
-        <v>33.18</v>
+        <v>40.61</v>
       </c>
       <c r="I80" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J80" s="1" t="n">
-        <v>46244</v>
+        <v>1.65</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
       </c>
       <c r="K80" t="n">
-        <v>1815</v>
+        <v>2685</v>
       </c>
       <c r="L80" t="n">
-        <v>0.97</v>
+        <v>1.81</v>
       </c>
       <c r="M80" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -4680,8 +8305,49 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>83.33842</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>6.825559</v>
+      </c>
+      <c r="R80" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="S80" t="n">
+        <v>16</v>
+      </c>
+      <c r="T80" t="n">
+        <v>529129930752</v>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>7.277</v>
+      </c>
+      <c r="X80" t="n">
+        <v>2.8169999</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>27.724</v>
+      </c>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="81">
@@ -4690,41 +8356,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GESHIP</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>46247</v>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D81" t="n">
-        <v>1298.8</v>
+        <v>174.55</v>
       </c>
       <c r="E81" t="n">
-        <v>1315.89</v>
+        <v>172.91</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.3</v>
+        <v>0.95</v>
       </c>
       <c r="G81" t="n">
-        <v>1411.24</v>
+        <v>194.58</v>
       </c>
       <c r="H81" t="n">
-        <v>36.75</v>
+        <v>40.52</v>
       </c>
       <c r="I81" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J81" s="1" t="n">
-        <v>46245</v>
+        <v>0.13</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
       </c>
       <c r="K81" t="n">
-        <v>1267</v>
+        <v>171</v>
       </c>
       <c r="L81" t="n">
-        <v>2.51</v>
+        <v>2.08</v>
       </c>
       <c r="M81" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -4733,8 +8403,47 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
+          <t>at/above 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>20.954382</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.0980474</v>
+      </c>
+      <c r="R81" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="S81" t="n">
+        <v>85</v>
+      </c>
+      <c r="T81" t="n">
+        <v>281219530752</v>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="n">
+        <v>23.771</v>
+      </c>
+      <c r="X81" t="n">
+        <v>13.617</v>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="82">
@@ -4743,38 +8452,42 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NAVA</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>46248</v>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D82" t="n">
-        <v>572.65</v>
+        <v>208.64</v>
       </c>
       <c r="E82" t="n">
-        <v>586.5599999999999</v>
+        <v>203.14</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.37</v>
+        <v>2.71</v>
       </c>
       <c r="G82" t="n">
-        <v>591.72</v>
+        <v>211.78</v>
       </c>
       <c r="H82" t="n">
-        <v>46.03</v>
+        <v>45.38</v>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J82" s="1" t="n">
-        <v>46247</v>
+        <v>0.34</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
       </c>
       <c r="K82" t="n">
-        <v>560.5</v>
+        <v>200.74</v>
       </c>
       <c r="L82" t="n">
-        <v>2.17</v>
+        <v>3.94</v>
       </c>
       <c r="M82" t="n">
         <v>35</v>
@@ -4786,8 +8499,47 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
+          <t>at/above 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>14.744877</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.9565442</v>
+      </c>
+      <c r="R82" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="S82" t="n">
+        <v>96</v>
+      </c>
+      <c r="T82" t="n">
+        <v>206717861888</v>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="n">
+        <v>50.985</v>
+      </c>
+      <c r="X82" t="n">
+        <v>37.791002</v>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="83">
@@ -4796,41 +8548,45 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="n">
-        <v>46248</v>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D83" t="n">
-        <v>2733.5</v>
+        <v>442.7</v>
       </c>
       <c r="E83" t="n">
-        <v>2780.66</v>
+        <v>452.25</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.7</v>
+        <v>-2.11</v>
       </c>
       <c r="G83" t="n">
-        <v>2965.3</v>
+        <v>459.79</v>
       </c>
       <c r="H83" t="n">
-        <v>40.55</v>
+        <v>42.83</v>
       </c>
       <c r="I83" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J83" s="1" t="n">
-        <v>46247</v>
+        <v>0.51</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="K83" t="n">
-        <v>2685</v>
+        <v>441.35</v>
       </c>
       <c r="L83" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
       <c r="M83" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4839,8 +8595,49 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>9.207571</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.7019919</v>
+      </c>
+      <c r="R83" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="S83" t="n">
+        <v>271</v>
+      </c>
+      <c r="T83" t="n">
+        <v>177368776704</v>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="n">
+        <v>15.151</v>
+      </c>
+      <c r="X83" t="n">
+        <v>9.581000000000001</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>10.274</v>
+      </c>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="84">
@@ -4849,41 +8646,45 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>46248</v>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D84" t="n">
-        <v>174.55</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>172.91</v>
+        <v>78.41</v>
       </c>
       <c r="F84" t="n">
-        <v>0.95</v>
+        <v>-1.93</v>
       </c>
       <c r="G84" t="n">
-        <v>194.58</v>
+        <v>78.06</v>
       </c>
       <c r="H84" t="n">
-        <v>40.52</v>
+        <v>42.14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J84" s="1" t="n">
-        <v>46244</v>
+        <v>0.28</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
       </c>
       <c r="K84" t="n">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="L84" t="n">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="M84" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4892,8 +8693,49 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
-        </is>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>28.168499</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.8688183</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S84" t="n">
+        <v>209</v>
+      </c>
+      <c r="T84" t="n">
+        <v>772463198208</v>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="n">
+        <v>46.019</v>
+      </c>
+      <c r="X84" t="n">
+        <v>31.094998</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>113.111</v>
+      </c>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="85">
@@ -4902,41 +8744,45 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CUB</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>46248</v>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
       </c>
       <c r="D85" t="n">
-        <v>208.64</v>
+        <v>667.3</v>
       </c>
       <c r="E85" t="n">
-        <v>203.14</v>
+        <v>679.91</v>
       </c>
       <c r="F85" t="n">
-        <v>2.71</v>
+        <v>-1.86</v>
       </c>
       <c r="G85" t="n">
-        <v>211.78</v>
+        <v>669.54</v>
       </c>
       <c r="H85" t="n">
-        <v>45.38</v>
+        <v>47.49</v>
       </c>
       <c r="I85" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J85" s="1" t="n">
-        <v>46238</v>
+        <v>0.33</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
       </c>
       <c r="K85" t="n">
-        <v>200.74</v>
+        <v>664.2</v>
       </c>
       <c r="L85" t="n">
-        <v>3.94</v>
+        <v>0.47</v>
       </c>
       <c r="M85" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -4945,114 +8791,49 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D86" t="n">
-        <v>442.7</v>
-      </c>
-      <c r="E86" t="n">
-        <v>452.01</v>
-      </c>
-      <c r="F86" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="G86" t="n">
-        <v>459.21</v>
-      </c>
-      <c r="H86" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J86" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="K86" t="n">
-        <v>441.35</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M86" t="n">
-        <v>25</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>NEAR 200DMA</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
           <t>within 3% of 200DMA; above breakdown low</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D87" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E87" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="G87" t="n">
-        <v>78.06</v>
-      </c>
-      <c r="H87" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J87" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="K87" t="n">
-        <v>76</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M87" t="n">
-        <v>25</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>NEAR 200DMA</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
-        </is>
+      <c r="P85" t="n">
+        <v>79.34601600000001</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.1554037</v>
+      </c>
+      <c r="R85" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="S85" t="n">
+        <v>50</v>
+      </c>
+      <c r="T85" t="n">
+        <v>337622401024</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="n">
+        <v>91.65100000000001</v>
+      </c>
+      <c r="X85" t="n">
+        <v>105.248</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>4.100000000000001</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/NSE_200DMA_Recovery_Scanner.xlsx
+++ b/output/NSE_200DMA_Recovery_Scanner.xlsx
@@ -644,7 +644,7 @@
         <v>81.13</v>
       </c>
       <c r="S2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T2" t="n">
         <v>452271374336</v>
@@ -742,7 +742,7 @@
         <v>17.08</v>
       </c>
       <c r="S3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="T3" t="n">
         <v>114452561920</v>
@@ -831,51 +831,45 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>29.091524</v>
+        <v>28.993242</v>
       </c>
       <c r="Q4" t="n">
         <v>7.079106</v>
       </c>
       <c r="R4" t="n">
-        <v>5.9</v>
+        <v>5.92</v>
       </c>
       <c r="S4" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="T4" t="n">
         <v>1008188391424</v>
       </c>
-      <c r="U4" t="n">
-        <v>21.639</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>19.485001</v>
+        <v>19.645001</v>
       </c>
       <c r="X4" t="n">
-        <v>6.158</v>
+        <v>6.021</v>
       </c>
       <c r="Y4" t="n">
         <v>344.737</v>
       </c>
-      <c r="Z4" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.626</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>17.4</v>
+        <v>11.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.5</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>24.5</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -1029,13 +1023,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>122.41681</v>
+        <v>98.03646000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>12.074311</v>
       </c>
       <c r="R6" t="n">
-        <v>11.42</v>
+        <v>14.26</v>
       </c>
       <c r="S6" t="n">
         <v>37</v>
@@ -1142,7 +1136,7 @@
         <v>36.48</v>
       </c>
       <c r="S7" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="T7" t="n">
         <v>810549968896</v>
@@ -1335,13 +1329,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.438168</v>
+        <v>58.479492</v>
       </c>
       <c r="Q9" t="n">
         <v>9.402361000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
@@ -1529,13 +1523,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.17379</v>
+        <v>37.4601</v>
       </c>
       <c r="Q11" t="n">
         <v>5.515607</v>
       </c>
       <c r="R11" t="n">
-        <v>21.52</v>
+        <v>21.93</v>
       </c>
       <c r="S11" t="n">
         <v>72</v>
@@ -1734,7 +1728,7 @@
         <v>28.04</v>
       </c>
       <c r="S13" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="T13" t="n">
         <v>423900053504</v>
@@ -1823,16 +1817,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9.728465</v>
+        <v>9.516741</v>
       </c>
       <c r="Q14" t="n">
         <v>2.097534</v>
       </c>
       <c r="R14" t="n">
-        <v>17.53</v>
+        <v>17.92</v>
       </c>
       <c r="S14" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="T14" t="n">
         <v>298888200192</v>
@@ -1917,13 +1911,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.460342</v>
+        <v>16.472553</v>
       </c>
       <c r="Q15" t="n">
         <v>1.6806881</v>
       </c>
       <c r="R15" t="n">
-        <v>26.98</v>
+        <v>26.96</v>
       </c>
       <c r="S15" t="n">
         <v>248</v>
@@ -2322,7 +2316,7 @@
         <v>108.37</v>
       </c>
       <c r="S19" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T19" t="n">
         <v>1338745946112</v>
@@ -2411,13 +2405,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>18.755718</v>
+        <v>18.760487</v>
       </c>
       <c r="Q20" t="n">
         <v>13.507057</v>
       </c>
       <c r="R20" t="n">
-        <v>39.34</v>
+        <v>39.33</v>
       </c>
       <c r="S20" t="n">
         <v>54</v>
@@ -2606,47 +2600,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>5.337037</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.7214199</v>
-      </c>
-      <c r="R22" t="n">
-        <v>27</v>
-      </c>
-      <c r="S22" t="n">
-        <v>323</v>
-      </c>
-      <c r="T22" t="n">
-        <v>656039411712</v>
-      </c>
-      <c r="U22" t="n">
-        <v>13.697</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
-        <v>48.535</v>
-      </c>
-      <c r="X22" t="n">
-        <v>34.992</v>
-      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>80.30000000000001</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>80.30000000000001</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>84</v>
-      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2704,47 +2674,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>48.788597</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>12.517901</v>
-      </c>
-      <c r="R23" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3002857160704</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="n">
-        <v>22.135</v>
-      </c>
-      <c r="X23" t="n">
-        <v>21.403</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.273</v>
-      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>76</v>
-      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2802,45 +2748,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>160.23636</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.3186584</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="n">
-        <v>168591523840</v>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="n">
-        <v>-11.457</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.961</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>9.928000000000001</v>
-      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="n">
-        <v>-23.1</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-96.8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-96.8</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>8</v>
-      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2898,47 +2822,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
         </is>
       </c>
-      <c r="P25" t="n">
-        <v>25.438437</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.9687612</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="S25" t="n">
-        <v>249</v>
-      </c>
-      <c r="T25" t="n">
-        <v>106242269184</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="n">
-        <v>18.431</v>
-      </c>
-      <c r="X25" t="n">
-        <v>16.983</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.236</v>
-      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>64</v>
-      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2996,47 +2896,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>54.039127</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.0853057</v>
-      </c>
-      <c r="R26" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>21</v>
-      </c>
-      <c r="T26" t="n">
-        <v>239427633152</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="n">
-        <v>17.254</v>
-      </c>
-      <c r="X26" t="n">
-        <v>8.457000000000001</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>55.868</v>
-      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>153.2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>153.2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>42</v>
-      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3095,44 +2971,22 @@
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>4.1930685</v>
-      </c>
-      <c r="R27" t="n">
-        <v>-31.78</v>
-      </c>
-      <c r="S27" t="n">
-        <v>18</v>
-      </c>
-      <c r="T27" t="n">
-        <v>155129659392</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-8.911</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="n">
-        <v>-186.002</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-24.914</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>152.371</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.437</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.252</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="n">
-        <v>12</v>
-      </c>
+      <c r="AF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3190,45 +3044,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>86.733604</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>10.799423</v>
-      </c>
-      <c r="R28" t="n">
-        <v>46.81</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="n">
-        <v>2648118657024</v>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="n">
-        <v>6.447</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.2919997</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>9.913</v>
-      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>36</v>
-      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3286,53 +3118,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>50.43283</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>10.30154</v>
-      </c>
-      <c r="R29" t="n">
-        <v>80.17</v>
-      </c>
-      <c r="S29" t="n">
-        <v>85</v>
-      </c>
-      <c r="T29" t="n">
-        <v>631966990336</v>
-      </c>
-      <c r="U29" t="n">
-        <v>21.645</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="n">
-        <v>14.774999</v>
-      </c>
-      <c r="X29" t="n">
-        <v>11.9320005</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.487</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.423</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>69</v>
-      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3390,53 +3192,23 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>29.951899</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>28.286232</v>
-      </c>
-      <c r="R30" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="S30" t="n">
-        <v>34</v>
-      </c>
-      <c r="T30" t="n">
-        <v>192941342720</v>
-      </c>
-      <c r="U30" t="n">
-        <v>10.786</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="n">
-        <v>20.204</v>
-      </c>
-      <c r="X30" t="n">
-        <v>11.311</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>84.316</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.26</v>
-      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>-42.3</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>-42.3</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>34</v>
-      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3444,7 +3216,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M%26M</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3494,47 +3266,23 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>20.877535</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.115483</v>
-      </c>
-      <c r="R31" t="n">
-        <v>164.21</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.9599999499999999</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4116573323264</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="n">
-        <v>17.031</v>
-      </c>
-      <c r="X31" t="n">
-        <v>8.609</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>125.278</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>62</v>
-      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3592,47 +3340,23 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>6.1426344</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.86730266</v>
-      </c>
-      <c r="R32" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="S32" t="n">
-        <v>255</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1356167249920</v>
-      </c>
-      <c r="U32" t="n">
-        <v>14.965999</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="n">
-        <v>29.405</v>
-      </c>
-      <c r="X32" t="n">
-        <v>38.147</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>72</v>
-      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3690,17 +3414,11 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>7.347592</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.883686</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="n">
-        <v>144244375552</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
@@ -3712,9 +3430,7 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="n">
-        <v>100</v>
-      </c>
+      <c r="AF33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3772,53 +3488,23 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P34" t="n">
-        <v>25.444912</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.2841005</v>
-      </c>
-      <c r="R34" t="n">
-        <v>100.02</v>
-      </c>
-      <c r="S34" t="n">
-        <v>244</v>
-      </c>
-      <c r="T34" t="n">
-        <v>485629394944</v>
-      </c>
-      <c r="U34" t="n">
-        <v>17.743999</v>
-      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="n">
-        <v>14.783</v>
-      </c>
-      <c r="X34" t="n">
-        <v>11.5559995</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>24.675</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.459</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.265</v>
-      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>59</v>
-      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3876,53 +3562,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P35" t="n">
-        <v>26.16391</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5.177395</v>
-      </c>
-      <c r="R35" t="n">
-        <v>21.78</v>
-      </c>
-      <c r="S35" t="n">
-        <v>248</v>
-      </c>
-      <c r="T35" t="n">
-        <v>347489959936</v>
-      </c>
-      <c r="U35" t="n">
-        <v>21.473</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="n">
-        <v>13.739</v>
-      </c>
-      <c r="X35" t="n">
-        <v>9.318</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.432</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.121</v>
-      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>47</v>
-      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3980,47 +3636,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P36" t="n">
-        <v>14.326874</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>10.491822</v>
-      </c>
-      <c r="R36" t="n">
-        <v>39.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>374</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2374206750720</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="n">
-        <v>54.70699999999999</v>
-      </c>
-      <c r="X36" t="n">
-        <v>38.068</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>39.034</v>
-      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>144.6</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>144.6</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>80</v>
-      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4078,53 +3710,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P37" t="n">
-        <v>59.513058</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>14.337361</v>
-      </c>
-      <c r="R37" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="S37" t="n">
-        <v>95</v>
-      </c>
-      <c r="T37" t="n">
-        <v>280979603456</v>
-      </c>
-      <c r="U37" t="n">
-        <v>23.913</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="n">
-        <v>38.09</v>
-      </c>
-      <c r="X37" t="n">
-        <v>36.923</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.917</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.464</v>
-      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>63</v>
-      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4182,53 +3784,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P38" t="n">
-        <v>35.626358</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>12.044059</v>
-      </c>
-      <c r="R38" t="n">
-        <v>759.55</v>
-      </c>
-      <c r="S38" t="n">
-        <v>190</v>
-      </c>
-      <c r="T38" t="n">
-        <v>575006113792</v>
-      </c>
-      <c r="U38" t="n">
-        <v>34.460998</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="n">
-        <v>27.021</v>
-      </c>
-      <c r="X38" t="n">
-        <v>22.399001</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>3.602</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.554</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.878</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>60</v>
-      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4286,45 +3858,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
         </is>
       </c>
-      <c r="P39" t="n">
-        <v>31.160711</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.157679</v>
-      </c>
-      <c r="R39" t="n">
-        <v>10.64</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="n">
-        <v>118415122432</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="n">
-        <v>10.953</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.329</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>48.061</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>38</v>
-      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4382,47 +3932,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>34.12324</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.882711</v>
-      </c>
-      <c r="R40" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>24</v>
-      </c>
-      <c r="T40" t="n">
-        <v>180692041728</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="n">
-        <v>33.731</v>
-      </c>
-      <c r="X40" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>64.041</v>
-      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="n">
-        <v>-42.7</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>-57.7</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>-57.7</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>28</v>
-      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4480,45 +4006,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
         </is>
       </c>
-      <c r="P41" t="n">
-        <v>104.28282</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>13.3846655</v>
-      </c>
-      <c r="R41" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="S41" t="n">
-        <v>6</v>
-      </c>
-      <c r="T41" t="n">
-        <v>571063140352</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="n">
-        <v>20.444</v>
-      </c>
-      <c r="X41" t="n">
-        <v>20.587</v>
-      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>676.4</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>676.4</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>68</v>
-      </c>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4576,47 +4080,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>26.382</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.2775254</v>
-      </c>
-      <c r="R42" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="S42" t="n">
-        <v>173</v>
-      </c>
-      <c r="T42" t="n">
-        <v>262502383616</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="n">
-        <v>24.655001</v>
-      </c>
-      <c r="X42" t="n">
-        <v>20.698</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>129.314</v>
-      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>74</v>
-      </c>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4674,47 +4154,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>16.582893</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.5415702</v>
-      </c>
-      <c r="R43" t="n">
-        <v>32.03</v>
-      </c>
-      <c r="S43" t="n">
-        <v>38</v>
-      </c>
-      <c r="T43" t="n">
-        <v>187167326208</v>
-      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="n">
-        <v>35.115</v>
-      </c>
-      <c r="X43" t="n">
-        <v>19.941</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>35.204</v>
-      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>42</v>
-      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4772,47 +4228,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>33.782997</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.1065493</v>
-      </c>
-      <c r="R44" t="n">
-        <v>120.09</v>
-      </c>
-      <c r="S44" t="n">
-        <v>93</v>
-      </c>
-      <c r="T44" t="n">
-        <v>5581888815104</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="n">
-        <v>10.609999</v>
-      </c>
-      <c r="X44" t="n">
-        <v>5.588</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>97.64</v>
-      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>38</v>
-      </c>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4870,53 +4302,23 @@
           <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>40.489838</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>7.677307</v>
-      </c>
-      <c r="R45" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="S45" t="n">
-        <v>124</v>
-      </c>
-      <c r="T45" t="n">
-        <v>12428031033344</v>
-      </c>
-      <c r="U45" t="n">
-        <v>20.151</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="n">
-        <v>32.573003</v>
-      </c>
-      <c r="X45" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>100.415</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.358</v>
-      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>35.09999999999999</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>35.09999999999999</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>54</v>
-      </c>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4974,47 +4376,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P46" t="n">
-        <v>31.679102</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.0924454</v>
-      </c>
-      <c r="R46" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="S46" t="n">
-        <v>65</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1220779442176</v>
-      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="n">
-        <v>14.453</v>
-      </c>
-      <c r="X46" t="n">
-        <v>6.0890004</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>168.051</v>
-      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="n">
-        <v>5.600000000000001</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>38</v>
-      </c>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5072,53 +4450,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P47" t="n">
-        <v>54.102196</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>27.279732</v>
-      </c>
-      <c r="R47" t="n">
-        <v>679.27</v>
-      </c>
-      <c r="S47" t="n">
-        <v>157</v>
-      </c>
-      <c r="T47" t="n">
-        <v>409904873472</v>
-      </c>
-      <c r="U47" t="n">
-        <v>52.5</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="n">
-        <v>18.868999</v>
-      </c>
-      <c r="X47" t="n">
-        <v>14.558</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>18.422</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.725</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.5669999999999999</v>
-      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>51</v>
-      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5176,51 +4524,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P48" t="n">
-        <v>143.77863</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>5.813523</v>
-      </c>
-      <c r="R48" t="n">
-        <v>50.23</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
-      <c r="T48" t="n">
-        <v>254703812608</v>
-      </c>
-      <c r="U48" t="n">
-        <v>5.583</v>
-      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
-      <c r="W48" t="n">
-        <v>6.243</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.4579999</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>46.566</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.131</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.476</v>
-      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>33</v>
-      </c>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5278,47 +4598,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P49" t="n">
-        <v>57.470177</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>8.454114000000001</v>
-      </c>
-      <c r="R49" t="n">
-        <v>57</v>
-      </c>
-      <c r="S49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T49" t="n">
-        <v>246401531904</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
-      <c r="W49" t="n">
-        <v>15.506</v>
-      </c>
-      <c r="X49" t="n">
-        <v>11.8389994</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>62</v>
-      </c>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5376,47 +4672,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P50" t="n">
-        <v>67.02742000000001</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>7.0875993</v>
-      </c>
-      <c r="R50" t="n">
-        <v>13.86</v>
-      </c>
-      <c r="S50" t="n">
-        <v>11</v>
-      </c>
-      <c r="T50" t="n">
-        <v>701356113920</v>
-      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
-      <c r="W50" t="n">
-        <v>16.316</v>
-      </c>
-      <c r="X50" t="n">
-        <v>11.023</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>34.15</v>
-      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>36</v>
-      </c>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5474,43 +4746,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P51" t="n">
-        <v>253.77501</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>-42.687134</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
-      <c r="T51" t="n">
-        <v>1071841673216</v>
-      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
-      <c r="W51" t="n">
-        <v>26.193002</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.1849999</v>
-      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.463</v>
-      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="n">
-        <v>37.5</v>
-      </c>
+      <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="n">
-        <v>35</v>
-      </c>
+      <c r="AF51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5568,47 +4820,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P52" t="n">
-        <v>38.910156</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>14.310254</v>
-      </c>
-      <c r="R52" t="n">
-        <v>19.59</v>
-      </c>
-      <c r="S52" t="n">
-        <v>166</v>
-      </c>
-      <c r="T52" t="n">
-        <v>189264805888</v>
-      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="n">
-        <v>40.046</v>
-      </c>
-      <c r="X52" t="n">
-        <v>31.785</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>4.863</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>56</v>
-      </c>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5666,47 +4894,23 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P53" t="n">
-        <v>29.214525</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>10.045888</v>
-      </c>
-      <c r="R53" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="S53" t="n">
-        <v>145</v>
-      </c>
-      <c r="T53" t="n">
-        <v>149484027904</v>
-      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
-      <c r="W53" t="n">
-        <v>56.596</v>
-      </c>
-      <c r="X53" t="n">
-        <v>44.739</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>9.593999999999999</v>
-      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>74</v>
-      </c>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5764,45 +4968,23 @@
           <t>within 3% of 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P54" t="n">
-        <v>19.174019</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2.1468048</v>
-      </c>
-      <c r="R54" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="S54" t="n">
-        <v>17</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3890559844352</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
-      <c r="W54" t="n">
-        <v>34.761003</v>
-      </c>
-      <c r="X54" t="n">
-        <v>28.467</v>
-      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>100</v>
-      </c>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5860,47 +5042,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
         </is>
       </c>
-      <c r="P55" t="n">
-        <v>40.022736</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>4.460094</v>
-      </c>
-      <c r="R55" t="n">
-        <v>290.31</v>
-      </c>
-      <c r="S55" t="n">
-        <v>205</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3417956941824</v>
-      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
-      <c r="W55" t="n">
-        <v>15.478</v>
-      </c>
-      <c r="X55" t="n">
-        <v>9.2930004</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>29.432</v>
-      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>44</v>
-      </c>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5958,47 +5116,23 @@
           <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P56" t="n">
-        <v>33.773373</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.9136887</v>
-      </c>
-      <c r="R56" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="S56" t="n">
-        <v>53</v>
-      </c>
-      <c r="T56" t="n">
-        <v>617058795520</v>
-      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
-      <c r="W56" t="n">
-        <v>6.771999600000001</v>
-      </c>
-      <c r="X56" t="n">
-        <v>5.619</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>11.469</v>
-      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>-24.5</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>-24.5</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>30</v>
-      </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6056,53 +5190,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; above 50DMA</t>
         </is>
       </c>
-      <c r="P57" t="n">
-        <v>17.394787</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>9.694862000000001</v>
-      </c>
-      <c r="R57" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="S57" t="n">
-        <v>667</v>
-      </c>
-      <c r="T57" t="n">
-        <v>184787845120</v>
-      </c>
-      <c r="U57" t="n">
-        <v>56.996</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
-      <c r="W57" t="n">
-        <v>24.779</v>
-      </c>
-      <c r="X57" t="n">
-        <v>17.066</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.784</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.852</v>
-      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>79</v>
-      </c>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6160,47 +5264,23 @@
           <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P58" t="n">
-        <v>15.7235565</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1.7499615</v>
-      </c>
-      <c r="R58" t="n">
-        <v>72.42</v>
-      </c>
-      <c r="S58" t="n">
-        <v>322</v>
-      </c>
-      <c r="T58" t="n">
-        <v>112478248960</v>
-      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
-      <c r="W58" t="n">
-        <v>9.854999000000001</v>
-      </c>
-      <c r="X58" t="n">
-        <v>8.382000000000001</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>3.461</v>
-      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>-39.3</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>-39.3</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>42</v>
-      </c>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6258,47 +5338,23 @@
           <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P59" t="n">
-        <v>45.71522</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>11.137925</v>
-      </c>
-      <c r="R59" t="n">
-        <v>122.06</v>
-      </c>
-      <c r="S59" t="n">
-        <v>65</v>
-      </c>
-      <c r="T59" t="n">
-        <v>871769178112</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
-      <c r="W59" t="n">
-        <v>13.516</v>
-      </c>
-      <c r="X59" t="n">
-        <v>12.236</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>6.092</v>
-      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>56</v>
-      </c>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6357,42 +5413,22 @@
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
-        <v>0.6559713</v>
-      </c>
-      <c r="R60" t="n">
-        <v>-89.77</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
-      <c r="T60" t="n">
-        <v>175048392704</v>
-      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
-      <c r="W60" t="n">
-        <v>93.80199999999999</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>273.033</v>
-      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="n">
-        <v>-52.90000000000001</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6450,47 +5486,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>34.616726</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>5.778402</v>
-      </c>
-      <c r="R61" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="S61" t="n">
-        <v>6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>89464422400</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
-      <c r="W61" t="n">
-        <v>15.117</v>
-      </c>
-      <c r="X61" t="n">
-        <v>10.132</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>29.595</v>
-      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>30</v>
-      </c>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6548,47 +5560,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P62" t="n">
-        <v>8.708930000000001</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>2.9618435</v>
-      </c>
-      <c r="R62" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="S62" t="n">
-        <v>243</v>
-      </c>
-      <c r="T62" t="n">
-        <v>2615386570752</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
-      <c r="W62" t="n">
-        <v>6.426</v>
-      </c>
-      <c r="X62" t="n">
-        <v>6.515</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0.431</v>
-      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>6.800000000000001</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>76</v>
-      </c>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6646,45 +5634,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P63" t="n">
-        <v>16.611982</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2.1909964</v>
-      </c>
-      <c r="R63" t="n">
-        <v>84.12</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
-      <c r="T63" t="n">
-        <v>110799880192</v>
-      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="n">
-        <v>54.527</v>
-      </c>
-      <c r="X63" t="n">
-        <v>42.543998</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>310.553</v>
-      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>74</v>
-      </c>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6742,47 +5708,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P64" t="n">
-        <v>53.19195</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>14.205161</v>
-      </c>
-      <c r="R64" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="S64" t="n">
-        <v>100</v>
-      </c>
-      <c r="T64" t="n">
-        <v>489687252992</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="n">
-        <v>7.454</v>
-      </c>
-      <c r="X64" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>335.854</v>
-      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>-29.4</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>-29.4</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>22</v>
-      </c>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6840,47 +5782,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P65" t="n">
-        <v>18.656094</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>4.5517774</v>
-      </c>
-      <c r="R65" t="n">
-        <v>119.8</v>
-      </c>
-      <c r="S65" t="n">
-        <v>80</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1021919952896</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
-      <c r="W65" t="n">
-        <v>25.354</v>
-      </c>
-      <c r="X65" t="n">
-        <v>18.450001</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>29.388</v>
-      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>68</v>
-      </c>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6938,45 +5856,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P66" t="n">
-        <v>25.202898</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.3351247</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.6899999999999999</v>
-      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
-      <c r="T66" t="n">
-        <v>119181647872</v>
-      </c>
+      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
-      <c r="W66" t="n">
-        <v>36.141</v>
-      </c>
-      <c r="X66" t="n">
-        <v>11.1420006</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>26.634</v>
-      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>62</v>
-      </c>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7034,47 +5930,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P67" t="n">
-        <v>66.697</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>12.903393</v>
-      </c>
-      <c r="R67" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="S67" t="n">
-        <v>13</v>
-      </c>
-      <c r="T67" t="n">
-        <v>147324108800</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
-      <c r="W67" t="n">
-        <v>8.273999999999999</v>
-      </c>
-      <c r="X67" t="n">
-        <v>3.571</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>190.282</v>
-      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>36</v>
-      </c>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7132,45 +6004,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P68" t="n">
-        <v>21.521738</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>4.552851</v>
-      </c>
-      <c r="R68" t="n">
-        <v>2.99</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
-      <c r="T68" t="n">
-        <v>96525000704</v>
-      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
-      <c r="W68" t="n">
-        <v>85.238</v>
-      </c>
-      <c r="X68" t="n">
-        <v>573.759</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0.114</v>
-      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="n">
-        <v>10644.1</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>130</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>94</v>
-      </c>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7228,47 +6078,23 @@
           <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P69" t="n">
-        <v>37.451374</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>11.421667</v>
-      </c>
-      <c r="R69" t="n">
-        <v>69.92</v>
-      </c>
-      <c r="S69" t="n">
-        <v>102</v>
-      </c>
-      <c r="T69" t="n">
-        <v>299965874176</v>
-      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="X69" t="n">
-        <v>10.665</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1.424</v>
-      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>70</v>
-      </c>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7326,45 +6152,23 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P70" t="n">
-        <v>19.340063</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>2.8785374</v>
-      </c>
-      <c r="R70" t="n">
-        <v>25.76</v>
-      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
-      <c r="T70" t="n">
-        <v>218080821248</v>
-      </c>
+      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="n">
-        <v>61.72299999999999</v>
-      </c>
-      <c r="X70" t="n">
-        <v>48.151</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>255.574</v>
-      </c>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>68</v>
-      </c>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7422,47 +6226,23 @@
           <t>within 3% of 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P71" t="n">
-        <v>40.83427</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>2.1815078</v>
-      </c>
-      <c r="R71" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="S71" t="n">
-        <v>18</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1110588260352</v>
-      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="n">
-        <v>11.1999996</v>
-      </c>
-      <c r="X71" t="n">
-        <v>4.818</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>43.613</v>
-      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>-43.7</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>-43.7</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>36</v>
-      </c>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7520,53 +6300,23 @@
           <t>at/above 200DMA; recovery &gt;=10%</t>
         </is>
       </c>
-      <c r="P72" t="n">
-        <v>10.035672</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.1744733</v>
-      </c>
-      <c r="R72" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="S72" t="n">
-        <v>412</v>
-      </c>
-      <c r="T72" t="n">
-        <v>742029393920</v>
-      </c>
-      <c r="U72" t="n">
-        <v>23.363</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
-      <c r="W72" t="n">
-        <v>21.968001</v>
-      </c>
-      <c r="X72" t="n">
-        <v>23.231001</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>18.802</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>2.429</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>1.702</v>
-      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>86</v>
-      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7625,38 +6375,22 @@
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
-        <v>3.0729208</v>
-      </c>
-      <c r="R73" t="n">
-        <v>-4.24</v>
-      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
-      <c r="T73" t="n">
-        <v>178797969408</v>
-      </c>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
-      <c r="W73" t="n">
-        <v>11.492</v>
-      </c>
-      <c r="X73" t="n">
-        <v>-3.15</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>25.791</v>
-      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="n">
-        <v>37.2</v>
-      </c>
+      <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="n">
-        <v>33</v>
-      </c>
+      <c r="AF73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7714,47 +6448,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P74" t="n">
-        <v>4.903233</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1.081117</v>
-      </c>
-      <c r="R74" t="n">
-        <v>261.97</v>
-      </c>
-      <c r="S74" t="n">
-        <v>443</v>
-      </c>
-      <c r="T74" t="n">
-        <v>183387652096</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
-      <c r="W74" t="n">
-        <v>54.431</v>
-      </c>
-      <c r="X74" t="n">
-        <v>60.307</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>6.409</v>
-      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>159.4</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>159.4</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>80</v>
-      </c>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7812,47 +6522,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P75" t="n">
-        <v>11.590909</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1.7740043</v>
-      </c>
-      <c r="R75" t="n">
-        <v>23.76</v>
-      </c>
-      <c r="S75" t="n">
-        <v>262</v>
-      </c>
-      <c r="T75" t="n">
-        <v>381879746560</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
-      <c r="W75" t="n">
-        <v>28.304002</v>
-      </c>
-      <c r="X75" t="n">
-        <v>17.458001</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>82</v>
-      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>34</v>
-      </c>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7910,47 +6596,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P76" t="n">
-        <v>20.555058</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2.760321</v>
-      </c>
-      <c r="R76" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="S76" t="n">
-        <v>57.99999999999999</v>
-      </c>
-      <c r="T76" t="n">
-        <v>569106890752</v>
-      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="n">
-        <v>42.416</v>
-      </c>
-      <c r="X76" t="n">
-        <v>29.786</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>484.313</v>
-      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>74</v>
-      </c>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8008,47 +6670,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P77" t="n">
-        <v>19.721561</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>2.6128383</v>
-      </c>
-      <c r="R77" t="n">
-        <v>29.45</v>
-      </c>
-      <c r="S77" t="n">
-        <v>170</v>
-      </c>
-      <c r="T77" t="n">
-        <v>184694390784</v>
-      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="n">
-        <v>17.395</v>
-      </c>
-      <c r="X77" t="n">
-        <v>33.823</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>4.475</v>
-      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>60</v>
-      </c>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8106,47 +6744,23 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P78" t="n">
-        <v>45.249382</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>8.203222999999999</v>
-      </c>
-      <c r="R78" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="S78" t="n">
-        <v>25</v>
-      </c>
-      <c r="T78" t="n">
-        <v>372200767488</v>
-      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="n">
-        <v>12.839</v>
-      </c>
-      <c r="X78" t="n">
-        <v>8.984</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>129.033</v>
-      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>44</v>
-      </c>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8204,53 +6818,23 @@
           <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P79" t="n">
-        <v>20.569326</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1.8531164</v>
-      </c>
-      <c r="R79" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>144</v>
-      </c>
-      <c r="T79" t="n">
-        <v>162278129664</v>
-      </c>
-      <c r="U79" t="n">
-        <v>10.309</v>
-      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
-      <c r="W79" t="n">
-        <v>25.088</v>
-      </c>
-      <c r="X79" t="n">
-        <v>18.333</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>20.684</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>6.018</v>
-      </c>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>-44.6</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>-44.6</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>51</v>
-      </c>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8308,47 +6892,23 @@
           <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P80" t="n">
-        <v>83.33842</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>6.825559</v>
-      </c>
-      <c r="R80" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="S80" t="n">
-        <v>16</v>
-      </c>
-      <c r="T80" t="n">
-        <v>529129930752</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="n">
-        <v>7.277</v>
-      </c>
-      <c r="X80" t="n">
-        <v>2.8169999</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>27.724</v>
-      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>28</v>
-      </c>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8406,45 +6966,23 @@
           <t>at/above 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P81" t="n">
-        <v>20.954382</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>1.0980474</v>
-      </c>
-      <c r="R81" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="S81" t="n">
-        <v>85</v>
-      </c>
-      <c r="T81" t="n">
-        <v>281219530752</v>
-      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="n">
-        <v>23.771</v>
-      </c>
-      <c r="X81" t="n">
-        <v>13.617</v>
-      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>34.59999999999999</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>34.59999999999999</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>85</v>
-      </c>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8502,45 +7040,23 @@
           <t>at/above 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P82" t="n">
-        <v>14.744877</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1.9565442</v>
-      </c>
-      <c r="R82" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="S82" t="n">
-        <v>96</v>
-      </c>
-      <c r="T82" t="n">
-        <v>206717861888</v>
-      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="n">
-        <v>50.985</v>
-      </c>
-      <c r="X82" t="n">
-        <v>37.791002</v>
-      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>100</v>
-      </c>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8598,47 +7114,23 @@
           <t>within 3% of 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P83" t="n">
-        <v>9.207571</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1.7019919</v>
-      </c>
-      <c r="R83" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="S83" t="n">
-        <v>271</v>
-      </c>
-      <c r="T83" t="n">
-        <v>177368776704</v>
-      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="n">
-        <v>15.151</v>
-      </c>
-      <c r="X83" t="n">
-        <v>9.581000000000001</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>10.274</v>
-      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>28</v>
-      </c>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8696,47 +7188,23 @@
           <t>within 3% of 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P84" t="n">
-        <v>28.168499</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.8688183</v>
-      </c>
-      <c r="R84" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="S84" t="n">
-        <v>209</v>
-      </c>
-      <c r="T84" t="n">
-        <v>772463198208</v>
-      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="n">
-        <v>46.019</v>
-      </c>
-      <c r="X84" t="n">
-        <v>31.094998</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>113.111</v>
-      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>56</v>
-      </c>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8794,47 +7262,23 @@
           <t>within 3% of 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P85" t="n">
-        <v>79.34601600000001</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1.1554037</v>
-      </c>
-      <c r="R85" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="S85" t="n">
-        <v>50</v>
-      </c>
-      <c r="T85" t="n">
-        <v>337622401024</v>
-      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="n">
-        <v>91.65100000000001</v>
-      </c>
-      <c r="X85" t="n">
-        <v>105.248</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0.007</v>
-      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="n">
-        <v>4.100000000000001</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>48</v>
-      </c>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/NSE_200DMA_Recovery_Scanner.xlsx
+++ b/output/NSE_200DMA_Recovery_Scanner.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF85"/>
+  <dimension ref="A1:AF87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,19 +596,19 @@
         <v>3558.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3584.28</v>
+        <v>3582.53</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.71</v>
+        <v>-0.66</v>
       </c>
       <c r="G2" t="n">
-        <v>3426.33</v>
+        <v>3423.6</v>
       </c>
       <c r="H2" t="n">
-        <v>58.73</v>
+        <v>58.92</v>
       </c>
       <c r="I2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>43.866634</v>
+        <v>43.10161</v>
       </c>
       <c r="Q2" t="n">
         <v>7.3281016</v>
       </c>
       <c r="R2" t="n">
-        <v>81.13</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>101</v>
@@ -694,19 +694,19 @@
         <v>278.12</v>
       </c>
       <c r="E3" t="n">
-        <v>279.51</v>
+        <v>279.93</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5</v>
+        <v>-0.65</v>
       </c>
       <c r="G3" t="n">
-        <v>251.14</v>
+        <v>251.79</v>
       </c>
       <c r="H3" t="n">
-        <v>74.72</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>16.283373</v>
+        <v>15.847294</v>
       </c>
       <c r="Q3" t="n">
         <v>4.646485</v>
       </c>
       <c r="R3" t="n">
-        <v>17.08</v>
+        <v>17.55</v>
       </c>
       <c r="S3" t="n">
         <v>108</v>
@@ -842,9 +842,7 @@
       <c r="S4" t="n">
         <v>204</v>
       </c>
-      <c r="T4" t="n">
-        <v>1008188391424</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
@@ -929,20 +927,18 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>86.91379000000001</v>
+        <v>89.22123999999999</v>
       </c>
       <c r="Q5" t="n">
         <v>14.464019</v>
       </c>
       <c r="R5" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="S5" t="n">
         <v>24</v>
       </c>
-      <c r="T5" t="n">
-        <v>331533746176</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
@@ -1088,19 +1084,19 @@
         <v>1621.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1617.58</v>
+        <v>1618.73</v>
       </c>
       <c r="F7" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G7" t="n">
-        <v>1538.94</v>
+        <v>1536.2</v>
       </c>
       <c r="H7" t="n">
-        <v>56.52</v>
+        <v>56.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1127,13 +1123,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>44.43805</v>
+        <v>42.920307</v>
       </c>
       <c r="Q7" t="n">
         <v>11.312315</v>
       </c>
       <c r="R7" t="n">
-        <v>36.48</v>
+        <v>37.77</v>
       </c>
       <c r="S7" t="n">
         <v>111</v>
@@ -1225,16 +1221,16 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>14.044352</v>
+        <v>14.283404</v>
       </c>
       <c r="Q8" t="n">
         <v>1.7764677</v>
       </c>
       <c r="R8" t="n">
-        <v>11.95</v>
+        <v>11.75</v>
       </c>
       <c r="S8" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="T8" t="n">
         <v>222470488064</v>
@@ -1278,45 +1274,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>826.9</v>
+        <v>951.7</v>
       </c>
       <c r="E9" t="n">
-        <v>818.76</v>
+        <v>944.37</v>
       </c>
       <c r="F9" t="n">
-        <v>0.99</v>
+        <v>0.78</v>
       </c>
       <c r="G9" t="n">
-        <v>767.6</v>
+        <v>917.52</v>
       </c>
       <c r="H9" t="n">
-        <v>55.54</v>
+        <v>56.78</v>
       </c>
       <c r="I9" t="n">
-        <v>0.65</v>
+        <v>3.89</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>738.9</v>
+        <v>903.25</v>
       </c>
       <c r="L9" t="n">
-        <v>11.91</v>
+        <v>5.36</v>
       </c>
       <c r="M9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1325,47 +1321,55 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.479492</v>
+        <v>14.144872</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.402361000000001</v>
+        <v>1.753955</v>
       </c>
       <c r="R9" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>63.85</v>
+      </c>
+      <c r="S9" t="n">
+        <v>68</v>
+      </c>
       <c r="T9" t="n">
-        <v>188056174592</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>161763082240</v>
+      </c>
+      <c r="U9" t="n">
+        <v>16.853</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>18.441999</v>
+        <v>10.4449995</v>
       </c>
       <c r="X9" t="n">
-        <v>14.681</v>
+        <v>34.782</v>
       </c>
       <c r="Y9" t="n">
-        <v>42.585</v>
-      </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+        <v>7.742</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.006</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.791</v>
+      </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>24</v>
+        <v>-39.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>-20.1</v>
+        <v>-34.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>-20.1</v>
+        <v>-34.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -1374,7 +1378,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1383,33 +1387,33 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4874.8</v>
+        <v>1703.8</v>
       </c>
       <c r="E10" t="n">
-        <v>4811.81</v>
+        <v>1754.54</v>
       </c>
       <c r="F10" t="n">
-        <v>1.31</v>
+        <v>-2.89</v>
       </c>
       <c r="G10" t="n">
-        <v>4640.3</v>
+        <v>1661.3</v>
       </c>
       <c r="H10" t="n">
-        <v>57.37</v>
+        <v>63.24</v>
       </c>
       <c r="I10" t="n">
-        <v>0.33</v>
+        <v>1.93</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4360.1</v>
+        <v>1473</v>
       </c>
       <c r="L10" t="n">
-        <v>11.8</v>
+        <v>15.67</v>
       </c>
       <c r="M10" t="n">
         <v>95</v>
@@ -1421,49 +1425,55 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>31.055614</v>
+        <v>454.34668</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.306124</v>
+        <v>3.7868536</v>
       </c>
       <c r="R10" t="n">
-        <v>156.97</v>
+        <v>3.75</v>
       </c>
       <c r="S10" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>223011028992</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
+        <v>128002572288</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5.939</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>35.718</v>
+        <v>6.630999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>28.608</v>
+        <v>8.4309995</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.671</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+        <v>11.693</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.715</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.845</v>
+      </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>8.300000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>6.600000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>6.600000000000001</v>
+        <v>-63.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1472,7 +1482,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1481,33 +1491,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>821.5</v>
+        <v>1298</v>
       </c>
       <c r="E11" t="n">
-        <v>810.67</v>
+        <v>1310.76</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>-0.97</v>
       </c>
       <c r="G11" t="n">
-        <v>771.58</v>
+        <v>1208.71</v>
       </c>
       <c r="H11" t="n">
-        <v>63.16</v>
+        <v>67.19</v>
       </c>
       <c r="I11" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>652</v>
+        <v>1123.6</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>15.52</v>
       </c>
       <c r="M11" t="n">
         <v>95</v>
@@ -1523,45 +1533,45 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>37.4601</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.515607</v>
+        <v>8.610682000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>21.93</v>
+        <v>25.96</v>
       </c>
       <c r="S11" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="T11" t="n">
-        <v>87311089664</v>
+        <v>814575058944</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>28.083</v>
+        <v>5.302</v>
       </c>
       <c r="X11" t="n">
-        <v>23.719</v>
+        <v>6.923</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.135</v>
+        <v>2.801</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.7</v>
+        <v>-16.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>4.7</v>
+        <v>-16.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -1570,7 +1580,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CEATLTD</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1579,33 +1589,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3688.8</v>
+        <v>826.9</v>
       </c>
       <c r="E12" t="n">
-        <v>3639.73</v>
+        <v>818.42</v>
       </c>
       <c r="F12" t="n">
-        <v>1.35</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3549.95</v>
+        <v>771.08</v>
       </c>
       <c r="H12" t="n">
-        <v>55.54</v>
+        <v>55.32</v>
       </c>
       <c r="I12" t="n">
-        <v>0.19</v>
+        <v>0.65</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3309.1</v>
+        <v>738.9</v>
       </c>
       <c r="L12" t="n">
-        <v>11.47</v>
+        <v>11.91</v>
       </c>
       <c r="M12" t="n">
         <v>95</v>
@@ -1621,45 +1631,43 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.264025</v>
+        <v>58.438168</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5360997</v>
+        <v>9.402361000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>146.01</v>
-      </c>
-      <c r="S12" t="n">
-        <v>95</v>
-      </c>
+        <v>14.15</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>149212299264</v>
+        <v>188056174592</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>4.145</v>
+        <v>18.441999</v>
       </c>
       <c r="X12" t="n">
-        <v>3.583</v>
+        <v>14.681</v>
       </c>
       <c r="Y12" t="n">
-        <v>64.742</v>
+        <v>42.585</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>22.3</v>
+        <v>24</v>
       </c>
       <c r="AD12" t="n">
-        <v>-96.2</v>
+        <v>-20.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>-96.2</v>
+        <v>-20.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -1668,7 +1676,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1677,36 +1685,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>282.6</v>
+        <v>4874.8</v>
       </c>
       <c r="E13" t="n">
-        <v>279.26</v>
+        <v>4809.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G13" t="n">
-        <v>278.79</v>
+        <v>4647.65</v>
       </c>
       <c r="H13" t="n">
-        <v>55.2</v>
+        <v>57.07</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>273</v>
+        <v>4360.1</v>
       </c>
       <c r="L13" t="n">
-        <v>3.52</v>
+        <v>11.8</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1715,49 +1723,49 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.078459</v>
+        <v>31.055614</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9018266</v>
+        <v>5.306124</v>
       </c>
       <c r="R13" t="n">
-        <v>28.04</v>
+        <v>156.97</v>
       </c>
       <c r="S13" t="n">
-        <v>354</v>
+        <v>150</v>
       </c>
       <c r="T13" t="n">
-        <v>423900053504</v>
+        <v>223011028992</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>24.001</v>
+        <v>35.718</v>
       </c>
       <c r="X13" t="n">
-        <v>11.3199994</v>
+        <v>28.608</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.507</v>
+        <v>1.671</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>-53.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>35.09999999999999</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="AE13" t="n">
-        <v>35.09999999999999</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="AF13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -1766,7 +1774,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>CEATLTD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1775,36 +1783,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>170.54</v>
+        <v>3688.8</v>
       </c>
       <c r="E14" t="n">
-        <v>166.6</v>
+        <v>3636.48</v>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>162.15</v>
+        <v>3554.71</v>
       </c>
       <c r="H14" t="n">
-        <v>52.59</v>
+        <v>55.71</v>
       </c>
       <c r="I14" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>161.2</v>
+        <v>3309.1</v>
       </c>
       <c r="L14" t="n">
-        <v>5.79</v>
+        <v>11.47</v>
       </c>
       <c r="M14" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1813,45 +1821,49 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9.516741</v>
+        <v>25.264025</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.097534</v>
+        <v>2.5360997</v>
       </c>
       <c r="R14" t="n">
-        <v>17.92</v>
+        <v>146.01</v>
       </c>
       <c r="S14" t="n">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="T14" t="n">
-        <v>298888200192</v>
+        <v>149212299264</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>2.396</v>
+        <v>4.145</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8670002</v>
+        <v>3.583</v>
       </c>
       <c r="Y14" t="n">
-        <v>108.059</v>
+        <v>64.742</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+        <v>22.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-96.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-96.2</v>
+      </c>
       <c r="AF14" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -1860,7 +1872,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1869,36 +1881,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>444.1</v>
+        <v>821.5</v>
       </c>
       <c r="E15" t="n">
-        <v>456.75</v>
+        <v>809.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.77</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>428.23</v>
+        <v>770.4299999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>58.97</v>
+        <v>63.78</v>
       </c>
       <c r="I15" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>365.3</v>
+        <v>652</v>
       </c>
       <c r="L15" t="n">
-        <v>21.57</v>
+        <v>26</v>
       </c>
       <c r="M15" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1907,49 +1919,49 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>16.472553</v>
+        <v>37.4601</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6806881</v>
+        <v>5.515607</v>
       </c>
       <c r="R15" t="n">
-        <v>26.96</v>
+        <v>21.93</v>
       </c>
       <c r="S15" t="n">
-        <v>248</v>
+        <v>72</v>
       </c>
       <c r="T15" t="n">
-        <v>280929370112</v>
+        <v>87311089664</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>6.451</v>
+        <v>28.083</v>
       </c>
       <c r="X15" t="n">
-        <v>5.829</v>
+        <v>23.719</v>
       </c>
       <c r="Y15" t="n">
-        <v>21.987</v>
+        <v>0.135</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2660</v>
+        <v>4.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>2660</v>
+        <v>4.7</v>
       </c>
       <c r="AF15" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1958,7 +1970,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1967,36 +1979,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>94.05</v>
+        <v>282.6</v>
       </c>
       <c r="E16" t="n">
-        <v>96.66</v>
+        <v>279.26</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>92.22</v>
+        <v>278.79</v>
       </c>
       <c r="H16" t="n">
-        <v>55.99</v>
+        <v>55.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.42</v>
+        <v>2.54</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>79.59999999999999</v>
+        <v>273</v>
       </c>
       <c r="L16" t="n">
-        <v>18.15</v>
+        <v>3.52</v>
       </c>
       <c r="M16" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2005,47 +2017,49 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>21.5711</v>
+        <v>9.961226</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7916298</v>
+        <v>1.9018266</v>
       </c>
       <c r="R16" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
+        <v>28.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>354</v>
+      </c>
       <c r="T16" t="n">
-        <v>104160116736</v>
+        <v>423900053504</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>58.55099999999999</v>
+        <v>24.001</v>
       </c>
       <c r="X16" t="n">
-        <v>44.877997</v>
+        <v>11.3199994</v>
       </c>
       <c r="Y16" t="n">
-        <v>195.685</v>
+        <v>10.507</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>24.6</v>
+        <v>-53.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>28.6</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="AE16" t="n">
-        <v>28.6</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="AF16" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -2054,7 +2068,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2063,36 +2077,36 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>940</v>
+        <v>170.54</v>
       </c>
       <c r="E17" t="n">
-        <v>963.5599999999999</v>
+        <v>166.6</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.45</v>
+        <v>2.36</v>
       </c>
       <c r="G17" t="n">
-        <v>892.75</v>
+        <v>162.15</v>
       </c>
       <c r="H17" t="n">
-        <v>56.6</v>
+        <v>52.59</v>
       </c>
       <c r="I17" t="n">
-        <v>0.65</v>
+        <v>0.28</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>784.95</v>
+        <v>161.2</v>
       </c>
       <c r="L17" t="n">
-        <v>19.75</v>
+        <v>5.79</v>
       </c>
       <c r="M17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2101,49 +2115,45 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>47.739967</v>
+        <v>9.516741</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.69312</v>
+        <v>2.097534</v>
       </c>
       <c r="R17" t="n">
-        <v>19.69</v>
+        <v>17.92</v>
       </c>
       <c r="S17" t="n">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="T17" t="n">
-        <v>162499756032</v>
+        <v>298888200192</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>26.553</v>
+        <v>2.396</v>
       </c>
       <c r="X17" t="n">
-        <v>24.400999</v>
+        <v>2.8670002</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.314</v>
+        <v>108.059</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>120.4</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -2152,7 +2162,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2161,33 +2171,33 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1496.5</v>
+        <v>444.1</v>
       </c>
       <c r="E18" t="n">
-        <v>1530.94</v>
+        <v>456.36</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.25</v>
+        <v>-2.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1443.66</v>
+        <v>428.86</v>
       </c>
       <c r="H18" t="n">
-        <v>59.16</v>
+        <v>59.27</v>
       </c>
       <c r="I18" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1356.6</v>
+        <v>365.3</v>
       </c>
       <c r="L18" t="n">
-        <v>10.31</v>
+        <v>21.57</v>
       </c>
       <c r="M18" t="n">
         <v>85</v>
@@ -2203,51 +2213,45 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>55.241787</v>
+        <v>16.472553</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.703518</v>
+        <v>1.6806881</v>
       </c>
       <c r="R18" t="n">
-        <v>27.09</v>
+        <v>26.96</v>
       </c>
       <c r="S18" t="n">
-        <v>88</v>
+        <v>248</v>
       </c>
       <c r="T18" t="n">
-        <v>393700409344</v>
-      </c>
-      <c r="U18" t="n">
-        <v>12.517</v>
-      </c>
+        <v>280929370112</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>18.714</v>
+        <v>6.451</v>
       </c>
       <c r="X18" t="n">
-        <v>14.272</v>
+        <v>5.829</v>
       </c>
       <c r="Y18" t="n">
-        <v>28.466</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.331</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.354</v>
-      </c>
+        <v>21.987</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>-15.6</v>
+        <v>12.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>-3.8</v>
+        <v>2660</v>
       </c>
       <c r="AE18" t="n">
-        <v>-3.8</v>
+        <v>2660</v>
       </c>
       <c r="AF18" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -2256,7 +2260,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2265,33 +2269,33 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5558</v>
+        <v>94.05</v>
       </c>
       <c r="E19" t="n">
-        <v>5682.22</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.19</v>
+        <v>-2.58</v>
       </c>
       <c r="G19" t="n">
-        <v>5348.37</v>
+        <v>92.16</v>
       </c>
       <c r="H19" t="n">
-        <v>57.12</v>
+        <v>56.47</v>
       </c>
       <c r="I19" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5035</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>10.39</v>
+        <v>18.15</v>
       </c>
       <c r="M19" t="n">
         <v>85</v>
@@ -2307,45 +2311,43 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>51.287254</v>
+        <v>21.5711</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.21624</v>
+        <v>2.7916298</v>
       </c>
       <c r="R19" t="n">
-        <v>108.37</v>
-      </c>
-      <c r="S19" t="n">
-        <v>163</v>
-      </c>
+        <v>4.36</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
-        <v>1338745946112</v>
+        <v>104160116736</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>15.212</v>
+        <v>58.55099999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>13.376</v>
+        <v>44.877997</v>
       </c>
       <c r="Y19" t="n">
-        <v>26.875</v>
+        <v>195.685</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>8.200000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>13.6</v>
+        <v>28.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>13.6</v>
+        <v>28.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -2354,7 +2356,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2363,33 +2365,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>737.85</v>
+        <v>940</v>
       </c>
       <c r="E20" t="n">
-        <v>751.37</v>
+        <v>962.38</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8</v>
+        <v>-2.33</v>
       </c>
       <c r="G20" t="n">
-        <v>711.95</v>
+        <v>894.14</v>
       </c>
       <c r="H20" t="n">
-        <v>55.85</v>
+        <v>56.43</v>
       </c>
       <c r="I20" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>652.25</v>
+        <v>784.95</v>
       </c>
       <c r="L20" t="n">
-        <v>13.12</v>
+        <v>19.75</v>
       </c>
       <c r="M20" t="n">
         <v>85</v>
@@ -2405,45 +2407,45 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>18.760487</v>
+        <v>47.61905</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.507057</v>
+        <v>9.69312</v>
       </c>
       <c r="R20" t="n">
-        <v>39.33</v>
+        <v>19.74</v>
       </c>
       <c r="S20" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="T20" t="n">
-        <v>607951388672</v>
+        <v>162499756032</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
-        <v>9.103999999999999</v>
+        <v>26.553</v>
       </c>
       <c r="X20" t="n">
-        <v>7.379</v>
+        <v>24.400999</v>
       </c>
       <c r="Y20" t="n">
-        <v>37.523</v>
+        <v>3.314</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>30.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>7.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>7.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2452,7 +2454,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2461,33 +2463,33 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1298</v>
+        <v>1496.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1311.85</v>
+        <v>1530.94</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.06</v>
+        <v>-2.25</v>
       </c>
       <c r="G21" t="n">
-        <v>1206.51</v>
+        <v>1443.66</v>
       </c>
       <c r="H21" t="n">
-        <v>67.27</v>
+        <v>59.16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1123.6</v>
+        <v>1356.6</v>
       </c>
       <c r="L21" t="n">
-        <v>15.52</v>
+        <v>10.31</v>
       </c>
       <c r="M21" t="n">
         <v>85</v>
@@ -2503,45 +2505,51 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>48.778652</v>
+        <v>54.93759</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.610682000000001</v>
+        <v>6.703518</v>
       </c>
       <c r="R21" t="n">
-        <v>26.61</v>
+        <v>27.24</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="T21" t="n">
-        <v>814575058944</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
+        <v>393700409344</v>
+      </c>
+      <c r="U21" t="n">
+        <v>12.517</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="n">
-        <v>5.302</v>
+        <v>18.714</v>
       </c>
       <c r="X21" t="n">
-        <v>6.923</v>
+        <v>14.272</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.801</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
+        <v>28.466</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.354</v>
+      </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>19.5</v>
+        <v>-15.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>-16.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AE21" t="n">
-        <v>-16.6</v>
+        <v>-3.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -2550,7 +2558,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2559,36 +2567,36 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>144.1</v>
+        <v>5558</v>
       </c>
       <c r="E22" t="n">
-        <v>147.76</v>
+        <v>5680</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.47</v>
+        <v>-2.15</v>
       </c>
       <c r="G22" t="n">
-        <v>142.97</v>
+        <v>5354.29</v>
       </c>
       <c r="H22" t="n">
-        <v>53.56</v>
+        <v>56.21</v>
       </c>
       <c r="I22" t="n">
-        <v>0.46</v>
+        <v>0.75</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>135.62</v>
+        <v>5035</v>
       </c>
       <c r="L22" t="n">
-        <v>6.25</v>
+        <v>10.39</v>
       </c>
       <c r="M22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2597,7 +2605,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2624,7 +2632,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2633,36 +2641,36 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>410.8</v>
+        <v>737.85</v>
       </c>
       <c r="E23" t="n">
-        <v>419.76</v>
+        <v>751.03</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.14</v>
+        <v>-1.75</v>
       </c>
       <c r="G23" t="n">
-        <v>408.23</v>
+        <v>712.84</v>
       </c>
       <c r="H23" t="n">
-        <v>58.27</v>
+        <v>55.79</v>
       </c>
       <c r="I23" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>382.2</v>
+        <v>652.25</v>
       </c>
       <c r="L23" t="n">
-        <v>7.48</v>
+        <v>13.12</v>
       </c>
       <c r="M23" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2671,7 +2679,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2698,7 +2706,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2707,33 +2715,33 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>440.65</v>
+        <v>144.1</v>
       </c>
       <c r="E24" t="n">
-        <v>444.74</v>
+        <v>147.76</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.92</v>
+        <v>-2.47</v>
       </c>
       <c r="G24" t="n">
-        <v>437.84</v>
+        <v>142.97</v>
       </c>
       <c r="H24" t="n">
-        <v>50.99</v>
+        <v>53.56</v>
       </c>
       <c r="I24" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>438.5</v>
+        <v>135.62</v>
       </c>
       <c r="L24" t="n">
-        <v>0.49</v>
+        <v>6.25</v>
       </c>
       <c r="M24" t="n">
         <v>80</v>
@@ -2745,7 +2753,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2772,7 +2780,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2781,33 +2789,33 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>221.06</v>
+        <v>410.8</v>
       </c>
       <c r="E25" t="n">
-        <v>220.31</v>
+        <v>419.76</v>
       </c>
       <c r="F25" t="n">
-        <v>0.34</v>
+        <v>-2.14</v>
       </c>
       <c r="G25" t="n">
-        <v>217.22</v>
+        <v>408.23</v>
       </c>
       <c r="H25" t="n">
-        <v>49.38</v>
+        <v>58.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>210.24</v>
+        <v>382.2</v>
       </c>
       <c r="L25" t="n">
-        <v>5.15</v>
+        <v>7.48</v>
       </c>
       <c r="M25" t="n">
         <v>80</v>
@@ -2819,7 +2827,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2846,7 +2854,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2855,33 +2863,33 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>939.2</v>
+        <v>440.65</v>
       </c>
       <c r="E26" t="n">
-        <v>912.46</v>
+        <v>442.57</v>
       </c>
       <c r="F26" t="n">
-        <v>2.93</v>
+        <v>-0.43</v>
       </c>
       <c r="G26" t="n">
-        <v>886.15</v>
+        <v>437.72</v>
       </c>
       <c r="H26" t="n">
-        <v>62.5</v>
+        <v>51.24</v>
       </c>
       <c r="I26" t="n">
-        <v>3.49</v>
+        <v>0.43</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>879.1</v>
+        <v>438.5</v>
       </c>
       <c r="L26" t="n">
-        <v>6.84</v>
+        <v>0.49</v>
       </c>
       <c r="M26" t="n">
         <v>80</v>
@@ -2893,7 +2901,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2920,7 +2928,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2929,36 +2937,36 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1402.9</v>
+        <v>221.06</v>
       </c>
       <c r="E27" t="n">
-        <v>1436.48</v>
+        <v>220.16</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.34</v>
+        <v>0.41</v>
       </c>
       <c r="G27" t="n">
-        <v>1361.18</v>
+        <v>217.3</v>
       </c>
       <c r="H27" t="n">
-        <v>51.87</v>
+        <v>49.51</v>
       </c>
       <c r="I27" t="n">
-        <v>1.55</v>
+        <v>0.25</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1080.1</v>
+        <v>210.24</v>
       </c>
       <c r="L27" t="n">
-        <v>29.89</v>
+        <v>5.15</v>
       </c>
       <c r="M27" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2967,7 +2975,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2994,7 +3002,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3003,36 +3011,36 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4060</v>
+        <v>939.2</v>
       </c>
       <c r="E28" t="n">
-        <v>4038.19</v>
+        <v>912.1799999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.54</v>
+        <v>2.96</v>
       </c>
       <c r="G28" t="n">
-        <v>4083.48</v>
+        <v>885.64</v>
       </c>
       <c r="H28" t="n">
-        <v>53.37</v>
+        <v>62.96</v>
       </c>
       <c r="I28" t="n">
-        <v>0.66</v>
+        <v>3.47</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3755.1</v>
+        <v>879.1</v>
       </c>
       <c r="L28" t="n">
-        <v>8.119999999999999</v>
+        <v>6.84</v>
       </c>
       <c r="M28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3041,7 +3049,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -3068,7 +3076,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3077,33 +3085,33 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4043.2</v>
+        <v>1402.9</v>
       </c>
       <c r="E29" t="n">
-        <v>4004.06</v>
+        <v>1435.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98</v>
+        <v>-2.24</v>
       </c>
       <c r="G29" t="n">
-        <v>4119.02</v>
+        <v>1364.79</v>
       </c>
       <c r="H29" t="n">
-        <v>44.24</v>
+        <v>51.74</v>
       </c>
       <c r="I29" t="n">
-        <v>2.78</v>
+        <v>1.49</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3811.1</v>
+        <v>1080.1</v>
       </c>
       <c r="L29" t="n">
-        <v>6.09</v>
+        <v>29.89</v>
       </c>
       <c r="M29" t="n">
         <v>75</v>
@@ -3115,7 +3123,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
+          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -3142,7 +3150,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3151,33 +3159,33 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>591.55</v>
+        <v>4060</v>
       </c>
       <c r="E30" t="n">
-        <v>581.48</v>
+        <v>4036.69</v>
       </c>
       <c r="F30" t="n">
-        <v>1.73</v>
+        <v>0.58</v>
       </c>
       <c r="G30" t="n">
-        <v>542.85</v>
+        <v>4079.02</v>
       </c>
       <c r="H30" t="n">
-        <v>59.64</v>
+        <v>53.84</v>
       </c>
       <c r="I30" t="n">
-        <v>1.12</v>
+        <v>0.65</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>450.75</v>
+        <v>3755.1</v>
       </c>
       <c r="L30" t="n">
-        <v>31.24</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>75</v>
@@ -3189,7 +3197,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -3216,7 +3224,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3225,33 +3233,33 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3428.3</v>
+        <v>4043.2</v>
       </c>
       <c r="E31" t="n">
-        <v>3354.41</v>
+        <v>4002.92</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="G31" t="n">
-        <v>3197.21</v>
+        <v>4115.86</v>
       </c>
       <c r="H31" t="n">
-        <v>59.7</v>
+        <v>44.39</v>
       </c>
       <c r="I31" t="n">
-        <v>0.41</v>
+        <v>2.24</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2896</v>
+        <v>3811.1</v>
       </c>
       <c r="L31" t="n">
-        <v>18.38</v>
+        <v>6.09</v>
       </c>
       <c r="M31" t="n">
         <v>75</v>
@@ -3263,7 +3271,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3290,7 +3298,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3299,33 +3307,33 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>118</v>
+        <v>591.55</v>
       </c>
       <c r="E32" t="n">
-        <v>115.23</v>
+        <v>580.59</v>
       </c>
       <c r="F32" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="G32" t="n">
-        <v>109.29</v>
+        <v>544.6900000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>68.73999999999999</v>
+        <v>59.55</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>98.5</v>
+        <v>450.75</v>
       </c>
       <c r="L32" t="n">
-        <v>19.8</v>
+        <v>31.24</v>
       </c>
       <c r="M32" t="n">
         <v>75</v>
@@ -3364,7 +3372,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3373,33 +3381,33 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3167.4</v>
+        <v>3428.3</v>
       </c>
       <c r="E33" t="n">
-        <v>3085.47</v>
+        <v>3354.41</v>
       </c>
       <c r="F33" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="G33" t="n">
-        <v>3099.91</v>
+        <v>3197.21</v>
       </c>
       <c r="H33" t="n">
-        <v>58.91</v>
+        <v>59.7</v>
       </c>
       <c r="I33" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2862</v>
+        <v>2896</v>
       </c>
       <c r="L33" t="n">
-        <v>10.67</v>
+        <v>18.38</v>
       </c>
       <c r="M33" t="n">
         <v>75</v>
@@ -3438,7 +3446,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3447,33 +3455,33 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2545</v>
+        <v>118</v>
       </c>
       <c r="E34" t="n">
-        <v>2478.76</v>
+        <v>115.23</v>
       </c>
       <c r="F34" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="G34" t="n">
-        <v>2340.14</v>
+        <v>109.29</v>
       </c>
       <c r="H34" t="n">
-        <v>63.59</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2013</v>
+        <v>98.5</v>
       </c>
       <c r="L34" t="n">
-        <v>26.43</v>
+        <v>19.8</v>
       </c>
       <c r="M34" t="n">
         <v>75</v>
@@ -3512,7 +3520,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3521,45 +3529,45 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>569.85</v>
+        <v>3167.4</v>
       </c>
       <c r="E35" t="n">
-        <v>582.21</v>
+        <v>3083.74</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.12</v>
+        <v>2.71</v>
       </c>
       <c r="G35" t="n">
-        <v>540.83</v>
+        <v>3096.47</v>
       </c>
       <c r="H35" t="n">
-        <v>53.78</v>
+        <v>59.25</v>
       </c>
       <c r="I35" t="n">
-        <v>0.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>548.8</v>
+        <v>2862</v>
       </c>
       <c r="L35" t="n">
-        <v>3.84</v>
+        <v>10.67</v>
       </c>
       <c r="M35" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -3586,7 +3594,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3595,45 +3603,45 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>561.9</v>
+        <v>2545</v>
       </c>
       <c r="E36" t="n">
-        <v>571.86</v>
+        <v>2476.31</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.74</v>
+        <v>2.77</v>
       </c>
       <c r="G36" t="n">
-        <v>547.61</v>
+        <v>2340.39</v>
       </c>
       <c r="H36" t="n">
-        <v>50.66</v>
+        <v>63.96</v>
       </c>
       <c r="I36" t="n">
-        <v>1.01</v>
+        <v>0.57</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>557.8</v>
+        <v>2013</v>
       </c>
       <c r="L36" t="n">
-        <v>0.74</v>
+        <v>26.43</v>
       </c>
       <c r="M36" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -3660,7 +3668,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3669,33 +3677,33 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1344.4</v>
+        <v>569.85</v>
       </c>
       <c r="E37" t="n">
-        <v>1359.51</v>
+        <v>582.21</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.11</v>
+        <v>-2.12</v>
       </c>
       <c r="G37" t="n">
-        <v>1332.85</v>
+        <v>540.83</v>
       </c>
       <c r="H37" t="n">
-        <v>50.88</v>
+        <v>53.78</v>
       </c>
       <c r="I37" t="n">
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1305</v>
+        <v>548.8</v>
       </c>
       <c r="L37" t="n">
-        <v>3.02</v>
+        <v>3.84</v>
       </c>
       <c r="M37" t="n">
         <v>70</v>
@@ -3734,7 +3742,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3743,22 +3751,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27060</v>
+        <v>561.9</v>
       </c>
       <c r="E38" t="n">
-        <v>27350.75</v>
+        <v>571.86</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.06</v>
+        <v>-1.74</v>
       </c>
       <c r="G38" t="n">
-        <v>26943.3</v>
+        <v>547.61</v>
       </c>
       <c r="H38" t="n">
-        <v>42.71</v>
+        <v>50.66</v>
       </c>
       <c r="I38" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3766,10 +3774,10 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>27000</v>
+        <v>557.8</v>
       </c>
       <c r="L38" t="n">
-        <v>0.22</v>
+        <v>0.74</v>
       </c>
       <c r="M38" t="n">
         <v>70</v>
@@ -3781,7 +3789,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3808,7 +3816,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3817,33 +3825,33 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>331.55</v>
+        <v>1344.4</v>
       </c>
       <c r="E39" t="n">
-        <v>333.74</v>
+        <v>1359.51</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.66</v>
+        <v>-1.11</v>
       </c>
       <c r="G39" t="n">
-        <v>329.74</v>
+        <v>1332.85</v>
       </c>
       <c r="H39" t="n">
-        <v>44.42</v>
+        <v>50.88</v>
       </c>
       <c r="I39" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>330.25</v>
+        <v>1305</v>
       </c>
       <c r="L39" t="n">
-        <v>0.39</v>
+        <v>3.02</v>
       </c>
       <c r="M39" t="n">
         <v>70</v>
@@ -3855,7 +3863,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3882,7 +3890,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3891,33 +3899,33 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>825.1</v>
+        <v>27060</v>
       </c>
       <c r="E40" t="n">
-        <v>826.87</v>
+        <v>27340.9</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.21</v>
+        <v>-1.03</v>
       </c>
       <c r="G40" t="n">
-        <v>815.9299999999999</v>
+        <v>26978.6</v>
       </c>
       <c r="H40" t="n">
-        <v>48.36</v>
+        <v>42.24</v>
       </c>
       <c r="I40" t="n">
-        <v>0.71</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>811.8</v>
+        <v>27000</v>
       </c>
       <c r="L40" t="n">
-        <v>1.64</v>
+        <v>0.22</v>
       </c>
       <c r="M40" t="n">
         <v>70</v>
@@ -3929,7 +3937,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3956,7 +3964,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3965,33 +3973,33 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6696</v>
+        <v>331.55</v>
       </c>
       <c r="E41" t="n">
-        <v>6659.96</v>
+        <v>333.74</v>
       </c>
       <c r="F41" t="n">
-        <v>0.54</v>
+        <v>-0.66</v>
       </c>
       <c r="G41" t="n">
-        <v>7006.07</v>
+        <v>329.74</v>
       </c>
       <c r="H41" t="n">
-        <v>39.57</v>
+        <v>44.42</v>
       </c>
       <c r="I41" t="n">
-        <v>0.66</v>
+        <v>0.32</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5673</v>
+        <v>330.25</v>
       </c>
       <c r="L41" t="n">
-        <v>18.03</v>
+        <v>0.39</v>
       </c>
       <c r="M41" t="n">
         <v>70</v>
@@ -4003,7 +4011,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -4030,7 +4038,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4039,33 +4047,33 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>287.3</v>
+        <v>825.1</v>
       </c>
       <c r="E42" t="n">
-        <v>283.54</v>
+        <v>826.27</v>
       </c>
       <c r="F42" t="n">
-        <v>1.32</v>
+        <v>-0.14</v>
       </c>
       <c r="G42" t="n">
-        <v>324.36</v>
+        <v>816.61</v>
       </c>
       <c r="H42" t="n">
-        <v>31.65</v>
+        <v>48.48</v>
       </c>
       <c r="I42" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>208.63</v>
+        <v>811.8</v>
       </c>
       <c r="L42" t="n">
-        <v>37.71</v>
+        <v>1.64</v>
       </c>
       <c r="M42" t="n">
         <v>70</v>
@@ -4077,7 +4085,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4113,33 +4121,33 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>531.15</v>
+        <v>6696</v>
       </c>
       <c r="E43" t="n">
-        <v>521.38</v>
+        <v>6663.26</v>
       </c>
       <c r="F43" t="n">
-        <v>1.87</v>
+        <v>0.49</v>
       </c>
       <c r="G43" t="n">
-        <v>510.3</v>
+        <v>7000.76</v>
       </c>
       <c r="H43" t="n">
-        <v>61.67</v>
+        <v>39.53</v>
       </c>
       <c r="I43" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>487.9</v>
+        <v>5673</v>
       </c>
       <c r="L43" t="n">
-        <v>8.859999999999999</v>
+        <v>18.03</v>
       </c>
       <c r="M43" t="n">
         <v>70</v>
@@ -4151,7 +4159,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -4178,7 +4186,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4187,33 +4195,33 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4057</v>
+        <v>287.3</v>
       </c>
       <c r="E44" t="n">
-        <v>3978.76</v>
+        <v>283.54</v>
       </c>
       <c r="F44" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="G44" t="n">
-        <v>3998.81</v>
+        <v>324.36</v>
       </c>
       <c r="H44" t="n">
-        <v>58.6</v>
+        <v>31.65</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>3720</v>
+        <v>208.63</v>
       </c>
       <c r="L44" t="n">
-        <v>9.06</v>
+        <v>37.71</v>
       </c>
       <c r="M44" t="n">
         <v>70</v>
@@ -4225,7 +4233,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -4252,7 +4260,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4261,33 +4269,33 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1992.1</v>
+        <v>531.15</v>
       </c>
       <c r="E45" t="n">
-        <v>1947.98</v>
+        <v>521.24</v>
       </c>
       <c r="F45" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>1903.73</v>
+        <v>509.7</v>
       </c>
       <c r="H45" t="n">
-        <v>61.25</v>
+        <v>61.84</v>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1901.3</v>
+        <v>487.9</v>
       </c>
       <c r="L45" t="n">
-        <v>4.78</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>70</v>
@@ -4299,7 +4307,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4335,36 +4343,36 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>382.05</v>
+        <v>4057</v>
       </c>
       <c r="E46" t="n">
-        <v>390.64</v>
+        <v>3978.76</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.2</v>
+        <v>1.97</v>
       </c>
       <c r="G46" t="n">
-        <v>384.62</v>
+        <v>3998.81</v>
       </c>
       <c r="H46" t="n">
-        <v>50.89</v>
+        <v>58.6</v>
       </c>
       <c r="I46" t="n">
-        <v>2.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>367.85</v>
+        <v>3720</v>
       </c>
       <c r="L46" t="n">
-        <v>3.86</v>
+        <v>9.06</v>
       </c>
       <c r="M46" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4373,7 +4381,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -4400,7 +4408,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4409,36 +4417,36 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>36750</v>
+        <v>1992.1</v>
       </c>
       <c r="E47" t="n">
-        <v>36917.68</v>
+        <v>1947.98</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.45</v>
+        <v>2.26</v>
       </c>
       <c r="G47" t="n">
-        <v>39986.8</v>
+        <v>1903.73</v>
       </c>
       <c r="H47" t="n">
-        <v>30.7</v>
+        <v>61.25</v>
       </c>
       <c r="I47" t="n">
-        <v>3.94</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>36410</v>
+        <v>1901.3</v>
       </c>
       <c r="L47" t="n">
-        <v>0.93</v>
+        <v>4.78</v>
       </c>
       <c r="M47" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4447,7 +4455,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4474,7 +4482,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4483,33 +4491,33 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7222</v>
+        <v>382.05</v>
       </c>
       <c r="E48" t="n">
-        <v>7252.02</v>
+        <v>390.64</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.41</v>
+        <v>-2.2</v>
       </c>
       <c r="G48" t="n">
-        <v>7557.64</v>
+        <v>384.62</v>
       </c>
       <c r="H48" t="n">
-        <v>43.57</v>
+        <v>50.89</v>
       </c>
       <c r="I48" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>6951</v>
+        <v>367.85</v>
       </c>
       <c r="L48" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="M48" t="n">
         <v>65</v>
@@ -4521,7 +4529,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -4548,7 +4556,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4557,33 +4565,33 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3275.8</v>
+        <v>36750</v>
       </c>
       <c r="E49" t="n">
-        <v>3274.08</v>
+        <v>36914.43</v>
       </c>
       <c r="F49" t="n">
-        <v>0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="G49" t="n">
-        <v>3359.19</v>
+        <v>40027.4</v>
       </c>
       <c r="H49" t="n">
-        <v>52.08</v>
+        <v>30.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0.66</v>
+        <v>3.9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>3164.7</v>
+        <v>36410</v>
       </c>
       <c r="L49" t="n">
-        <v>3.51</v>
+        <v>0.93</v>
       </c>
       <c r="M49" t="n">
         <v>65</v>
@@ -4595,7 +4603,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -4622,7 +4630,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4631,33 +4639,33 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>929</v>
+        <v>7222</v>
       </c>
       <c r="E50" t="n">
-        <v>919.79</v>
+        <v>7246.59</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>-0.34</v>
       </c>
       <c r="G50" t="n">
-        <v>957.1</v>
+        <v>7550.01</v>
       </c>
       <c r="H50" t="n">
-        <v>46.17</v>
+        <v>43.66</v>
       </c>
       <c r="I50" t="n">
-        <v>1.11</v>
+        <v>2.61</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>879.1</v>
+        <v>6951</v>
       </c>
       <c r="L50" t="n">
-        <v>5.68</v>
+        <v>3.9</v>
       </c>
       <c r="M50" t="n">
         <v>65</v>
@@ -4669,7 +4677,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -4696,7 +4704,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4705,33 +4713,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>101.51</v>
+        <v>3275.8</v>
       </c>
       <c r="E51" t="n">
-        <v>100.34</v>
+        <v>3274.7</v>
       </c>
       <c r="F51" t="n">
-        <v>1.17</v>
+        <v>0.03</v>
       </c>
       <c r="G51" t="n">
-        <v>108.13</v>
+        <v>3349.23</v>
       </c>
       <c r="H51" t="n">
-        <v>32.22</v>
+        <v>52.49</v>
       </c>
       <c r="I51" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>92.3</v>
+        <v>3164.7</v>
       </c>
       <c r="L51" t="n">
-        <v>9.98</v>
+        <v>3.51</v>
       </c>
       <c r="M51" t="n">
         <v>65</v>
@@ -4743,7 +4751,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -4770,7 +4778,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4779,33 +4787,33 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>762.25</v>
+        <v>929</v>
       </c>
       <c r="E52" t="n">
-        <v>748.01</v>
+        <v>919.23</v>
       </c>
       <c r="F52" t="n">
-        <v>1.9</v>
+        <v>1.06</v>
       </c>
       <c r="G52" t="n">
-        <v>782.6</v>
+        <v>956.63</v>
       </c>
       <c r="H52" t="n">
-        <v>40.86</v>
+        <v>46.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>720</v>
+        <v>879.1</v>
       </c>
       <c r="L52" t="n">
-        <v>5.87</v>
+        <v>5.68</v>
       </c>
       <c r="M52" t="n">
         <v>65</v>
@@ -4844,7 +4852,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4853,33 +4861,33 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>345.9</v>
+        <v>101.51</v>
       </c>
       <c r="E53" t="n">
-        <v>338.21</v>
+        <v>100.4</v>
       </c>
       <c r="F53" t="n">
-        <v>2.27</v>
+        <v>1.1</v>
       </c>
       <c r="G53" t="n">
-        <v>352.93</v>
+        <v>108.19</v>
       </c>
       <c r="H53" t="n">
-        <v>46.73</v>
+        <v>31.86</v>
       </c>
       <c r="I53" t="n">
-        <v>0.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>326</v>
+        <v>92.3</v>
       </c>
       <c r="L53" t="n">
-        <v>6.1</v>
+        <v>9.98</v>
       </c>
       <c r="M53" t="n">
         <v>65</v>
@@ -4918,7 +4926,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4927,36 +4935,36 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>391.15</v>
+        <v>762.25</v>
       </c>
       <c r="E54" t="n">
-        <v>401.48</v>
+        <v>748.01</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.57</v>
+        <v>1.9</v>
       </c>
       <c r="G54" t="n">
-        <v>391.15</v>
+        <v>782.6</v>
       </c>
       <c r="H54" t="n">
-        <v>51.08</v>
+        <v>40.86</v>
       </c>
       <c r="I54" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>368.4</v>
+        <v>720</v>
       </c>
       <c r="L54" t="n">
-        <v>6.18</v>
+        <v>5.87</v>
       </c>
       <c r="M54" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4965,7 +4973,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4992,7 +5000,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5001,36 +5009,36 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11619</v>
+        <v>345.9</v>
       </c>
       <c r="E55" t="n">
-        <v>11791.94</v>
+        <v>338.29</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.47</v>
+        <v>2.25</v>
       </c>
       <c r="G55" t="n">
-        <v>11599.76</v>
+        <v>352.63</v>
       </c>
       <c r="H55" t="n">
-        <v>43.34</v>
+        <v>46.4</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>11570</v>
+        <v>326</v>
       </c>
       <c r="L55" t="n">
-        <v>0.42</v>
+        <v>6.1</v>
       </c>
       <c r="M55" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5039,7 +5047,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -5152,16 +5160,16 @@
         <v>186.82</v>
       </c>
       <c r="E57" t="n">
-        <v>185.97</v>
+        <v>185.9</v>
       </c>
       <c r="F57" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G57" t="n">
-        <v>185.43</v>
+        <v>185.46</v>
       </c>
       <c r="H57" t="n">
-        <v>49.61</v>
+        <v>49.53</v>
       </c>
       <c r="I57" t="n">
         <v>0.45</v>
@@ -5226,19 +5234,19 @@
         <v>1138.7</v>
       </c>
       <c r="E58" t="n">
-        <v>1118.47</v>
+        <v>1117.67</v>
       </c>
       <c r="F58" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="G58" t="n">
-        <v>1127.48</v>
+        <v>1128.11</v>
       </c>
       <c r="H58" t="n">
-        <v>56.06</v>
+        <v>56.14</v>
       </c>
       <c r="I58" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -5300,19 +5308,19 @@
         <v>5580</v>
       </c>
       <c r="E59" t="n">
-        <v>5469.4</v>
+        <v>5468.01</v>
       </c>
       <c r="F59" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="G59" t="n">
-        <v>5067.93</v>
+        <v>5078.14</v>
       </c>
       <c r="H59" t="n">
-        <v>64.68000000000001</v>
+        <v>64.52</v>
       </c>
       <c r="I59" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -5584,7 +5592,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5593,22 +5601,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1397.4</v>
+        <v>1718.1</v>
       </c>
       <c r="E63" t="n">
-        <v>1408.24</v>
+        <v>1730.7</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.77</v>
+        <v>-0.73</v>
       </c>
       <c r="G63" t="n">
-        <v>1433.57</v>
+        <v>1863.63</v>
       </c>
       <c r="H63" t="n">
-        <v>46.45</v>
+        <v>37.48</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5616,10 +5624,10 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>1385.2</v>
+        <v>1714.4</v>
       </c>
       <c r="L63" t="n">
-        <v>0.88</v>
+        <v>0.22</v>
       </c>
       <c r="M63" t="n">
         <v>55</v>
@@ -5658,7 +5666,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5667,22 +5675,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1718.1</v>
+        <v>1397.4</v>
       </c>
       <c r="E64" t="n">
-        <v>1730.7</v>
+        <v>1406.72</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.73</v>
+        <v>-0.66</v>
       </c>
       <c r="G64" t="n">
-        <v>1863.63</v>
+        <v>1434.81</v>
       </c>
       <c r="H64" t="n">
-        <v>37.48</v>
+        <v>46.82</v>
       </c>
       <c r="I64" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -5690,10 +5698,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1714.4</v>
+        <v>1385.2</v>
       </c>
       <c r="L64" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="M64" t="n">
         <v>55</v>
@@ -5744,16 +5752,16 @@
         <v>2235</v>
       </c>
       <c r="E65" t="n">
-        <v>2242.97</v>
+        <v>2245.45</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.36</v>
+        <v>-0.47</v>
       </c>
       <c r="G65" t="n">
-        <v>2378.4</v>
+        <v>2381.35</v>
       </c>
       <c r="H65" t="n">
-        <v>30.68</v>
+        <v>29.9</v>
       </c>
       <c r="I65" t="n">
         <v>0.5</v>
@@ -5892,19 +5900,19 @@
         <v>622.95</v>
       </c>
       <c r="E67" t="n">
-        <v>618.66</v>
+        <v>618.67</v>
       </c>
       <c r="F67" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>675.8</v>
+        <v>675.37</v>
       </c>
       <c r="H67" t="n">
-        <v>34.17</v>
+        <v>34.35</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -5966,19 +5974,19 @@
         <v>64.34999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>63.45</v>
+        <v>63.43</v>
       </c>
       <c r="F68" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="G68" t="n">
-        <v>66.11</v>
+        <v>66</v>
       </c>
       <c r="H68" t="n">
-        <v>51.35</v>
+        <v>51.7</v>
       </c>
       <c r="I68" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6114,19 +6122,19 @@
         <v>498.2</v>
       </c>
       <c r="E70" t="n">
-        <v>486.42</v>
+        <v>486.35</v>
       </c>
       <c r="F70" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G70" t="n">
-        <v>505.47</v>
+        <v>506.04</v>
       </c>
       <c r="H70" t="n">
-        <v>45.58</v>
+        <v>45.65</v>
       </c>
       <c r="I70" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6188,16 +6196,16 @@
         <v>1091.5</v>
       </c>
       <c r="E71" t="n">
-        <v>1122.7</v>
+        <v>1122.84</v>
       </c>
       <c r="F71" t="n">
-        <v>-2.78</v>
+        <v>-2.79</v>
       </c>
       <c r="G71" t="n">
-        <v>1083.72</v>
+        <v>1082.14</v>
       </c>
       <c r="H71" t="n">
-        <v>51.16</v>
+        <v>50.85</v>
       </c>
       <c r="I71" t="n">
         <v>0.53</v>
@@ -6336,19 +6344,19 @@
         <v>1559.2</v>
       </c>
       <c r="E73" t="n">
-        <v>1606.09</v>
+        <v>1606.66</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.92</v>
+        <v>-2.95</v>
       </c>
       <c r="G73" t="n">
-        <v>1632.83</v>
+        <v>1635.71</v>
       </c>
       <c r="H73" t="n">
-        <v>42.46</v>
+        <v>42.24</v>
       </c>
       <c r="I73" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -6410,16 +6418,16 @@
         <v>1284.5</v>
       </c>
       <c r="E74" t="n">
-        <v>1318.87</v>
+        <v>1320.33</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.61</v>
+        <v>-2.71</v>
       </c>
       <c r="G74" t="n">
-        <v>1405.23</v>
+        <v>1402.96</v>
       </c>
       <c r="H74" t="n">
-        <v>34.87</v>
+        <v>35.75</v>
       </c>
       <c r="I74" t="n">
         <v>0.51</v>
@@ -6472,7 +6480,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6481,33 +6489,33 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>275.4</v>
+        <v>391.15</v>
       </c>
       <c r="E75" t="n">
-        <v>281.72</v>
+        <v>401.27</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.24</v>
+        <v>-2.52</v>
       </c>
       <c r="G75" t="n">
-        <v>306.53</v>
+        <v>391.41</v>
       </c>
       <c r="H75" t="n">
-        <v>32.01</v>
+        <v>50.97</v>
       </c>
       <c r="I75" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>271.65</v>
+        <v>368.4</v>
       </c>
       <c r="L75" t="n">
-        <v>1.38</v>
+        <v>6.18</v>
       </c>
       <c r="M75" t="n">
         <v>45</v>
@@ -6519,7 +6527,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
+          <t>within 3% of 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -6546,7 +6554,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6555,33 +6563,33 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>686.95</v>
+        <v>275.4</v>
       </c>
       <c r="E76" t="n">
-        <v>702.47</v>
+        <v>281.91</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.21</v>
+        <v>-2.31</v>
       </c>
       <c r="G76" t="n">
-        <v>705.49</v>
+        <v>305.75</v>
       </c>
       <c r="H76" t="n">
-        <v>45.48</v>
+        <v>31.51</v>
       </c>
       <c r="I76" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>657</v>
+        <v>271.65</v>
       </c>
       <c r="L76" t="n">
-        <v>4.56</v>
+        <v>1.38</v>
       </c>
       <c r="M76" t="n">
         <v>45</v>
@@ -6620,7 +6628,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6629,33 +6637,33 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>580.8</v>
+        <v>686.95</v>
       </c>
       <c r="E77" t="n">
-        <v>591.41</v>
+        <v>702.47</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.79</v>
+        <v>-2.21</v>
       </c>
       <c r="G77" t="n">
-        <v>589.87</v>
+        <v>705.49</v>
       </c>
       <c r="H77" t="n">
-        <v>48.08</v>
+        <v>45.48</v>
       </c>
       <c r="I77" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>578.5</v>
+        <v>657</v>
       </c>
       <c r="L77" t="n">
-        <v>0.4</v>
+        <v>4.56</v>
       </c>
       <c r="M77" t="n">
         <v>45</v>
@@ -6694,7 +6702,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6703,33 +6711,33 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1832.6</v>
+        <v>580.8</v>
       </c>
       <c r="E78" t="n">
-        <v>1856.59</v>
+        <v>591.41</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.29</v>
+        <v>-1.79</v>
       </c>
       <c r="G78" t="n">
-        <v>1947.77</v>
+        <v>589.87</v>
       </c>
       <c r="H78" t="n">
-        <v>34.01</v>
+        <v>48.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1815</v>
+        <v>578.5</v>
       </c>
       <c r="L78" t="n">
-        <v>0.97</v>
+        <v>0.4</v>
       </c>
       <c r="M78" t="n">
         <v>45</v>
@@ -6768,7 +6776,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6777,22 +6785,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>572.65</v>
+        <v>11619</v>
       </c>
       <c r="E79" t="n">
-        <v>586.21</v>
+        <v>11791.8</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.31</v>
+        <v>-1.47</v>
       </c>
       <c r="G79" t="n">
-        <v>590.52</v>
+        <v>11619.58</v>
       </c>
       <c r="H79" t="n">
-        <v>46.52</v>
+        <v>42.89</v>
       </c>
       <c r="I79" t="n">
-        <v>3.63</v>
+        <v>0.68</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6800,13 +6808,13 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>560.5</v>
+        <v>11570</v>
       </c>
       <c r="L79" t="n">
-        <v>2.17</v>
+        <v>0.42</v>
       </c>
       <c r="M79" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -6815,7 +6823,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -6842,7 +6850,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6851,36 +6859,36 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2733.5</v>
+        <v>1832.6</v>
       </c>
       <c r="E80" t="n">
-        <v>2779.47</v>
+        <v>1857.86</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.65</v>
+        <v>-1.36</v>
       </c>
       <c r="G80" t="n">
-        <v>2960.46</v>
+        <v>1948.97</v>
       </c>
       <c r="H80" t="n">
-        <v>40.61</v>
+        <v>33.18</v>
       </c>
       <c r="I80" t="n">
-        <v>1.65</v>
+        <v>0.59</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>2685</v>
+        <v>1815</v>
       </c>
       <c r="L80" t="n">
-        <v>1.81</v>
+        <v>0.97</v>
       </c>
       <c r="M80" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -6889,7 +6897,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -6916,7 +6924,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6925,33 +6933,33 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>174.55</v>
+        <v>572.65</v>
       </c>
       <c r="E81" t="n">
-        <v>172.91</v>
+        <v>585.89</v>
       </c>
       <c r="F81" t="n">
-        <v>0.95</v>
+        <v>-2.26</v>
       </c>
       <c r="G81" t="n">
-        <v>194.58</v>
+        <v>589.6799999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>40.52</v>
+        <v>46.83</v>
       </c>
       <c r="I81" t="n">
-        <v>0.13</v>
+        <v>3.66</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>171</v>
+        <v>560.5</v>
       </c>
       <c r="L81" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="M81" t="n">
         <v>35</v>
@@ -6963,7 +6971,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -6990,7 +6998,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6999,33 +7007,33 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>208.64</v>
+        <v>2733.5</v>
       </c>
       <c r="E82" t="n">
-        <v>203.14</v>
+        <v>2780.66</v>
       </c>
       <c r="F82" t="n">
-        <v>2.71</v>
+        <v>-1.7</v>
       </c>
       <c r="G82" t="n">
-        <v>211.78</v>
+        <v>2965.3</v>
       </c>
       <c r="H82" t="n">
-        <v>45.38</v>
+        <v>40.55</v>
       </c>
       <c r="I82" t="n">
-        <v>0.34</v>
+        <v>1.67</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>200.74</v>
+        <v>2685</v>
       </c>
       <c r="L82" t="n">
-        <v>3.94</v>
+        <v>1.81</v>
       </c>
       <c r="M82" t="n">
         <v>35</v>
@@ -7037,7 +7045,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -7064,7 +7072,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7073,36 +7081,36 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>442.7</v>
+        <v>174.55</v>
       </c>
       <c r="E83" t="n">
-        <v>452.25</v>
+        <v>172.91</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.11</v>
+        <v>0.95</v>
       </c>
       <c r="G83" t="n">
-        <v>459.79</v>
+        <v>194.58</v>
       </c>
       <c r="H83" t="n">
-        <v>42.83</v>
+        <v>40.52</v>
       </c>
       <c r="I83" t="n">
-        <v>0.51</v>
+        <v>0.13</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>441.35</v>
+        <v>171</v>
       </c>
       <c r="L83" t="n">
-        <v>0.31</v>
+        <v>2.08</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -7111,7 +7119,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
+          <t>at/above 200DMA; above breakdown low</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -7138,7 +7146,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7147,36 +7155,36 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>76.90000000000001</v>
+        <v>208.64</v>
       </c>
       <c r="E84" t="n">
-        <v>78.41</v>
+        <v>203.14</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.93</v>
+        <v>2.71</v>
       </c>
       <c r="G84" t="n">
-        <v>78.06</v>
+        <v>211.78</v>
       </c>
       <c r="H84" t="n">
-        <v>42.14</v>
+        <v>45.38</v>
       </c>
       <c r="I84" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>76</v>
+        <v>200.74</v>
       </c>
       <c r="L84" t="n">
-        <v>1.18</v>
+        <v>3.94</v>
       </c>
       <c r="M84" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -7185,7 +7193,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
+          <t>at/above 200DMA; above breakdown low</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -7212,7 +7220,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7221,33 +7229,33 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>667.3</v>
+        <v>442.7</v>
       </c>
       <c r="E85" t="n">
-        <v>679.91</v>
+        <v>452.01</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.86</v>
+        <v>-2.06</v>
       </c>
       <c r="G85" t="n">
-        <v>669.54</v>
+        <v>459.21</v>
       </c>
       <c r="H85" t="n">
-        <v>47.49</v>
+        <v>43.71</v>
       </c>
       <c r="I85" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>664.2</v>
+        <v>441.35</v>
       </c>
       <c r="L85" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="M85" t="n">
         <v>25</v>
@@ -7280,6 +7288,154 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="E86" t="n">
+        <v>78.41</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="G86" t="n">
+        <v>78.06</v>
+      </c>
+      <c r="H86" t="n">
+        <v>42.14</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>76</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M86" t="n">
+        <v>25</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>NEAR 200DMA</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TATAINVEST</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>667.3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>679.91</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="G87" t="n">
+        <v>669.54</v>
+      </c>
+      <c r="H87" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>664.2</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M87" t="n">
+        <v>25</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>NEAR 200DMA</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/NSE_200DMA_Recovery_Scanner.xlsx
+++ b/output/NSE_200DMA_Recovery_Scanner.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF87"/>
+  <dimension ref="A1:AF84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,19 +596,19 @@
         <v>3558.9</v>
       </c>
       <c r="E2" t="n">
-        <v>3582.53</v>
+        <v>3584.28</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.66</v>
+        <v>-0.71</v>
       </c>
       <c r="G2" t="n">
-        <v>3423.6</v>
+        <v>3426.33</v>
       </c>
       <c r="H2" t="n">
-        <v>58.92</v>
+        <v>58.73</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>43.10161</v>
+        <v>43.866634</v>
       </c>
       <c r="Q2" t="n">
         <v>7.3281016</v>
       </c>
       <c r="R2" t="n">
-        <v>82.56999999999999</v>
+        <v>81.13</v>
       </c>
       <c r="S2" t="n">
         <v>101</v>
@@ -694,19 +694,19 @@
         <v>278.12</v>
       </c>
       <c r="E3" t="n">
-        <v>279.93</v>
+        <v>279.51</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.65</v>
+        <v>-0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>251.79</v>
+        <v>251.14</v>
       </c>
       <c r="H3" t="n">
-        <v>73.93000000000001</v>
+        <v>74.72</v>
       </c>
       <c r="I3" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>15.847294</v>
+        <v>16.283373</v>
       </c>
       <c r="Q3" t="n">
         <v>4.646485</v>
       </c>
       <c r="R3" t="n">
-        <v>17.55</v>
+        <v>17.08</v>
       </c>
       <c r="S3" t="n">
         <v>108</v>
@@ -842,7 +842,9 @@
       <c r="S4" t="n">
         <v>204</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>1008188391424</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
@@ -938,7 +940,9 @@
       <c r="S5" t="n">
         <v>24</v>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>331533746176</v>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
@@ -1084,19 +1088,19 @@
         <v>1621.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1618.73</v>
+        <v>1617.58</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1536.2</v>
+        <v>1538.94</v>
       </c>
       <c r="H7" t="n">
-        <v>56.61</v>
+        <v>56.52</v>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1123,13 +1127,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>42.920307</v>
+        <v>44.43805</v>
       </c>
       <c r="Q7" t="n">
         <v>11.312315</v>
       </c>
       <c r="R7" t="n">
-        <v>37.77</v>
+        <v>36.48</v>
       </c>
       <c r="S7" t="n">
         <v>111</v>
@@ -1230,7 +1234,7 @@
         <v>11.75</v>
       </c>
       <c r="S8" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="T8" t="n">
         <v>222470488064</v>
@@ -1274,45 +1278,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>951.7</v>
+        <v>826.9</v>
       </c>
       <c r="E9" t="n">
-        <v>944.37</v>
+        <v>818.76</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="G9" t="n">
-        <v>917.52</v>
+        <v>767.6</v>
       </c>
       <c r="H9" t="n">
-        <v>56.78</v>
+        <v>55.54</v>
       </c>
       <c r="I9" t="n">
-        <v>3.89</v>
+        <v>0.65</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>903.25</v>
+        <v>738.9</v>
       </c>
       <c r="L9" t="n">
-        <v>5.36</v>
+        <v>11.91</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1321,55 +1325,47 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>14.144872</v>
+        <v>58.479492</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.753955</v>
+        <v>9.402361000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="S9" t="n">
-        <v>68</v>
-      </c>
+        <v>14.14</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>161763082240</v>
-      </c>
-      <c r="U9" t="n">
-        <v>16.853</v>
-      </c>
+        <v>188056174592</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>10.4449995</v>
+        <v>18.441999</v>
       </c>
       <c r="X9" t="n">
-        <v>34.782</v>
+        <v>14.681</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.742</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.006</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.791</v>
-      </c>
+        <v>42.585</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>-39.6</v>
+        <v>24</v>
       </c>
       <c r="AD9" t="n">
-        <v>-34.1</v>
+        <v>-20.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>-34.1</v>
+        <v>-20.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -1378,7 +1374,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1387,33 +1383,33 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1703.8</v>
+        <v>4874.8</v>
       </c>
       <c r="E10" t="n">
-        <v>1754.54</v>
+        <v>4811.81</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.89</v>
+        <v>1.31</v>
       </c>
       <c r="G10" t="n">
-        <v>1661.3</v>
+        <v>4640.3</v>
       </c>
       <c r="H10" t="n">
-        <v>63.24</v>
+        <v>57.37</v>
       </c>
       <c r="I10" t="n">
-        <v>1.93</v>
+        <v>0.33</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1473</v>
+        <v>4360.1</v>
       </c>
       <c r="L10" t="n">
-        <v>15.67</v>
+        <v>11.8</v>
       </c>
       <c r="M10" t="n">
         <v>95</v>
@@ -1425,55 +1421,49 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>454.34668</v>
+        <v>31.055614</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7868536</v>
+        <v>5.306124</v>
       </c>
       <c r="R10" t="n">
-        <v>3.75</v>
+        <v>156.97</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="T10" t="n">
-        <v>128002572288</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5.939</v>
-      </c>
+        <v>223011028992</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>6.630999999999999</v>
+        <v>35.718</v>
       </c>
       <c r="X10" t="n">
-        <v>8.4309995</v>
+        <v>28.608</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.693</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.715</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.845</v>
-      </c>
+        <v>1.671</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>-63.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="AE10" t="n">
-        <v>-63.6</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -1482,7 +1472,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1491,33 +1481,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1298</v>
+        <v>821.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1310.76</v>
+        <v>810.67</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.97</v>
+        <v>1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>1208.71</v>
+        <v>771.58</v>
       </c>
       <c r="H11" t="n">
-        <v>67.19</v>
+        <v>63.16</v>
       </c>
       <c r="I11" t="n">
-        <v>0.82</v>
+        <v>0.58</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1123.6</v>
+        <v>652</v>
       </c>
       <c r="L11" t="n">
-        <v>15.52</v>
+        <v>26</v>
       </c>
       <c r="M11" t="n">
         <v>95</v>
@@ -1533,45 +1523,45 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>37.4601</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.610682000000001</v>
+        <v>5.515607</v>
       </c>
       <c r="R11" t="n">
-        <v>25.96</v>
+        <v>21.93</v>
       </c>
       <c r="S11" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="T11" t="n">
-        <v>814575058944</v>
+        <v>87311089664</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>5.302</v>
+        <v>28.083</v>
       </c>
       <c r="X11" t="n">
-        <v>6.923</v>
+        <v>23.719</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.801</v>
+        <v>0.135</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>-16.6</v>
+        <v>4.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>-16.6</v>
+        <v>4.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -1580,7 +1570,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>CEATLTD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1589,33 +1579,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>826.9</v>
+        <v>3688.8</v>
       </c>
       <c r="E12" t="n">
-        <v>818.42</v>
+        <v>3639.73</v>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G12" t="n">
-        <v>771.08</v>
+        <v>3549.95</v>
       </c>
       <c r="H12" t="n">
-        <v>55.32</v>
+        <v>55.54</v>
       </c>
       <c r="I12" t="n">
-        <v>0.65</v>
+        <v>0.19</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>738.9</v>
+        <v>3309.1</v>
       </c>
       <c r="L12" t="n">
-        <v>11.91</v>
+        <v>11.47</v>
       </c>
       <c r="M12" t="n">
         <v>95</v>
@@ -1631,43 +1621,45 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>58.438168</v>
+        <v>25.264025</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.402361000000001</v>
+        <v>2.5360997</v>
       </c>
       <c r="R12" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
+        <v>146.01</v>
+      </c>
+      <c r="S12" t="n">
+        <v>95</v>
+      </c>
       <c r="T12" t="n">
-        <v>188056174592</v>
+        <v>149212299264</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>18.441999</v>
+        <v>4.145</v>
       </c>
       <c r="X12" t="n">
-        <v>14.681</v>
+        <v>3.583</v>
       </c>
       <c r="Y12" t="n">
-        <v>42.585</v>
+        <v>64.742</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>24</v>
+        <v>22.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>-20.1</v>
+        <v>-96.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>-20.1</v>
+        <v>-96.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -1676,7 +1668,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1685,36 +1677,36 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4874.8</v>
+        <v>282.6</v>
       </c>
       <c r="E13" t="n">
-        <v>4809.38</v>
+        <v>279.26</v>
       </c>
       <c r="F13" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>4647.65</v>
+        <v>278.79</v>
       </c>
       <c r="H13" t="n">
-        <v>57.07</v>
+        <v>55.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>2.54</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4360.1</v>
+        <v>273</v>
       </c>
       <c r="L13" t="n">
-        <v>11.8</v>
+        <v>3.52</v>
       </c>
       <c r="M13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1723,49 +1715,49 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>31.055614</v>
+        <v>10.078459</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.306124</v>
+        <v>1.9018266</v>
       </c>
       <c r="R13" t="n">
-        <v>156.97</v>
+        <v>28.04</v>
       </c>
       <c r="S13" t="n">
-        <v>150</v>
+        <v>354</v>
       </c>
       <c r="T13" t="n">
-        <v>223011028992</v>
+        <v>423900053504</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>35.718</v>
+        <v>24.001</v>
       </c>
       <c r="X13" t="n">
-        <v>28.608</v>
+        <v>11.3199994</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.671</v>
+        <v>10.507</v>
       </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>8.300000000000001</v>
+        <v>-53.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.600000000000001</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>6.600000000000001</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="AF13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1774,7 +1766,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CEATLTD</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1783,36 +1775,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3688.8</v>
+        <v>170.54</v>
       </c>
       <c r="E14" t="n">
-        <v>3636.48</v>
+        <v>166.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>3554.71</v>
+        <v>162.15</v>
       </c>
       <c r="H14" t="n">
-        <v>55.71</v>
+        <v>52.59</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3309.1</v>
+        <v>161.2</v>
       </c>
       <c r="L14" t="n">
-        <v>11.47</v>
+        <v>5.79</v>
       </c>
       <c r="M14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1821,49 +1813,45 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>25.264025</v>
+        <v>9.516741</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5360997</v>
+        <v>2.097534</v>
       </c>
       <c r="R14" t="n">
-        <v>146.01</v>
+        <v>17.92</v>
       </c>
       <c r="S14" t="n">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="T14" t="n">
-        <v>149212299264</v>
+        <v>298888200192</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>4.145</v>
+        <v>2.396</v>
       </c>
       <c r="X14" t="n">
-        <v>3.583</v>
+        <v>2.8670002</v>
       </c>
       <c r="Y14" t="n">
-        <v>64.742</v>
+        <v>108.059</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-96.2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-96.2</v>
-      </c>
+        <v>120.4</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1872,7 +1860,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1881,36 +1869,36 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>821.5</v>
+        <v>444.1</v>
       </c>
       <c r="E15" t="n">
-        <v>809.1</v>
+        <v>456.75</v>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>-2.77</v>
       </c>
       <c r="G15" t="n">
-        <v>770.4299999999999</v>
+        <v>428.23</v>
       </c>
       <c r="H15" t="n">
-        <v>63.78</v>
+        <v>58.97</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>652</v>
+        <v>365.3</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>21.57</v>
       </c>
       <c r="M15" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1919,49 +1907,49 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37.4601</v>
+        <v>16.472553</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.515607</v>
+        <v>1.6806881</v>
       </c>
       <c r="R15" t="n">
-        <v>21.93</v>
+        <v>26.96</v>
       </c>
       <c r="S15" t="n">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="T15" t="n">
-        <v>87311089664</v>
+        <v>280929370112</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>28.083</v>
+        <v>6.451</v>
       </c>
       <c r="X15" t="n">
-        <v>23.719</v>
+        <v>5.829</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.135</v>
+        <v>21.987</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.7</v>
+        <v>2660</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.7</v>
+        <v>2660</v>
       </c>
       <c r="AF15" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1970,7 +1958,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1979,36 +1967,36 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>282.6</v>
+        <v>94.05</v>
       </c>
       <c r="E16" t="n">
-        <v>279.26</v>
+        <v>96.66</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>-2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>278.79</v>
+        <v>92.22</v>
       </c>
       <c r="H16" t="n">
-        <v>55.2</v>
+        <v>55.99</v>
       </c>
       <c r="I16" t="n">
-        <v>2.54</v>
+        <v>0.42</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>273</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>3.52</v>
+        <v>18.15</v>
       </c>
       <c r="M16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2017,49 +2005,47 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>9.961226</v>
+        <v>21.5711</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9018266</v>
+        <v>2.7916298</v>
       </c>
       <c r="R16" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>354</v>
-      </c>
+        <v>4.36</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>423900053504</v>
+        <v>104160116736</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
-        <v>24.001</v>
+        <v>58.55099999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>11.3199994</v>
+        <v>44.877997</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.507</v>
+        <v>195.685</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>-53.2</v>
+        <v>24.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>35.09999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>35.09999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -2068,7 +2054,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2077,36 +2063,36 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>170.54</v>
+        <v>940</v>
       </c>
       <c r="E17" t="n">
-        <v>166.6</v>
+        <v>963.5599999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.36</v>
+        <v>-2.45</v>
       </c>
       <c r="G17" t="n">
-        <v>162.15</v>
+        <v>892.75</v>
       </c>
       <c r="H17" t="n">
-        <v>52.59</v>
+        <v>56.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.28</v>
+        <v>0.65</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>161.2</v>
+        <v>784.95</v>
       </c>
       <c r="L17" t="n">
-        <v>5.79</v>
+        <v>19.75</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2115,45 +2101,49 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9.516741</v>
+        <v>47.61905</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.097534</v>
+        <v>9.69312</v>
       </c>
       <c r="R17" t="n">
-        <v>17.92</v>
+        <v>19.74</v>
       </c>
       <c r="S17" t="n">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="T17" t="n">
-        <v>298888200192</v>
+        <v>162499756032</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>2.396</v>
+        <v>26.553</v>
       </c>
       <c r="X17" t="n">
-        <v>2.8670002</v>
+        <v>24.400999</v>
       </c>
       <c r="Y17" t="n">
-        <v>108.059</v>
+        <v>3.314</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+        <v>30.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
@@ -2162,7 +2152,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2171,33 +2161,33 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>444.1</v>
+        <v>1496.5</v>
       </c>
       <c r="E18" t="n">
-        <v>456.36</v>
+        <v>1530.94</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.69</v>
+        <v>-2.25</v>
       </c>
       <c r="G18" t="n">
-        <v>428.86</v>
+        <v>1443.66</v>
       </c>
       <c r="H18" t="n">
-        <v>59.27</v>
+        <v>59.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>365.3</v>
+        <v>1356.6</v>
       </c>
       <c r="L18" t="n">
-        <v>21.57</v>
+        <v>10.31</v>
       </c>
       <c r="M18" t="n">
         <v>85</v>
@@ -2213,45 +2203,51 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>16.472553</v>
+        <v>55.241787</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.6806881</v>
+        <v>6.703518</v>
       </c>
       <c r="R18" t="n">
-        <v>26.96</v>
+        <v>27.09</v>
       </c>
       <c r="S18" t="n">
-        <v>248</v>
+        <v>89</v>
       </c>
       <c r="T18" t="n">
-        <v>280929370112</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
+        <v>393700409344</v>
+      </c>
+      <c r="U18" t="n">
+        <v>12.517</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>6.451</v>
+        <v>18.714</v>
       </c>
       <c r="X18" t="n">
-        <v>5.829</v>
+        <v>14.272</v>
       </c>
       <c r="Y18" t="n">
-        <v>21.987</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+        <v>28.466</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.354</v>
+      </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>12.8</v>
+        <v>-15.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2660</v>
+        <v>-3.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>2660</v>
+        <v>-3.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2269,33 +2265,33 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.05</v>
+        <v>5558</v>
       </c>
       <c r="E19" t="n">
-        <v>96.54000000000001</v>
+        <v>5682.22</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.58</v>
+        <v>-2.19</v>
       </c>
       <c r="G19" t="n">
-        <v>92.16</v>
+        <v>5348.37</v>
       </c>
       <c r="H19" t="n">
-        <v>56.47</v>
+        <v>57.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>79.59999999999999</v>
+        <v>5035</v>
       </c>
       <c r="L19" t="n">
-        <v>18.15</v>
+        <v>10.39</v>
       </c>
       <c r="M19" t="n">
         <v>85</v>
@@ -2311,43 +2307,45 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>21.5711</v>
+        <v>51.287254</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.7916298</v>
+        <v>26.21624</v>
       </c>
       <c r="R19" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
+        <v>108.37</v>
+      </c>
+      <c r="S19" t="n">
+        <v>163</v>
+      </c>
       <c r="T19" t="n">
-        <v>104160116736</v>
+        <v>1338745946112</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>58.55099999999999</v>
+        <v>15.212</v>
       </c>
       <c r="X19" t="n">
-        <v>44.877997</v>
+        <v>13.376</v>
       </c>
       <c r="Y19" t="n">
-        <v>195.685</v>
+        <v>26.875</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>24.6</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="AF19" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -2356,7 +2354,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2365,33 +2363,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>940</v>
+        <v>737.85</v>
       </c>
       <c r="E20" t="n">
-        <v>962.38</v>
+        <v>751.37</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.33</v>
+        <v>-1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>894.14</v>
+        <v>711.95</v>
       </c>
       <c r="H20" t="n">
-        <v>56.43</v>
+        <v>55.85</v>
       </c>
       <c r="I20" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>784.95</v>
+        <v>652.25</v>
       </c>
       <c r="L20" t="n">
-        <v>19.75</v>
+        <v>13.12</v>
       </c>
       <c r="M20" t="n">
         <v>85</v>
@@ -2407,45 +2405,45 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47.61905</v>
+        <v>18.760487</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.69312</v>
+        <v>13.507057</v>
       </c>
       <c r="R20" t="n">
-        <v>19.74</v>
+        <v>39.33</v>
       </c>
       <c r="S20" t="n">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="T20" t="n">
-        <v>162499756032</v>
+        <v>607951388672</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
-        <v>26.553</v>
+        <v>9.103999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>24.400999</v>
+        <v>7.379</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.314</v>
+        <v>37.523</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>30.1</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>-2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AE20" t="n">
-        <v>-2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -2454,7 +2452,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2463,33 +2461,33 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1496.5</v>
+        <v>1298</v>
       </c>
       <c r="E21" t="n">
-        <v>1530.94</v>
+        <v>1311.85</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.25</v>
+        <v>-1.06</v>
       </c>
       <c r="G21" t="n">
-        <v>1443.66</v>
+        <v>1206.51</v>
       </c>
       <c r="H21" t="n">
-        <v>59.16</v>
+        <v>67.27</v>
       </c>
       <c r="I21" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1356.6</v>
+        <v>1123.6</v>
       </c>
       <c r="L21" t="n">
-        <v>10.31</v>
+        <v>15.52</v>
       </c>
       <c r="M21" t="n">
         <v>85</v>
@@ -2505,51 +2503,45 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>54.93759</v>
+        <v>48.778652</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.703518</v>
+        <v>8.610682000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>27.24</v>
+        <v>26.61</v>
       </c>
       <c r="S21" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="T21" t="n">
-        <v>393700409344</v>
-      </c>
-      <c r="U21" t="n">
-        <v>12.517</v>
-      </c>
+        <v>814575058944</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="n">
-        <v>18.714</v>
+        <v>5.302</v>
       </c>
       <c r="X21" t="n">
-        <v>14.272</v>
+        <v>6.923</v>
       </c>
       <c r="Y21" t="n">
-        <v>28.466</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.331</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.354</v>
-      </c>
+        <v>2.801</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>-15.6</v>
+        <v>19.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>-3.8</v>
+        <v>-16.6</v>
       </c>
       <c r="AE21" t="n">
-        <v>-3.8</v>
+        <v>-16.6</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
@@ -2558,7 +2550,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2567,36 +2559,36 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5558</v>
+        <v>144.1</v>
       </c>
       <c r="E22" t="n">
-        <v>5680</v>
+        <v>147.76</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.15</v>
+        <v>-2.47</v>
       </c>
       <c r="G22" t="n">
-        <v>5354.29</v>
+        <v>142.97</v>
       </c>
       <c r="H22" t="n">
-        <v>56.21</v>
+        <v>53.56</v>
       </c>
       <c r="I22" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>5035</v>
+        <v>135.62</v>
       </c>
       <c r="L22" t="n">
-        <v>10.39</v>
+        <v>6.25</v>
       </c>
       <c r="M22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2605,26 +2597,50 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>5.337037</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.7214199</v>
+      </c>
+      <c r="R22" t="n">
+        <v>27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>323</v>
+      </c>
+      <c r="T22" t="n">
+        <v>656039411712</v>
+      </c>
+      <c r="U22" t="n">
+        <v>13.697</v>
+      </c>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>48.535</v>
+      </c>
+      <c r="X22" t="n">
+        <v>34.992</v>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
+      <c r="AC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2632,7 +2648,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2641,36 +2657,36 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>737.85</v>
+        <v>410.8</v>
       </c>
       <c r="E23" t="n">
-        <v>751.03</v>
+        <v>419.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.75</v>
+        <v>-2.14</v>
       </c>
       <c r="G23" t="n">
-        <v>712.84</v>
+        <v>408.23</v>
       </c>
       <c r="H23" t="n">
-        <v>55.79</v>
+        <v>58.27</v>
       </c>
       <c r="I23" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>652.25</v>
+        <v>382.2</v>
       </c>
       <c r="L23" t="n">
-        <v>13.12</v>
+        <v>7.48</v>
       </c>
       <c r="M23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2679,26 +2695,50 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>49.021477</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12.517901</v>
+      </c>
+      <c r="R23" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="S23" t="n">
+        <v>61</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3002857160704</v>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>22.135</v>
+      </c>
+      <c r="X23" t="n">
+        <v>21.403</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.273</v>
+      </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2706,7 +2746,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2715,33 +2755,33 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>144.1</v>
+        <v>440.65</v>
       </c>
       <c r="E24" t="n">
-        <v>147.76</v>
+        <v>444.74</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.47</v>
+        <v>-0.92</v>
       </c>
       <c r="G24" t="n">
-        <v>142.97</v>
+        <v>437.84</v>
       </c>
       <c r="H24" t="n">
-        <v>53.56</v>
+        <v>50.99</v>
       </c>
       <c r="I24" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>135.62</v>
+        <v>438.5</v>
       </c>
       <c r="L24" t="n">
-        <v>6.25</v>
+        <v>0.49</v>
       </c>
       <c r="M24" t="n">
         <v>80</v>
@@ -2753,26 +2793,48 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>158.50719</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.3186584</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.78</v>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>168591523840</v>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-11.457</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.961</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9.928000000000001</v>
+      </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AC24" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-96.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-96.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2780,7 +2842,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2789,33 +2851,33 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>410.8</v>
+        <v>221.06</v>
       </c>
       <c r="E25" t="n">
-        <v>419.76</v>
+        <v>220.31</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.14</v>
+        <v>0.34</v>
       </c>
       <c r="G25" t="n">
-        <v>408.23</v>
+        <v>217.22</v>
       </c>
       <c r="H25" t="n">
-        <v>58.27</v>
+        <v>49.38</v>
       </c>
       <c r="I25" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>382.2</v>
+        <v>210.24</v>
       </c>
       <c r="L25" t="n">
-        <v>7.48</v>
+        <v>5.15</v>
       </c>
       <c r="M25" t="n">
         <v>80</v>
@@ -2827,26 +2889,50 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>25.438437</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.9687612</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="S25" t="n">
+        <v>253</v>
+      </c>
+      <c r="T25" t="n">
+        <v>106242269184</v>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>18.431</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16.983</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.236</v>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2854,7 +2940,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2863,33 +2949,33 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>440.65</v>
+        <v>939.2</v>
       </c>
       <c r="E26" t="n">
-        <v>442.57</v>
+        <v>912.46</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.43</v>
+        <v>2.93</v>
       </c>
       <c r="G26" t="n">
-        <v>437.72</v>
+        <v>886.15</v>
       </c>
       <c r="H26" t="n">
-        <v>51.24</v>
+        <v>62.5</v>
       </c>
       <c r="I26" t="n">
-        <v>0.43</v>
+        <v>3.49</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>438.5</v>
+        <v>879.1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.49</v>
+        <v>6.84</v>
       </c>
       <c r="M26" t="n">
         <v>80</v>
@@ -2901,26 +2987,50 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>54.039127</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6.0853057</v>
+      </c>
+      <c r="R26" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="S26" t="n">
+        <v>21</v>
+      </c>
+      <c r="T26" t="n">
+        <v>239427633152</v>
+      </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>17.254</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8.457000000000001</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>55.868</v>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AC26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2928,7 +3038,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2937,36 +3047,36 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>221.06</v>
+        <v>1402.9</v>
       </c>
       <c r="E27" t="n">
-        <v>220.16</v>
+        <v>1436.48</v>
       </c>
       <c r="F27" t="n">
-        <v>0.41</v>
+        <v>-2.34</v>
       </c>
       <c r="G27" t="n">
-        <v>217.3</v>
+        <v>1361.18</v>
       </c>
       <c r="H27" t="n">
-        <v>49.51</v>
+        <v>51.87</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25</v>
+        <v>1.55</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>210.24</v>
+        <v>1080.1</v>
       </c>
       <c r="L27" t="n">
-        <v>5.15</v>
+        <v>29.89</v>
       </c>
       <c r="M27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2975,26 +3085,48 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; above 50DMA</t>
+          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>4.1930685</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-31.85</v>
+      </c>
+      <c r="S27" t="n">
+        <v>18</v>
+      </c>
+      <c r="T27" t="n">
+        <v>155129659392</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-8.911</v>
+      </c>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-186.002</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-24.914</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>152.371</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.437</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.252</v>
+      </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3002,7 +3134,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3011,36 +3143,36 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>939.2</v>
+        <v>4060</v>
       </c>
       <c r="E28" t="n">
-        <v>912.1799999999999</v>
+        <v>4038.19</v>
       </c>
       <c r="F28" t="n">
-        <v>2.96</v>
+        <v>0.54</v>
       </c>
       <c r="G28" t="n">
-        <v>885.64</v>
+        <v>4083.48</v>
       </c>
       <c r="H28" t="n">
-        <v>62.96</v>
+        <v>53.37</v>
       </c>
       <c r="I28" t="n">
-        <v>3.47</v>
+        <v>0.66</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>879.1</v>
+        <v>3755.1</v>
       </c>
       <c r="L28" t="n">
-        <v>6.84</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3049,26 +3181,48 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>86.733604</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10.799423</v>
+      </c>
+      <c r="R28" t="n">
+        <v>46.81</v>
+      </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>2648118657024</v>
+      </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>6.447</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.2919997</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.913</v>
+      </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
+      <c r="AC28" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3076,7 +3230,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3085,33 +3239,33 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1402.9</v>
+        <v>4043.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1435.1</v>
+        <v>4004.06</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.24</v>
+        <v>0.98</v>
       </c>
       <c r="G29" t="n">
-        <v>1364.79</v>
+        <v>4119.02</v>
       </c>
       <c r="H29" t="n">
-        <v>51.74</v>
+        <v>44.24</v>
       </c>
       <c r="I29" t="n">
-        <v>1.49</v>
+        <v>2.78</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1080.1</v>
+        <v>3811.1</v>
       </c>
       <c r="L29" t="n">
-        <v>29.89</v>
+        <v>6.09</v>
       </c>
       <c r="M29" t="n">
         <v>75</v>
@@ -3123,26 +3277,56 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=10%; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>50.502125</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>10.30154</v>
+      </c>
+      <c r="R29" t="n">
+        <v>80.06</v>
+      </c>
+      <c r="S29" t="n">
+        <v>87</v>
+      </c>
+      <c r="T29" t="n">
+        <v>631966990336</v>
+      </c>
+      <c r="U29" t="n">
+        <v>21.645</v>
+      </c>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>14.774999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.9320005</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.423</v>
+      </c>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
+      <c r="AC29" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3150,7 +3334,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3159,33 +3343,33 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4060</v>
+        <v>591.55</v>
       </c>
       <c r="E30" t="n">
-        <v>4036.69</v>
+        <v>581.48</v>
       </c>
       <c r="F30" t="n">
-        <v>0.58</v>
+        <v>1.73</v>
       </c>
       <c r="G30" t="n">
-        <v>4079.02</v>
+        <v>542.85</v>
       </c>
       <c r="H30" t="n">
-        <v>53.84</v>
+        <v>59.64</v>
       </c>
       <c r="I30" t="n">
-        <v>0.65</v>
+        <v>1.12</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3755.1</v>
+        <v>450.75</v>
       </c>
       <c r="L30" t="n">
-        <v>8.119999999999999</v>
+        <v>31.24</v>
       </c>
       <c r="M30" t="n">
         <v>75</v>
@@ -3197,26 +3381,56 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>29.951899</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>28.286232</v>
+      </c>
+      <c r="R30" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>34</v>
+      </c>
+      <c r="T30" t="n">
+        <v>192941342720</v>
+      </c>
+      <c r="U30" t="n">
+        <v>10.786</v>
+      </c>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>20.204</v>
+      </c>
+      <c r="X30" t="n">
+        <v>11.311</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>84.316</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.26</v>
+      </c>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>-42.3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3224,7 +3438,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3233,33 +3447,33 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4043.2</v>
+        <v>3428.3</v>
       </c>
       <c r="E31" t="n">
-        <v>4002.92</v>
+        <v>3354.41</v>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>4115.86</v>
+        <v>3197.21</v>
       </c>
       <c r="H31" t="n">
-        <v>44.39</v>
+        <v>59.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2.24</v>
+        <v>0.41</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3811.1</v>
+        <v>2896</v>
       </c>
       <c r="L31" t="n">
-        <v>6.09</v>
+        <v>18.38</v>
       </c>
       <c r="M31" t="n">
         <v>75</v>
@@ -3271,26 +3485,50 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>20.876265</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.115483</v>
+      </c>
+      <c r="R31" t="n">
+        <v>164.22</v>
+      </c>
+      <c r="S31" t="n">
+        <v>96</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4116573323264</v>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>17.031</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.609</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>125.278</v>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
+      <c r="AC31" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3298,7 +3536,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3307,33 +3545,33 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>591.55</v>
+        <v>118</v>
       </c>
       <c r="E32" t="n">
-        <v>580.59</v>
+        <v>115.23</v>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="n">
-        <v>544.6900000000001</v>
+        <v>109.29</v>
       </c>
       <c r="H32" t="n">
-        <v>59.55</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>1.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>450.75</v>
+        <v>98.5</v>
       </c>
       <c r="L32" t="n">
-        <v>31.24</v>
+        <v>19.8</v>
       </c>
       <c r="M32" t="n">
         <v>75</v>
@@ -3348,23 +3586,47 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>6.1426344</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.86730266</v>
+      </c>
+      <c r="R32" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="S32" t="n">
+        <v>255</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1356167249920</v>
+      </c>
+      <c r="U32" t="n">
+        <v>14.965999</v>
+      </c>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>29.405</v>
+      </c>
+      <c r="X32" t="n">
+        <v>38.147</v>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3372,7 +3634,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>JSWDULUX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3381,33 +3643,33 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3428.3</v>
+        <v>3167.4</v>
       </c>
       <c r="E33" t="n">
-        <v>3354.41</v>
+        <v>3085.47</v>
       </c>
       <c r="F33" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="G33" t="n">
-        <v>3197.21</v>
+        <v>3099.91</v>
       </c>
       <c r="H33" t="n">
-        <v>59.7</v>
+        <v>58.91</v>
       </c>
       <c r="I33" t="n">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2896</v>
+        <v>2862</v>
       </c>
       <c r="L33" t="n">
-        <v>18.38</v>
+        <v>10.67</v>
       </c>
       <c r="M33" t="n">
         <v>75</v>
@@ -3422,11 +3684,17 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>7.347592</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.883686</v>
+      </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>144244375552</v>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
@@ -3438,7 +3706,9 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
+      <c r="AF33" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3446,7 +3716,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3455,33 +3725,33 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>118</v>
+        <v>2545</v>
       </c>
       <c r="E34" t="n">
-        <v>115.23</v>
+        <v>2478.76</v>
       </c>
       <c r="F34" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="G34" t="n">
-        <v>109.29</v>
+        <v>2340.14</v>
       </c>
       <c r="H34" t="n">
-        <v>68.73999999999999</v>
+        <v>63.59</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>98.5</v>
+        <v>2013</v>
       </c>
       <c r="L34" t="n">
-        <v>19.8</v>
+        <v>26.43</v>
       </c>
       <c r="M34" t="n">
         <v>75</v>
@@ -3496,23 +3766,53 @@
           <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>25.444912</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.2841005</v>
+      </c>
+      <c r="R34" t="n">
+        <v>100.02</v>
+      </c>
+      <c r="S34" t="n">
+        <v>244</v>
+      </c>
+      <c r="T34" t="n">
+        <v>485629394944</v>
+      </c>
+      <c r="U34" t="n">
+        <v>17.743999</v>
+      </c>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
+      <c r="W34" t="n">
+        <v>14.783</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.5559995</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>24.675</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.265</v>
+      </c>
       <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
+      <c r="AC34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3520,7 +3820,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3529,64 +3829,94 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3167.4</v>
+        <v>569.85</v>
       </c>
       <c r="E35" t="n">
-        <v>3083.74</v>
+        <v>582.21</v>
       </c>
       <c r="F35" t="n">
-        <v>2.71</v>
+        <v>-2.12</v>
       </c>
       <c r="G35" t="n">
-        <v>3096.47</v>
+        <v>540.83</v>
       </c>
       <c r="H35" t="n">
-        <v>59.25</v>
+        <v>53.78</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2862</v>
+        <v>548.8</v>
       </c>
       <c r="L35" t="n">
-        <v>10.67</v>
+        <v>3.84</v>
       </c>
       <c r="M35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>26.16391</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.177395</v>
+      </c>
+      <c r="R35" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="S35" t="n">
+        <v>250</v>
+      </c>
+      <c r="T35" t="n">
+        <v>347489959936</v>
+      </c>
+      <c r="U35" t="n">
+        <v>21.473</v>
+      </c>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>13.739</v>
+      </c>
+      <c r="X35" t="n">
+        <v>9.318</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.121</v>
+      </c>
       <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3594,7 +3924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3603,64 +3933,88 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2545</v>
+        <v>561.9</v>
       </c>
       <c r="E36" t="n">
-        <v>2476.31</v>
+        <v>571.86</v>
       </c>
       <c r="F36" t="n">
-        <v>2.77</v>
+        <v>-1.74</v>
       </c>
       <c r="G36" t="n">
-        <v>2340.39</v>
+        <v>547.61</v>
       </c>
       <c r="H36" t="n">
-        <v>63.96</v>
+        <v>50.66</v>
       </c>
       <c r="I36" t="n">
-        <v>0.57</v>
+        <v>1.01</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2013</v>
+        <v>557.8</v>
       </c>
       <c r="L36" t="n">
-        <v>26.43</v>
+        <v>0.74</v>
       </c>
       <c r="M36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>14.326874</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>10.491822</v>
+      </c>
+      <c r="R36" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>374</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2374206750720</v>
+      </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>54.70699999999999</v>
+      </c>
+      <c r="X36" t="n">
+        <v>38.068</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.034</v>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3668,7 +4022,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3677,33 +4031,33 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>569.85</v>
+        <v>1344.4</v>
       </c>
       <c r="E37" t="n">
-        <v>582.21</v>
+        <v>1359.51</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.12</v>
+        <v>-1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>540.83</v>
+        <v>1332.85</v>
       </c>
       <c r="H37" t="n">
-        <v>53.78</v>
+        <v>50.88</v>
       </c>
       <c r="I37" t="n">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>548.8</v>
+        <v>1305</v>
       </c>
       <c r="L37" t="n">
-        <v>3.84</v>
+        <v>3.02</v>
       </c>
       <c r="M37" t="n">
         <v>70</v>
@@ -3718,23 +4072,53 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>59.513058</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>14.337361</v>
+      </c>
+      <c r="R37" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="S37" t="n">
+        <v>95</v>
+      </c>
+      <c r="T37" t="n">
+        <v>280979603456</v>
+      </c>
+      <c r="U37" t="n">
+        <v>23.913</v>
+      </c>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="X37" t="n">
+        <v>36.923</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.464</v>
+      </c>
       <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
+      <c r="AC37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3742,7 +4126,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3751,22 +4135,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>561.9</v>
+        <v>331.55</v>
       </c>
       <c r="E38" t="n">
-        <v>571.86</v>
+        <v>333.74</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.74</v>
+        <v>-0.66</v>
       </c>
       <c r="G38" t="n">
-        <v>547.61</v>
+        <v>329.74</v>
       </c>
       <c r="H38" t="n">
-        <v>50.66</v>
+        <v>44.42</v>
       </c>
       <c r="I38" t="n">
-        <v>1.01</v>
+        <v>0.32</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3774,10 +4158,10 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>557.8</v>
+        <v>330.25</v>
       </c>
       <c r="L38" t="n">
-        <v>0.74</v>
+        <v>0.39</v>
       </c>
       <c r="M38" t="n">
         <v>70</v>
@@ -3789,26 +4173,48 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>31.160711</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.157679</v>
+      </c>
+      <c r="R38" t="n">
+        <v>10.64</v>
+      </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>118415122432</v>
+      </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>10.953</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.329</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>48.061</v>
+      </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3816,7 +4222,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3825,33 +4231,33 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1344.4</v>
+        <v>825.1</v>
       </c>
       <c r="E39" t="n">
-        <v>1359.51</v>
+        <v>826.87</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.11</v>
+        <v>-0.21</v>
       </c>
       <c r="G39" t="n">
-        <v>1332.85</v>
+        <v>815.9299999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>50.88</v>
+        <v>48.36</v>
       </c>
       <c r="I39" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1305</v>
+        <v>811.8</v>
       </c>
       <c r="L39" t="n">
-        <v>3.02</v>
+        <v>1.64</v>
       </c>
       <c r="M39" t="n">
         <v>70</v>
@@ -3863,26 +4269,50 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>34.250725</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.882711</v>
+      </c>
+      <c r="R39" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="S39" t="n">
+        <v>24</v>
+      </c>
+      <c r="T39" t="n">
+        <v>180692041728</v>
+      </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>33.731</v>
+      </c>
+      <c r="X39" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>64.041</v>
+      </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
+      <c r="AC39" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>-57.7</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3890,7 +4320,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3899,33 +4329,33 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>27060</v>
+        <v>6696</v>
       </c>
       <c r="E40" t="n">
-        <v>27340.9</v>
+        <v>6659.96</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.03</v>
+        <v>0.54</v>
       </c>
       <c r="G40" t="n">
-        <v>26978.6</v>
+        <v>7006.07</v>
       </c>
       <c r="H40" t="n">
-        <v>42.24</v>
+        <v>39.57</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>0.66</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>27000</v>
+        <v>5673</v>
       </c>
       <c r="L40" t="n">
-        <v>0.22</v>
+        <v>18.03</v>
       </c>
       <c r="M40" t="n">
         <v>70</v>
@@ -3937,26 +4367,48 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>104.16926</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>13.3846655</v>
+      </c>
+      <c r="R40" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>571063140352</v>
+      </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>20.444</v>
+      </c>
+      <c r="X40" t="n">
+        <v>20.587</v>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3964,7 +4416,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3973,33 +4425,33 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>331.55</v>
+        <v>287.3</v>
       </c>
       <c r="E41" t="n">
-        <v>333.74</v>
+        <v>283.54</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.66</v>
+        <v>1.32</v>
       </c>
       <c r="G41" t="n">
-        <v>329.74</v>
+        <v>324.36</v>
       </c>
       <c r="H41" t="n">
-        <v>44.42</v>
+        <v>31.65</v>
       </c>
       <c r="I41" t="n">
-        <v>0.32</v>
+        <v>0.76</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>330.25</v>
+        <v>208.63</v>
       </c>
       <c r="L41" t="n">
-        <v>0.39</v>
+        <v>37.71</v>
       </c>
       <c r="M41" t="n">
         <v>70</v>
@@ -4011,26 +4463,50 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>26.382</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4.2775254</v>
+      </c>
+      <c r="R41" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="S41" t="n">
+        <v>173</v>
+      </c>
+      <c r="T41" t="n">
+        <v>262502383616</v>
+      </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>24.655001</v>
+      </c>
+      <c r="X41" t="n">
+        <v>20.698</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>129.314</v>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4038,7 +4514,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4047,33 +4523,33 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>825.1</v>
+        <v>531.15</v>
       </c>
       <c r="E42" t="n">
-        <v>826.27</v>
+        <v>521.38</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.14</v>
+        <v>1.87</v>
       </c>
       <c r="G42" t="n">
-        <v>816.61</v>
+        <v>510.3</v>
       </c>
       <c r="H42" t="n">
-        <v>48.48</v>
+        <v>61.67</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.04</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>811.8</v>
+        <v>487.9</v>
       </c>
       <c r="L42" t="n">
-        <v>1.64</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>70</v>
@@ -4085,26 +4561,50 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>16.582893</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.5415702</v>
+      </c>
+      <c r="R42" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="S42" t="n">
+        <v>38</v>
+      </c>
+      <c r="T42" t="n">
+        <v>187167326208</v>
+      </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+      <c r="W42" t="n">
+        <v>35.115</v>
+      </c>
+      <c r="X42" t="n">
+        <v>19.941</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>35.204</v>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
+      <c r="AC42" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4112,7 +4612,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4121,33 +4621,33 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6696</v>
+        <v>4057</v>
       </c>
       <c r="E43" t="n">
-        <v>6663.26</v>
+        <v>3978.76</v>
       </c>
       <c r="F43" t="n">
-        <v>0.49</v>
+        <v>1.97</v>
       </c>
       <c r="G43" t="n">
-        <v>7000.76</v>
+        <v>3998.81</v>
       </c>
       <c r="H43" t="n">
-        <v>39.53</v>
+        <v>58.6</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5673</v>
+        <v>3720</v>
       </c>
       <c r="L43" t="n">
-        <v>18.03</v>
+        <v>9.06</v>
       </c>
       <c r="M43" t="n">
         <v>70</v>
@@ -4159,26 +4659,50 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>33.782997</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.1065493</v>
+      </c>
+      <c r="R43" t="n">
+        <v>120.09</v>
+      </c>
+      <c r="S43" t="n">
+        <v>93</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5581888815104</v>
+      </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>10.609999</v>
+      </c>
+      <c r="X43" t="n">
+        <v>5.588</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>97.64</v>
+      </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4186,7 +4710,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4195,33 +4719,33 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>287.3</v>
+        <v>1992.1</v>
       </c>
       <c r="E44" t="n">
-        <v>283.54</v>
+        <v>1947.98</v>
       </c>
       <c r="F44" t="n">
-        <v>1.32</v>
+        <v>2.26</v>
       </c>
       <c r="G44" t="n">
-        <v>324.36</v>
+        <v>1903.73</v>
       </c>
       <c r="H44" t="n">
-        <v>31.65</v>
+        <v>61.25</v>
       </c>
       <c r="I44" t="n">
-        <v>0.76</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>208.63</v>
+        <v>1901.3</v>
       </c>
       <c r="L44" t="n">
-        <v>37.71</v>
+        <v>4.78</v>
       </c>
       <c r="M44" t="n">
         <v>70</v>
@@ -4233,26 +4757,56 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=10%</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>41.667015</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>7.677307</v>
+      </c>
+      <c r="R44" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="S44" t="n">
+        <v>120</v>
+      </c>
+      <c r="T44" t="n">
+        <v>12428031033344</v>
+      </c>
+      <c r="U44" t="n">
+        <v>20.151</v>
+      </c>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>32.573003</v>
+      </c>
+      <c r="X44" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>100.415</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.358</v>
+      </c>
       <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4260,7 +4814,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4269,36 +4823,36 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>531.15</v>
+        <v>382.05</v>
       </c>
       <c r="E45" t="n">
-        <v>521.24</v>
+        <v>390.64</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="G45" t="n">
-        <v>509.7</v>
+        <v>384.62</v>
       </c>
       <c r="H45" t="n">
-        <v>61.84</v>
+        <v>50.89</v>
       </c>
       <c r="I45" t="n">
-        <v>1.04</v>
+        <v>2.33</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>487.9</v>
+        <v>367.85</v>
       </c>
       <c r="L45" t="n">
-        <v>8.859999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="M45" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4307,26 +4861,50 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>31.652859</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.0924454</v>
+      </c>
+      <c r="R45" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="S45" t="n">
+        <v>65</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1220779442176</v>
+      </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>14.453</v>
+      </c>
+      <c r="X45" t="n">
+        <v>6.0890004</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>168.051</v>
+      </c>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4334,7 +4912,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4343,36 +4921,36 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4057</v>
+        <v>36750</v>
       </c>
       <c r="E46" t="n">
-        <v>3978.76</v>
+        <v>36917.68</v>
       </c>
       <c r="F46" t="n">
-        <v>1.97</v>
+        <v>-0.45</v>
       </c>
       <c r="G46" t="n">
-        <v>3998.81</v>
+        <v>39986.8</v>
       </c>
       <c r="H46" t="n">
-        <v>58.6</v>
+        <v>30.7</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>3720</v>
+        <v>36410</v>
       </c>
       <c r="L46" t="n">
-        <v>9.06</v>
+        <v>0.93</v>
       </c>
       <c r="M46" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4381,26 +4959,50 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>54.102196</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>27.279732</v>
+      </c>
+      <c r="R46" t="n">
+        <v>679.27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>218</v>
+      </c>
+      <c r="T46" t="n">
+        <v>409904873472</v>
+      </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>18.332</v>
+      </c>
+      <c r="X46" t="n">
+        <v>14.126</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>18.422</v>
+      </c>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4408,7 +5010,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4417,22 +5019,22 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1992.1</v>
+        <v>7222</v>
       </c>
       <c r="E47" t="n">
-        <v>1947.98</v>
+        <v>7252.02</v>
       </c>
       <c r="F47" t="n">
-        <v>2.26</v>
+        <v>-0.41</v>
       </c>
       <c r="G47" t="n">
-        <v>1903.73</v>
+        <v>7557.64</v>
       </c>
       <c r="H47" t="n">
-        <v>61.25</v>
+        <v>43.57</v>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4440,13 +5042,13 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1901.3</v>
+        <v>6951</v>
       </c>
       <c r="L47" t="n">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="M47" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4455,26 +5057,48 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>277.76923</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.813523</v>
+      </c>
+      <c r="R47" t="n">
+        <v>26</v>
+      </c>
       <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>254703812608</v>
+      </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>6.387</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>46.566</v>
+      </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
+      <c r="AC47" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4482,7 +5106,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4491,33 +5115,33 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>382.05</v>
+        <v>3275.8</v>
       </c>
       <c r="E48" t="n">
-        <v>390.64</v>
+        <v>3274.08</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.2</v>
+        <v>0.05</v>
       </c>
       <c r="G48" t="n">
-        <v>384.62</v>
+        <v>3359.19</v>
       </c>
       <c r="H48" t="n">
-        <v>50.89</v>
+        <v>52.08</v>
       </c>
       <c r="I48" t="n">
-        <v>2.33</v>
+        <v>0.66</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>367.85</v>
+        <v>3164.7</v>
       </c>
       <c r="L48" t="n">
-        <v>3.86</v>
+        <v>3.51</v>
       </c>
       <c r="M48" t="n">
         <v>65</v>
@@ -4529,26 +5153,50 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>57.470177</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>8.454114000000001</v>
+      </c>
+      <c r="R48" t="n">
+        <v>57</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>246401531904</v>
+      </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
+      <c r="W48" t="n">
+        <v>15.506</v>
+      </c>
+      <c r="X48" t="n">
+        <v>11.8389994</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
+      <c r="AC48" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4556,7 +5204,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4565,33 +5213,33 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>36750</v>
+        <v>929</v>
       </c>
       <c r="E49" t="n">
-        <v>36914.43</v>
+        <v>919.79</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.45</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>40027.4</v>
+        <v>957.1</v>
       </c>
       <c r="H49" t="n">
-        <v>30.04</v>
+        <v>46.17</v>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>1.11</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>36410</v>
+        <v>879.1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.93</v>
+        <v>5.68</v>
       </c>
       <c r="M49" t="n">
         <v>65</v>
@@ -4603,26 +5251,50 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>67.124275</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7.0875993</v>
+      </c>
+      <c r="R49" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="n">
+        <v>701356113920</v>
+      </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>16.316</v>
+      </c>
+      <c r="X49" t="n">
+        <v>11.023</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>34.15</v>
+      </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
+      <c r="AC49" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4630,7 +5302,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4639,33 +5311,33 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7222</v>
+        <v>101.51</v>
       </c>
       <c r="E50" t="n">
-        <v>7246.59</v>
+        <v>100.34</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.34</v>
+        <v>1.17</v>
       </c>
       <c r="G50" t="n">
-        <v>7550.01</v>
+        <v>108.13</v>
       </c>
       <c r="H50" t="n">
-        <v>43.66</v>
+        <v>32.22</v>
       </c>
       <c r="I50" t="n">
-        <v>2.61</v>
+        <v>0.68</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>6951</v>
+        <v>92.3</v>
       </c>
       <c r="L50" t="n">
-        <v>3.9</v>
+        <v>9.98</v>
       </c>
       <c r="M50" t="n">
         <v>65</v>
@@ -4677,26 +5349,42 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>253.77501</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-42.687134</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.4</v>
+      </c>
       <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>1071841673216</v>
+      </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
+      <c r="W50" t="n">
+        <v>25.013</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3.0720001</v>
+      </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>23.7</v>
+      </c>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
+      <c r="AF50" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4704,7 +5392,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4713,33 +5401,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3275.8</v>
+        <v>762.25</v>
       </c>
       <c r="E51" t="n">
-        <v>3274.7</v>
+        <v>748.01</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03</v>
+        <v>1.9</v>
       </c>
       <c r="G51" t="n">
-        <v>3349.23</v>
+        <v>782.6</v>
       </c>
       <c r="H51" t="n">
-        <v>52.49</v>
+        <v>40.86</v>
       </c>
       <c r="I51" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>3164.7</v>
+        <v>720</v>
       </c>
       <c r="L51" t="n">
-        <v>3.51</v>
+        <v>5.87</v>
       </c>
       <c r="M51" t="n">
         <v>65</v>
@@ -4751,26 +5439,50 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>38.910156</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>14.310254</v>
+      </c>
+      <c r="R51" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="S51" t="n">
+        <v>166</v>
+      </c>
+      <c r="T51" t="n">
+        <v>189264805888</v>
+      </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
+      <c r="W51" t="n">
+        <v>40.046</v>
+      </c>
+      <c r="X51" t="n">
+        <v>31.785</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>4.863</v>
+      </c>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4778,7 +5490,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4787,33 +5499,33 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>929</v>
+        <v>345.9</v>
       </c>
       <c r="E52" t="n">
-        <v>919.23</v>
+        <v>338.21</v>
       </c>
       <c r="F52" t="n">
-        <v>1.06</v>
+        <v>2.27</v>
       </c>
       <c r="G52" t="n">
-        <v>956.63</v>
+        <v>352.93</v>
       </c>
       <c r="H52" t="n">
-        <v>46.2</v>
+        <v>46.73</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.26</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>879.1</v>
+        <v>326</v>
       </c>
       <c r="L52" t="n">
-        <v>5.68</v>
+        <v>6.1</v>
       </c>
       <c r="M52" t="n">
         <v>65</v>
@@ -4828,23 +5540,47 @@
           <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>29.214525</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>10.045888</v>
+      </c>
+      <c r="R52" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="S52" t="n">
+        <v>145</v>
+      </c>
+      <c r="T52" t="n">
+        <v>149484027904</v>
+      </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
+      <c r="W52" t="n">
+        <v>56.596</v>
+      </c>
+      <c r="X52" t="n">
+        <v>44.739</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>9.593999999999999</v>
+      </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4852,7 +5588,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4861,36 +5597,36 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>101.51</v>
+        <v>391.15</v>
       </c>
       <c r="E53" t="n">
-        <v>100.4</v>
+        <v>401.48</v>
       </c>
       <c r="F53" t="n">
-        <v>1.1</v>
+        <v>-2.57</v>
       </c>
       <c r="G53" t="n">
-        <v>108.19</v>
+        <v>391.15</v>
       </c>
       <c r="H53" t="n">
-        <v>31.86</v>
+        <v>51.08</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>92.3</v>
+        <v>368.4</v>
       </c>
       <c r="L53" t="n">
-        <v>9.98</v>
+        <v>6.18</v>
       </c>
       <c r="M53" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4899,26 +5635,48 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
+          <t>within 3% of 200DMA; recovery &gt;=5%; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>19.174019</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2.1468048</v>
+      </c>
+      <c r="R53" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>17</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3890559844352</v>
+      </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
+      <c r="W53" t="n">
+        <v>34.761003</v>
+      </c>
+      <c r="X53" t="n">
+        <v>28.467</v>
+      </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4926,7 +5684,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4935,36 +5693,36 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>762.25</v>
+        <v>11619</v>
       </c>
       <c r="E54" t="n">
-        <v>748.01</v>
+        <v>11791.94</v>
       </c>
       <c r="F54" t="n">
-        <v>1.9</v>
+        <v>-1.47</v>
       </c>
       <c r="G54" t="n">
-        <v>782.6</v>
+        <v>11599.76</v>
       </c>
       <c r="H54" t="n">
-        <v>40.86</v>
+        <v>43.34</v>
       </c>
       <c r="I54" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>720</v>
+        <v>11570</v>
       </c>
       <c r="L54" t="n">
-        <v>5.87</v>
+        <v>0.42</v>
       </c>
       <c r="M54" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4973,26 +5731,50 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>40.022736</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4.460094</v>
+      </c>
+      <c r="R54" t="n">
+        <v>290.31</v>
+      </c>
+      <c r="S54" t="n">
+        <v>207</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3417956941824</v>
+      </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
+      <c r="W54" t="n">
+        <v>15.478</v>
+      </c>
+      <c r="X54" t="n">
+        <v>9.2930004</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>29.432</v>
+      </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5000,7 +5782,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5009,36 +5791,36 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>345.9</v>
+        <v>2095.3</v>
       </c>
       <c r="E55" t="n">
-        <v>338.29</v>
+        <v>2110.01</v>
       </c>
       <c r="F55" t="n">
-        <v>2.25</v>
+        <v>-0.7</v>
       </c>
       <c r="G55" t="n">
-        <v>352.63</v>
+        <v>2019.87</v>
       </c>
       <c r="H55" t="n">
-        <v>46.4</v>
+        <v>57.65</v>
       </c>
       <c r="I55" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>326</v>
+        <v>2043</v>
       </c>
       <c r="L55" t="n">
-        <v>6.1</v>
+        <v>2.56</v>
       </c>
       <c r="M55" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5047,26 +5829,50 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>33.773373</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.9136887</v>
+      </c>
+      <c r="R55" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="S55" t="n">
+        <v>52</v>
+      </c>
+      <c r="T55" t="n">
+        <v>617058795520</v>
+      </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>6.771999600000001</v>
+      </c>
+      <c r="X55" t="n">
+        <v>5.619</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>11.469</v>
+      </c>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5074,7 +5880,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5083,33 +5889,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2095.3</v>
+        <v>186.82</v>
       </c>
       <c r="E56" t="n">
-        <v>2110.01</v>
+        <v>185.97</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.7</v>
+        <v>0.46</v>
       </c>
       <c r="G56" t="n">
-        <v>2019.87</v>
+        <v>185.43</v>
       </c>
       <c r="H56" t="n">
-        <v>57.65</v>
+        <v>49.61</v>
       </c>
       <c r="I56" t="n">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>2043</v>
+        <v>170.1</v>
       </c>
       <c r="L56" t="n">
-        <v>2.56</v>
+        <v>9.83</v>
       </c>
       <c r="M56" t="n">
         <v>60</v>
@@ -5121,26 +5927,56 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>17.427238</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>9.694862000000001</v>
+      </c>
+      <c r="R56" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="S56" t="n">
+        <v>669</v>
+      </c>
+      <c r="T56" t="n">
+        <v>184787845120</v>
+      </c>
+      <c r="U56" t="n">
+        <v>56.996</v>
+      </c>
       <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
+      <c r="W56" t="n">
+        <v>24.779</v>
+      </c>
+      <c r="X56" t="n">
+        <v>17.066</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.784</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.852</v>
+      </c>
       <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5148,7 +5984,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5157,33 +5993,33 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>186.82</v>
+        <v>1138.7</v>
       </c>
       <c r="E57" t="n">
-        <v>185.9</v>
+        <v>1118.47</v>
       </c>
       <c r="F57" t="n">
-        <v>0.49</v>
+        <v>1.81</v>
       </c>
       <c r="G57" t="n">
-        <v>185.46</v>
+        <v>1127.48</v>
       </c>
       <c r="H57" t="n">
-        <v>49.53</v>
+        <v>56.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>170.1</v>
+        <v>1114</v>
       </c>
       <c r="L57" t="n">
-        <v>9.83</v>
+        <v>2.22</v>
       </c>
       <c r="M57" t="n">
         <v>60</v>
@@ -5195,26 +6031,50 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; above 50DMA</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
+          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>15.7235565</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.7499615</v>
+      </c>
+      <c r="R57" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="S57" t="n">
+        <v>316</v>
+      </c>
+      <c r="T57" t="n">
+        <v>112478248960</v>
+      </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>9.854999000000001</v>
+      </c>
+      <c r="X57" t="n">
+        <v>8.382000000000001</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>3.461</v>
+      </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5222,7 +6082,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5231,33 +6091,33 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1138.7</v>
+        <v>5580</v>
       </c>
       <c r="E58" t="n">
-        <v>1117.67</v>
+        <v>5469.4</v>
       </c>
       <c r="F58" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="G58" t="n">
-        <v>1128.11</v>
+        <v>5067.93</v>
       </c>
       <c r="H58" t="n">
-        <v>56.14</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>1.13</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>1114</v>
+        <v>5390</v>
       </c>
       <c r="L58" t="n">
-        <v>2.22</v>
+        <v>3.53</v>
       </c>
       <c r="M58" t="n">
         <v>60</v>
@@ -5272,23 +6132,47 @@
           <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>45.66285</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>11.137925</v>
+      </c>
+      <c r="R58" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>65</v>
+      </c>
+      <c r="T58" t="n">
+        <v>871769178112</v>
+      </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>13.516</v>
+      </c>
+      <c r="X58" t="n">
+        <v>12.236</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.092</v>
+      </c>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5296,7 +6180,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5305,36 +6189,36 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5580</v>
+        <v>152.39</v>
       </c>
       <c r="E59" t="n">
-        <v>5468.01</v>
+        <v>155.77</v>
       </c>
       <c r="F59" t="n">
-        <v>2.05</v>
+        <v>-2.17</v>
       </c>
       <c r="G59" t="n">
-        <v>5078.14</v>
+        <v>167.55</v>
       </c>
       <c r="H59" t="n">
-        <v>64.52</v>
+        <v>35.7</v>
       </c>
       <c r="I59" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>5390</v>
+        <v>152</v>
       </c>
       <c r="L59" t="n">
-        <v>3.53</v>
+        <v>0.26</v>
       </c>
       <c r="M59" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5343,26 +6227,46 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>0.6559713</v>
+      </c>
+      <c r="R59" t="n">
+        <v>-89.77</v>
+      </c>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>175048392704</v>
+      </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
+      <c r="W59" t="n">
+        <v>93.80199999999999</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>273.033</v>
+      </c>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>-52.90000000000001</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5370,7 +6274,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5379,33 +6283,33 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>152.39</v>
+        <v>298.05</v>
       </c>
       <c r="E60" t="n">
-        <v>155.77</v>
+        <v>302.2</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.17</v>
+        <v>-1.37</v>
       </c>
       <c r="G60" t="n">
-        <v>167.55</v>
+        <v>320.01</v>
       </c>
       <c r="H60" t="n">
-        <v>35.7</v>
+        <v>42.97</v>
       </c>
       <c r="I60" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>152</v>
+        <v>288.1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.26</v>
+        <v>3.45</v>
       </c>
       <c r="M60" t="n">
         <v>55</v>
@@ -5420,23 +6324,47 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>34.616726</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>5.778402</v>
+      </c>
+      <c r="R60" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="n">
+        <v>89464422400</v>
+      </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
+      <c r="W60" t="n">
+        <v>15.117</v>
+      </c>
+      <c r="X60" t="n">
+        <v>10.132</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>29.595</v>
+      </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5444,7 +6372,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TARIL</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5453,33 +6381,33 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>298.05</v>
+        <v>413.5</v>
       </c>
       <c r="E61" t="n">
-        <v>302.2</v>
+        <v>419.17</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.37</v>
+        <v>-1.35</v>
       </c>
       <c r="G61" t="n">
-        <v>320.01</v>
+        <v>421.36</v>
       </c>
       <c r="H61" t="n">
-        <v>42.97</v>
+        <v>48.92</v>
       </c>
       <c r="I61" t="n">
-        <v>2.28</v>
+        <v>0.91</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>288.1</v>
+        <v>385.9</v>
       </c>
       <c r="L61" t="n">
-        <v>3.45</v>
+        <v>7.15</v>
       </c>
       <c r="M61" t="n">
         <v>55</v>
@@ -5491,26 +6419,50 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>8.708930000000001</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.9618435</v>
+      </c>
+      <c r="R61" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="S61" t="n">
+        <v>242</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2615386570752</v>
+      </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>6.426</v>
+      </c>
+      <c r="X61" t="n">
+        <v>6.515</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.431</v>
+      </c>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5518,7 +6470,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5527,33 +6479,33 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>413.5</v>
+        <v>1397.4</v>
       </c>
       <c r="E62" t="n">
-        <v>419.17</v>
+        <v>1408.24</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.35</v>
+        <v>-0.77</v>
       </c>
       <c r="G62" t="n">
-        <v>421.36</v>
+        <v>1433.57</v>
       </c>
       <c r="H62" t="n">
-        <v>48.92</v>
+        <v>46.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>385.9</v>
+        <v>1385.2</v>
       </c>
       <c r="L62" t="n">
-        <v>7.15</v>
+        <v>0.88</v>
       </c>
       <c r="M62" t="n">
         <v>55</v>
@@ -5565,26 +6517,48 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; recovery &gt;=5%</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>16.207376</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>2.1909964</v>
+      </c>
+      <c r="R62" t="n">
+        <v>86.22</v>
+      </c>
       <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="T62" t="n">
+        <v>110799880192</v>
+      </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
+      <c r="W62" t="n">
+        <v>54.527</v>
+      </c>
+      <c r="X62" t="n">
+        <v>42.543998</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>310.553</v>
+      </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5642,23 +6616,47 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>51.812424</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>14.205161</v>
+      </c>
+      <c r="R63" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="S63" t="n">
+        <v>102</v>
+      </c>
+      <c r="T63" t="n">
+        <v>489687252992</v>
+      </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
+      <c r="W63" t="n">
+        <v>7.454</v>
+      </c>
+      <c r="X63" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>335.854</v>
+      </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5666,7 +6664,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5675,22 +6673,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1397.4</v>
+        <v>2235</v>
       </c>
       <c r="E64" t="n">
-        <v>1406.72</v>
+        <v>2242.97</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.66</v>
+        <v>-0.36</v>
       </c>
       <c r="G64" t="n">
-        <v>1434.81</v>
+        <v>2378.4</v>
       </c>
       <c r="H64" t="n">
-        <v>46.82</v>
+        <v>30.68</v>
       </c>
       <c r="I64" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -5698,10 +6696,10 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>1385.2</v>
+        <v>2230.1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.88</v>
+        <v>0.22</v>
       </c>
       <c r="M64" t="n">
         <v>55</v>
@@ -5716,23 +6714,47 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>18.518518</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>4.5517774</v>
+      </c>
+      <c r="R64" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="S64" t="n">
+        <v>81</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1021919952896</v>
+      </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
+      <c r="W64" t="n">
+        <v>25.354</v>
+      </c>
+      <c r="X64" t="n">
+        <v>18.450001</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>29.388</v>
+      </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5740,7 +6762,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5749,33 +6771,33 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2235</v>
+        <v>17.39</v>
       </c>
       <c r="E65" t="n">
-        <v>2245.45</v>
+        <v>17.35</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.47</v>
+        <v>0.24</v>
       </c>
       <c r="G65" t="n">
-        <v>2381.35</v>
+        <v>17.68</v>
       </c>
       <c r="H65" t="n">
-        <v>29.9</v>
+        <v>44.93</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>2230.1</v>
+        <v>16.75</v>
       </c>
       <c r="L65" t="n">
-        <v>0.22</v>
+        <v>3.82</v>
       </c>
       <c r="M65" t="n">
         <v>55</v>
@@ -5790,23 +6812,45 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>24.842857</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.3351247</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.7</v>
+      </c>
       <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
+      <c r="T65" t="n">
+        <v>119181647872</v>
+      </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
+      <c r="W65" t="n">
+        <v>36.141</v>
+      </c>
+      <c r="X65" t="n">
+        <v>11.1420006</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>26.634</v>
+      </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr"/>
-      <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5814,7 +6858,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5823,33 +6867,33 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>17.39</v>
+        <v>622.95</v>
       </c>
       <c r="E66" t="n">
-        <v>17.35</v>
+        <v>618.66</v>
       </c>
       <c r="F66" t="n">
-        <v>0.24</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>17.68</v>
+        <v>675.8</v>
       </c>
       <c r="H66" t="n">
-        <v>44.93</v>
+        <v>34.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>16.75</v>
+        <v>606.65</v>
       </c>
       <c r="L66" t="n">
-        <v>3.82</v>
+        <v>2.69</v>
       </c>
       <c r="M66" t="n">
         <v>55</v>
@@ -5864,23 +6908,47 @@
           <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>66.697</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>12.903393</v>
+      </c>
+      <c r="R66" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="n">
+        <v>147324108800</v>
+      </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
+      <c r="W66" t="n">
+        <v>8.273999999999999</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3.571</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>190.282</v>
+      </c>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5888,7 +6956,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>MMTC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5897,33 +6965,33 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>622.95</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>618.67</v>
+        <v>63.45</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="G67" t="n">
-        <v>675.37</v>
+        <v>66.11</v>
       </c>
       <c r="H67" t="n">
-        <v>34.35</v>
+        <v>51.35</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>606.65</v>
+        <v>59.9</v>
       </c>
       <c r="L67" t="n">
-        <v>2.69</v>
+        <v>7.43</v>
       </c>
       <c r="M67" t="n">
         <v>55</v>
@@ -5935,26 +7003,48 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>21.521738</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4.552851</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.99</v>
+      </c>
       <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
+      <c r="T67" t="n">
+        <v>96525000704</v>
+      </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
+      <c r="W67" t="n">
+        <v>85.238</v>
+      </c>
+      <c r="X67" t="n">
+        <v>573.759</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.114</v>
+      </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr"/>
-      <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>10644.1</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5962,7 +7052,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MMTC</t>
+          <t>GRSE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5971,33 +7061,33 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>64.34999999999999</v>
+        <v>2618.6</v>
       </c>
       <c r="E68" t="n">
-        <v>63.43</v>
+        <v>2574.51</v>
       </c>
       <c r="F68" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="G68" t="n">
-        <v>66</v>
+        <v>2652.61</v>
       </c>
       <c r="H68" t="n">
-        <v>51.7</v>
+        <v>51.05</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>59.9</v>
+        <v>2471.7</v>
       </c>
       <c r="L68" t="n">
-        <v>7.43</v>
+        <v>5.94</v>
       </c>
       <c r="M68" t="n">
         <v>55</v>
@@ -6012,23 +7102,47 @@
           <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>37.451374</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>11.421667</v>
+      </c>
+      <c r="R68" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="S68" t="n">
+        <v>102</v>
+      </c>
+      <c r="T68" t="n">
+        <v>299965874176</v>
+      </c>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
+      <c r="W68" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="X68" t="n">
+        <v>10.665</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.424</v>
+      </c>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr"/>
-      <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6036,7 +7150,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6045,33 +7159,33 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2618.6</v>
+        <v>498.2</v>
       </c>
       <c r="E69" t="n">
-        <v>2574.51</v>
+        <v>486.42</v>
       </c>
       <c r="F69" t="n">
-        <v>1.71</v>
+        <v>2.42</v>
       </c>
       <c r="G69" t="n">
-        <v>2652.61</v>
+        <v>505.47</v>
       </c>
       <c r="H69" t="n">
-        <v>51.05</v>
+        <v>45.58</v>
       </c>
       <c r="I69" t="n">
-        <v>0.93</v>
+        <v>0.51</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>2471.7</v>
+        <v>481.75</v>
       </c>
       <c r="L69" t="n">
-        <v>5.94</v>
+        <v>3.41</v>
       </c>
       <c r="M69" t="n">
         <v>55</v>
@@ -6083,26 +7197,48 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>19.340063</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.8785374</v>
+      </c>
+      <c r="R69" t="n">
+        <v>25.76</v>
+      </c>
       <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
+      <c r="T69" t="n">
+        <v>218080821248</v>
+      </c>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
+      <c r="W69" t="n">
+        <v>61.72299999999999</v>
+      </c>
+      <c r="X69" t="n">
+        <v>48.151</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>255.574</v>
+      </c>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6110,7 +7246,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6119,64 +7255,88 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>498.2</v>
+        <v>1091.5</v>
       </c>
       <c r="E70" t="n">
-        <v>486.35</v>
+        <v>1122.7</v>
       </c>
       <c r="F70" t="n">
-        <v>2.44</v>
+        <v>-2.78</v>
       </c>
       <c r="G70" t="n">
-        <v>506.04</v>
+        <v>1083.72</v>
       </c>
       <c r="H70" t="n">
-        <v>45.65</v>
+        <v>51.16</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>481.75</v>
+        <v>1086</v>
       </c>
       <c r="L70" t="n">
-        <v>3.41</v>
+        <v>0.51</v>
       </c>
       <c r="M70" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NEAR 200DMA</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>at/above 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>40.818996</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.1815078</v>
+      </c>
+      <c r="R70" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="S70" t="n">
+        <v>18</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1110588260352</v>
+      </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
+      <c r="W70" t="n">
+        <v>11.1999996</v>
+      </c>
+      <c r="X70" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>43.613</v>
+      </c>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr"/>
-      <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6184,7 +7344,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6193,33 +7353,33 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1091.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>1122.84</v>
+        <v>82.89</v>
       </c>
       <c r="F71" t="n">
-        <v>-2.79</v>
+        <v>1.82</v>
       </c>
       <c r="G71" t="n">
-        <v>1082.14</v>
+        <v>85.59</v>
       </c>
       <c r="H71" t="n">
-        <v>50.85</v>
+        <v>46.45</v>
       </c>
       <c r="I71" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1086</v>
+        <v>74.55</v>
       </c>
       <c r="L71" t="n">
-        <v>0.51</v>
+        <v>13.21</v>
       </c>
       <c r="M71" t="n">
         <v>50</v>
@@ -6231,26 +7391,56 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; above 50DMA; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
+          <t>at/above 200DMA; recovery &gt;=10%</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10.035672</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.1744733</v>
+      </c>
+      <c r="R71" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="S71" t="n">
+        <v>412</v>
+      </c>
+      <c r="T71" t="n">
+        <v>742029393920</v>
+      </c>
+      <c r="U71" t="n">
+        <v>23.363</v>
+      </c>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+      <c r="W71" t="n">
+        <v>21.968001</v>
+      </c>
+      <c r="X71" t="n">
+        <v>23.231001</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>18.802</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1.702</v>
+      </c>
       <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6258,7 +7448,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6267,36 +7457,36 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>84.40000000000001</v>
+        <v>1559.2</v>
       </c>
       <c r="E72" t="n">
-        <v>82.89</v>
+        <v>1606.09</v>
       </c>
       <c r="F72" t="n">
-        <v>1.82</v>
+        <v>-2.92</v>
       </c>
       <c r="G72" t="n">
-        <v>85.59</v>
+        <v>1632.83</v>
       </c>
       <c r="H72" t="n">
-        <v>46.45</v>
+        <v>42.46</v>
       </c>
       <c r="I72" t="n">
-        <v>1.12</v>
+        <v>0.97</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>74.55</v>
+        <v>1506.7</v>
       </c>
       <c r="L72" t="n">
-        <v>13.21</v>
+        <v>3.48</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -6305,26 +7495,42 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>at/above 200DMA; recovery &gt;=10%</t>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="Q72" t="n">
+        <v>3.0729208</v>
+      </c>
+      <c r="R72" t="n">
+        <v>-4.24</v>
+      </c>
       <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
+      <c r="T72" t="n">
+        <v>178797969408</v>
+      </c>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>11.492</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>25.791</v>
+      </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>37.2</v>
+      </c>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
+      <c r="AF72" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6332,7 +7538,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6341,33 +7547,33 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1559.2</v>
+        <v>1284.5</v>
       </c>
       <c r="E73" t="n">
-        <v>1606.66</v>
+        <v>1318.87</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.95</v>
+        <v>-2.61</v>
       </c>
       <c r="G73" t="n">
-        <v>1635.71</v>
+        <v>1405.23</v>
       </c>
       <c r="H73" t="n">
-        <v>42.24</v>
+        <v>34.87</v>
       </c>
       <c r="I73" t="n">
-        <v>1.04</v>
+        <v>0.51</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>1506.7</v>
+        <v>1267</v>
       </c>
       <c r="L73" t="n">
-        <v>3.48</v>
+        <v>1.38</v>
       </c>
       <c r="M73" t="n">
         <v>45</v>
@@ -6382,23 +7588,47 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>4.9043565</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.081117</v>
+      </c>
+      <c r="R73" t="n">
+        <v>261.91</v>
+      </c>
+      <c r="S73" t="n">
+        <v>448.0000000000001</v>
+      </c>
+      <c r="T73" t="n">
+        <v>183387652096</v>
+      </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
+      <c r="W73" t="n">
+        <v>54.431</v>
+      </c>
+      <c r="X73" t="n">
+        <v>60.307</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>6.409</v>
+      </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>159.4</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6406,7 +7636,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6415,30 +7645,30 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1284.5</v>
+        <v>275.4</v>
       </c>
       <c r="E74" t="n">
-        <v>1320.33</v>
+        <v>281.72</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.71</v>
+        <v>-2.24</v>
       </c>
       <c r="G74" t="n">
-        <v>1402.96</v>
+        <v>306.53</v>
       </c>
       <c r="H74" t="n">
-        <v>35.75</v>
+        <v>32.01</v>
       </c>
       <c r="I74" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1267</v>
+        <v>271.65</v>
       </c>
       <c r="L74" t="n">
         <v>1.38</v>
@@ -6456,23 +7686,47 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>11.590909</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.7740043</v>
+      </c>
+      <c r="R74" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="S74" t="n">
+        <v>261</v>
+      </c>
+      <c r="T74" t="n">
+        <v>381879746560</v>
+      </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
+      <c r="W74" t="n">
+        <v>28.304002</v>
+      </c>
+      <c r="X74" t="n">
+        <v>17.458001</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>82</v>
+      </c>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6480,7 +7734,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6489,33 +7743,33 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>391.15</v>
+        <v>686.95</v>
       </c>
       <c r="E75" t="n">
-        <v>401.27</v>
+        <v>702.47</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.52</v>
+        <v>-2.21</v>
       </c>
       <c r="G75" t="n">
-        <v>391.41</v>
+        <v>705.49</v>
       </c>
       <c r="H75" t="n">
-        <v>50.97</v>
+        <v>45.48</v>
       </c>
       <c r="I75" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>368.4</v>
+        <v>657</v>
       </c>
       <c r="L75" t="n">
-        <v>6.18</v>
+        <v>4.56</v>
       </c>
       <c r="M75" t="n">
         <v>45</v>
@@ -6527,26 +7781,50 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; recovery &gt;=5%; RSI &gt;=50</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
+          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>20.555058</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2.760321</v>
+      </c>
+      <c r="R75" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="S75" t="n">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="T75" t="n">
+        <v>569106890752</v>
+      </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
+      <c r="W75" t="n">
+        <v>42.416</v>
+      </c>
+      <c r="X75" t="n">
+        <v>29.786</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>484.313</v>
+      </c>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr"/>
-      <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6554,7 +7832,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6563,33 +7841,33 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>275.4</v>
+        <v>580.8</v>
       </c>
       <c r="E76" t="n">
-        <v>281.91</v>
+        <v>591.41</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.31</v>
+        <v>-1.79</v>
       </c>
       <c r="G76" t="n">
-        <v>305.75</v>
+        <v>589.87</v>
       </c>
       <c r="H76" t="n">
-        <v>31.51</v>
+        <v>48.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>271.65</v>
+        <v>578.5</v>
       </c>
       <c r="L76" t="n">
-        <v>1.38</v>
+        <v>0.4</v>
       </c>
       <c r="M76" t="n">
         <v>45</v>
@@ -6604,23 +7882,47 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>19.721561</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.6128383</v>
+      </c>
+      <c r="R76" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="S76" t="n">
+        <v>170</v>
+      </c>
+      <c r="T76" t="n">
+        <v>184694390784</v>
+      </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
+      <c r="W76" t="n">
+        <v>17.395</v>
+      </c>
+      <c r="X76" t="n">
+        <v>33.823</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>4.475</v>
+      </c>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
-      <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6628,7 +7930,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6637,33 +7939,33 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>686.95</v>
+        <v>1832.6</v>
       </c>
       <c r="E77" t="n">
-        <v>702.47</v>
+        <v>1856.59</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.21</v>
+        <v>-1.29</v>
       </c>
       <c r="G77" t="n">
-        <v>705.49</v>
+        <v>1947.77</v>
       </c>
       <c r="H77" t="n">
-        <v>45.48</v>
+        <v>34.01</v>
       </c>
       <c r="I77" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>657</v>
+        <v>1815</v>
       </c>
       <c r="L77" t="n">
-        <v>4.56</v>
+        <v>0.97</v>
       </c>
       <c r="M77" t="n">
         <v>45</v>
@@ -6678,23 +7980,47 @@
           <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>45.249382</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>8.203222999999999</v>
+      </c>
+      <c r="R77" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="n">
+        <v>372200767488</v>
+      </c>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
+      <c r="W77" t="n">
+        <v>12.839</v>
+      </c>
+      <c r="X77" t="n">
+        <v>8.984</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>129.033</v>
+      </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr"/>
-      <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6702,7 +8028,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6711,36 +8037,36 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>580.8</v>
+        <v>572.65</v>
       </c>
       <c r="E78" t="n">
-        <v>591.41</v>
+        <v>586.21</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.79</v>
+        <v>-2.31</v>
       </c>
       <c r="G78" t="n">
-        <v>589.87</v>
+        <v>590.52</v>
       </c>
       <c r="H78" t="n">
-        <v>48.08</v>
+        <v>46.52</v>
       </c>
       <c r="I78" t="n">
-        <v>0.66</v>
+        <v>3.63</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>578.5</v>
+        <v>560.5</v>
       </c>
       <c r="L78" t="n">
-        <v>0.4</v>
+        <v>2.17</v>
       </c>
       <c r="M78" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -6749,26 +8075,56 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>20.569326</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.8531164</v>
+      </c>
+      <c r="R78" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="S78" t="n">
+        <v>144</v>
+      </c>
+      <c r="T78" t="n">
+        <v>162278129664</v>
+      </c>
+      <c r="U78" t="n">
+        <v>10.309</v>
+      </c>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
+      <c r="W78" t="n">
+        <v>25.088</v>
+      </c>
+      <c r="X78" t="n">
+        <v>18.333</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>20.684</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>6.018</v>
+      </c>
       <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6776,7 +8132,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6785,22 +8141,22 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11619</v>
+        <v>2733.5</v>
       </c>
       <c r="E79" t="n">
-        <v>11791.8</v>
+        <v>2779.47</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.47</v>
+        <v>-1.65</v>
       </c>
       <c r="G79" t="n">
-        <v>11619.58</v>
+        <v>2960.46</v>
       </c>
       <c r="H79" t="n">
-        <v>42.89</v>
+        <v>40.61</v>
       </c>
       <c r="I79" t="n">
-        <v>0.68</v>
+        <v>1.65</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -6808,13 +8164,13 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>11570</v>
+        <v>2685</v>
       </c>
       <c r="L79" t="n">
-        <v>0.42</v>
+        <v>1.81</v>
       </c>
       <c r="M79" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -6823,26 +8179,50 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>83.33842</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>6.825559</v>
+      </c>
+      <c r="R79" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="S79" t="n">
+        <v>16</v>
+      </c>
+      <c r="T79" t="n">
+        <v>529129930752</v>
+      </c>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
+      <c r="W79" t="n">
+        <v>7.277</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2.8169999</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>27.724</v>
+      </c>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6850,7 +8230,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6859,22 +8239,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1832.6</v>
+        <v>174.55</v>
       </c>
       <c r="E80" t="n">
-        <v>1857.86</v>
+        <v>172.91</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.36</v>
+        <v>0.95</v>
       </c>
       <c r="G80" t="n">
-        <v>1948.97</v>
+        <v>194.58</v>
       </c>
       <c r="H80" t="n">
-        <v>33.18</v>
+        <v>40.52</v>
       </c>
       <c r="I80" t="n">
-        <v>0.59</v>
+        <v>0.13</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -6882,13 +8262,13 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>1815</v>
+        <v>171</v>
       </c>
       <c r="L80" t="n">
-        <v>0.97</v>
+        <v>2.08</v>
       </c>
       <c r="M80" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -6897,26 +8277,48 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; moving toward 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
+          <t>at/above 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>20.954382</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.0980474</v>
+      </c>
+      <c r="R80" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="S80" t="n">
+        <v>86</v>
+      </c>
+      <c r="T80" t="n">
+        <v>281219530752</v>
+      </c>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>23.771</v>
+      </c>
+      <c r="X80" t="n">
+        <v>13.617</v>
+      </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6924,7 +8326,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6933,33 +8335,33 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>572.65</v>
+        <v>208.64</v>
       </c>
       <c r="E81" t="n">
-        <v>585.89</v>
+        <v>203.14</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.26</v>
+        <v>2.71</v>
       </c>
       <c r="G81" t="n">
-        <v>589.6799999999999</v>
+        <v>211.78</v>
       </c>
       <c r="H81" t="n">
-        <v>46.83</v>
+        <v>45.38</v>
       </c>
       <c r="I81" t="n">
-        <v>3.66</v>
+        <v>0.34</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>560.5</v>
+        <v>200.74</v>
       </c>
       <c r="L81" t="n">
-        <v>2.17</v>
+        <v>3.94</v>
       </c>
       <c r="M81" t="n">
         <v>35</v>
@@ -6971,26 +8373,48 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
+          <t>at/above 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>14.744877</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.9565442</v>
+      </c>
+      <c r="R81" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="S81" t="n">
+        <v>96</v>
+      </c>
+      <c r="T81" t="n">
+        <v>206717861888</v>
+      </c>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
+      <c r="W81" t="n">
+        <v>50.985</v>
+      </c>
+      <c r="X81" t="n">
+        <v>37.791002</v>
+      </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr"/>
-      <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6998,7 +8422,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7007,36 +8431,36 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2733.5</v>
+        <v>442.7</v>
       </c>
       <c r="E82" t="n">
-        <v>2780.66</v>
+        <v>452.25</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.7</v>
+        <v>-2.11</v>
       </c>
       <c r="G82" t="n">
-        <v>2965.3</v>
+        <v>459.79</v>
       </c>
       <c r="H82" t="n">
-        <v>40.55</v>
+        <v>42.83</v>
       </c>
       <c r="I82" t="n">
-        <v>1.67</v>
+        <v>0.51</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>2685</v>
+        <v>441.35</v>
       </c>
       <c r="L82" t="n">
-        <v>1.81</v>
+        <v>0.31</v>
       </c>
       <c r="M82" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -7045,26 +8469,50 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>within 3% of 200DMA; above breakdown low; volume &gt;=1.2x</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>9.207571</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.7019919</v>
+      </c>
+      <c r="R82" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="S82" t="n">
+        <v>271</v>
+      </c>
+      <c r="T82" t="n">
+        <v>177368776704</v>
+      </c>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
+      <c r="W82" t="n">
+        <v>15.151</v>
+      </c>
+      <c r="X82" t="n">
+        <v>9.581000000000001</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>10.274</v>
+      </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -7072,7 +8520,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7081,36 +8529,36 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>174.55</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E83" t="n">
-        <v>172.91</v>
+        <v>78.41</v>
       </c>
       <c r="F83" t="n">
-        <v>0.95</v>
+        <v>-1.93</v>
       </c>
       <c r="G83" t="n">
-        <v>194.58</v>
+        <v>78.06</v>
       </c>
       <c r="H83" t="n">
-        <v>40.52</v>
+        <v>42.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="L83" t="n">
-        <v>2.08</v>
+        <v>1.18</v>
       </c>
       <c r="M83" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -7119,26 +8567,50 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>28.168499</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.8688183</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S83" t="n">
+        <v>209</v>
+      </c>
+      <c r="T83" t="n">
+        <v>772463198208</v>
+      </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
+      <c r="W83" t="n">
+        <v>46.019</v>
+      </c>
+      <c r="X83" t="n">
+        <v>31.094998</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>113.111</v>
+      </c>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7146,7 +8618,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7155,36 +8627,36 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>208.64</v>
+        <v>667.3</v>
       </c>
       <c r="E84" t="n">
-        <v>203.14</v>
+        <v>679.91</v>
       </c>
       <c r="F84" t="n">
-        <v>2.71</v>
+        <v>-1.86</v>
       </c>
       <c r="G84" t="n">
-        <v>211.78</v>
+        <v>669.54</v>
       </c>
       <c r="H84" t="n">
-        <v>45.38</v>
+        <v>47.49</v>
       </c>
       <c r="I84" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>200.74</v>
+        <v>664.2</v>
       </c>
       <c r="L84" t="n">
-        <v>3.94</v>
+        <v>0.47</v>
       </c>
       <c r="M84" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -7193,248 +8665,50 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>at/above 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+          <t>within 3% of 200DMA; above breakdown low</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>79.34601600000001</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.1554037</v>
+      </c>
+      <c r="R84" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="S84" t="n">
+        <v>51</v>
+      </c>
+      <c r="T84" t="n">
+        <v>337622401024</v>
+      </c>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
+      <c r="W84" t="n">
+        <v>91.65100000000001</v>
+      </c>
+      <c r="X84" t="n">
+        <v>105.248</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0.007</v>
+      </c>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr"/>
-      <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>442.7</v>
-      </c>
-      <c r="E85" t="n">
-        <v>452.01</v>
-      </c>
-      <c r="F85" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="G85" t="n">
-        <v>459.21</v>
-      </c>
-      <c r="H85" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>441.35</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M85" t="n">
-        <v>25</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>NEAR 200DMA</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
-      <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E86" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="F86" t="n">
-        <v>-1.93</v>
-      </c>
-      <c r="G86" t="n">
-        <v>78.06</v>
-      </c>
-      <c r="H86" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>76</v>
-      </c>
-      <c r="L86" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M86" t="n">
-        <v>25</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>NEAR 200DMA</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
-      <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TATAINVEST</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>667.3</v>
-      </c>
-      <c r="E87" t="n">
-        <v>679.91</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="G87" t="n">
-        <v>669.54</v>
-      </c>
-      <c r="H87" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>664.2</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M87" t="n">
-        <v>25</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>NEAR 200DMA</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>within 3% of 200DMA; above breakdown low</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
-      <c r="AC87" t="inlineStr"/>
-      <c r="AD87" t="inlineStr"/>
-      <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>4.100000000000001</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
